--- a/output/Каталог_2019_май.xlsx
+++ b/output/Каталог_2019_май.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум. Фотографирование Первого Президента РК – Елбасы Н.А.Назарбаева и Президента РК К.-Ж.Токаева (проверить). Фото-сессия (съёмка фотографирования). Оператор: Абилов.</t>
+          <t>XII Астанинский экономический форум. Церемония фотографирования Первого Президента РК – Елбасы Н.А.Назарбаева и Президента РК К.-Ж.Токаева. Оператор: Абилов.</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>31.05.19 PRK i D.Tusk 1 etazh stacionar.1</t>
+          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. Abilov.,xcode mix,40.1</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
@@ -1540,14 +1540,14 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Встреча Президента РК (PRK) с Председателем Европейского совета Д.Туском. Стационар.</t>
+          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Абилов.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. Abilov.,xcode mix,40.1</t>
+          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. N.Kulmanov.,xcode mix,41.1</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
@@ -1555,14 +1555,14 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Абилов.</t>
+          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Н.Кульманов.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. N.Kulmanov.,xcode mix,41.1</t>
+          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. Prohodka. Abilov.,xcode mix,30.1</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
@@ -1570,14 +1570,14 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Н.Кульманов.</t>
+          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Проходка. Оператор: Абилов.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. Prohodka. Abilov.,xcode mix,30.1</t>
+          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. X.O.,xcode mix,52.1</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
@@ -1585,14 +1585,14 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Проходка. Оператор: Абилов.</t>
+          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Х.О.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. X.O.,xcode mix,52.1</t>
+          <t>31.05.2019 Elbasy vruch.diplomov. NU Krupn.plan.1</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
@@ -1600,14 +1600,14 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Х.О.</t>
+          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. Крупный план.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>31.05.2019 Elbasy vruch.diplomov. NU Krupn.plan.1</t>
+          <t>31.05.2019 Elbasy vruch.diplomy. NU PGM 2,xcode mix,49.1</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
@@ -1615,14 +1615,14 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. Крупный план.</t>
+          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. PGM (программный микс).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>31.05.2019 Elbasy vruch.diplomy. NU PGM 2,xcode mix,49.1</t>
+          <t>31.05.2019 Vruch.diplomy. NU Krupn.plan. bez Elbasy.1</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
@@ -1630,14 +1630,14 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. PGM (программный микс).</t>
+          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. Крупный план; без Елбасы.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>31.05.2019 Vruch.diplomy. NU Krupn.plan. bez Elbasy.1</t>
+          <t>31.05.2019 Vruch.diplomy. NU PGM 1 bez Elbasy,xcode mix,66.1</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
@@ -1645,50 +1645,35 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. Крупный план; без Елбасы.</t>
+          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. PGM (программный микс); без Елбасы.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>31.05.2019 Vruch.diplomy. NU PGM 1 bez Elbasy,xcode mix,66.1</t>
+          <t>21.06.19 Almaty Konferenciya Kr.Plan SKJ-8,xcode mix,35.1</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>43616</v>
+        <v>43637</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. PGM (программный микс); без Елбасы.</t>
+          <t>Международная научно-практическая конференция «30 лет лидерства» с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Выступление Елбасы. г. Алматы (по имени файла). Крупный план.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>21.06.19 Almaty Konferenciya Kr.Plan SKJ-8,xcode mix,35.1</t>
+          <t>21.06.19 Almaty Konferenciya PGM SKJ-5  166_0243.1</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
         <v>43637</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Международная научно-практическая конференция «30 лет лидерства» с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Выступление Елбасы. г. Алматы (по имени файла). Крупный план.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>21.06.19 Almaty Konferenciya PGM SKJ-5  166_0243.1</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="n">
-        <v>43637</v>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Международная научно-практическая конференция «30 лет лидерства» с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Выступление Елбасы. г. Алматы (по имени файла). PGM (программный микс).</t>
         </is>
@@ -1705,7 +1690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -3063,45 +3048,41 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>16.05.2019_AEF_Foto Elbasy i PRK_Abilov_66,xcode mix,288.1</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="3" t="n">
         <v>43601</v>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>XII Астанинский экономический форум. Фотографирование Первого Президента РК – Елбасы Н.А.Назарбаева и Президента РК К.-Ж.Токаева (проверить). Фото-сессия (съёмка фотографирования). Оператор: Абилов.</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>XII Астанинский экономический форум. Церемония фотографирования Первого Президента РК – Елбасы Н.А.Назарбаева и Президента РК К.-Ж.Токаева. Оператор: Абилов.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Фото-сессия (съёмка фотографирования)</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Абилов</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>PRK = Президент РК К.-Ж.Токаев (с 20.03.2019) — проверить по видео.</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-nursultan-nazarbaev-prinyal-uchastie-v-rabote-xii-astaninskogo-ekonomicheskogo</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики»</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
 - Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
@@ -3112,7 +3093,7 @@
 С полным текстом выступления можно ознакомиться здесь.</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
@@ -5087,41 +5068,37 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>31.05.19 PRK i D.Tusk 1 etazh stacionar.1</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="n">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. Abilov.,xcode mix,40.1</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
         <v>43616</v>
       </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>Встреча Президента РК (PRK) с Председателем Европейского совета Д.Туском. Стационар.</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>Стационар</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>PRK = Президент РК — в мае 2019 это К.-Ж.Токаев. Проверить по видео, чья это встреча с Д.Туском.</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Абилов.</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Абилов</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-vstretilsya-s-predsedatelem-evropeyskogo-soveta-donaldom</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана встретился с Председателем Европейского совета Дональдом Туском</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Поприветствовав гостя, Нурсултан Назарбаев отметил высокий уровень развития взаимоотношений между Казахстаном и Европейским союзом.
 - Мы встречались с вами несколько раз. В период вашего председательства было заключено Соглашение о расширенном партнерстве и сотрудничестве между Европейским Союзом и Республикой Казахстан. В этом году ожидается завершение его ратификации. В целом, у нас хорошие перспективы, - сказал Елбасы.
@@ -5130,7 +5107,7 @@
 Пресс-служба Первого Президента РК – Елбасы</t>
         </is>
       </c>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
@@ -5139,7 +5116,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. Abilov.,xcode mix,40.1</t>
+          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. N.Kulmanov.,xcode mix,41.1</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
@@ -5147,13 +5124,13 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Абилов.</t>
+          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Н.Кульманов.</t>
         </is>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Абилов</t>
+          <t>Н.Кульманов</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -5185,7 +5162,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. N.Kulmanov.,xcode mix,41.1</t>
+          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. Prohodka. Abilov.,xcode mix,30.1</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
@@ -5193,13 +5170,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Н.Кульманов.</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="n"/>
+          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Проходка. Оператор: Абилов.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Проходка</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Н.Кульманов</t>
+          <t>Абилов</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -5231,7 +5212,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. Prohodka. Abilov.,xcode mix,30.1</t>
+          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. X.O.,xcode mix,52.1</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
@@ -5239,17 +5220,13 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Проходка. Оператор: Абилов.</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Проходка</t>
-        </is>
-      </c>
+          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Х.О.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Абилов</t>
+          <t>Х.О.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -5281,7 +5258,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>31.05.19 Vstrecha Elbasy s D.Tuskom. X.O.,xcode mix,52.1</t>
+          <t>31.05.2019 Elbasy vruch.diplomov. NU Krupn.plan.1</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
@@ -5289,73 +5266,27 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Х.О.</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Х.О.</t>
-        </is>
-      </c>
+          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. Крупный план.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Крупный план</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-vstretilsya-s-predsedatelem-evropeyskogo-soveta-donaldom</t>
+          <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-vruchil-diplomy-s-otlichiem-vypusknikam-nazarbaev</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Первый Президент Казахстана встретился с Председателем Европейского совета Дональдом Туском</t>
+          <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>Поприветствовав гостя, Нурсултан Назарбаев отметил высокий уровень развития взаимоотношений между Казахстаном и Европейским союзом.
-- Мы встречались с вами несколько раз. В период вашего председательства было заключено Соглашение о расширенном партнерстве и сотрудничестве между Европейским Союзом и Республикой Казахстан. В этом году ожидается завершение его ратификации. В целом, у нас хорошие перспективы, - сказал Елбасы.
-В свою очередь Дональд Туск подчеркнул особую роль Нурсултана Назарбаева в становлении и развитии Казахстана, укреплении международного авторитета страны.
-- Ваша роль в регионе особая и важная. Я очень рад встретиться с Вами. Мы высоко ценим Ваш разумный и ответственный подход в транзите власти. Думаю, что вся Европа была впечатлена этим шагом, - отметил Председатель Европейского совета.
-Пресс-служба Первого Президента РК – Елбасы</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>31.05.2019 Elbasy vruch.diplomov. NU Krupn.plan.1</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="n">
-        <v>43616</v>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. Крупный план.</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Крупный план</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-vruchil-diplomy-s-otlichiem-vypusknikam-nazarbaev</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
 - Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
@@ -5370,44 +5301,44 @@
 Пресс-служба Первого Президента РК – Елбасы</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>31.05.2019 Elbasy vruch.diplomy. NU PGM 2,xcode mix,49.1</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n">
+      <c r="B78" s="3" t="n">
         <v>43616</v>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. PGM (программный микс).</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>PGM (программный микс)</t>
         </is>
       </c>
-      <c r="E79" s="2" t="n"/>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-vruchil-diplomy-s-otlichiem-vypusknikam-nazarbaev</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
 - Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
@@ -5422,44 +5353,44 @@
 Пресс-служба Первого Президента РК – Елбасы</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>31.05.2019 Vruch.diplomy. NU Krupn.plan. bez Elbasy.1</t>
         </is>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B79" s="3" t="n">
         <v>43616</v>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. Крупный план; без Елбасы.</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Крупный план; без Елбасы</t>
         </is>
       </c>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-vruchil-diplomy-s-otlichiem-vypusknikam-nazarbaev</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
 - Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
@@ -5474,44 +5405,44 @@
 Пресс-служба Первого Президента РК – Елбасы</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>31.05.2019 Vruch.diplomy. NU PGM 1 bez Elbasy,xcode mix,66.1</t>
         </is>
       </c>
-      <c r="B81" s="3" t="n">
+      <c r="B80" s="3" t="n">
         <v>43616</v>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. PGM (программный микс); без Елбасы.</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>PGM (программный микс); без Елбасы</t>
         </is>
       </c>
-      <c r="E81" s="2" t="n"/>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-vruchil-diplomy-s-otlichiem-vypusknikam-nazarbaev</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
 - Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
@@ -5526,48 +5457,48 @@
 Пресс-служба Первого Президента РК – Елбасы</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>21.06.19 Almaty Konferenciya Kr.Plan SKJ-8,xcode mix,35.1</t>
         </is>
       </c>
-      <c r="B82" s="5" t="n">
+      <c r="B81" s="5" t="n">
         <v>43637</v>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>Международная научно-практическая конференция «30 лет лидерства» с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Выступление Елбасы. г. Алматы (по имени файла). Крупный план.</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>Крупный план</t>
         </is>
       </c>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>Дата 21.06.2019 подтверждена: на сайте в этот день конференция «30 лет лидерства».</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/pervyy-prezident-kazakhstana-prinyal-uchastie-v-mezhdunarodnoy-nauchno-prakticheskoy</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="H81" s="4" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана принял участие в Международной научно-практической конференции «30 лет лидерства»</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr">
+      <c r="I81" s="4" t="inlineStr">
         <is>
           <t>Выступая перед участниками конференции, Елбасы отметил, что вся его деятельность на посту первого руководителя страны была посвящена развитию Казахстана.
 Нурсултан Назарбаев рассказал о трудностях на пути строительства и становления Независимости. В частности, Первый Президент Казахстана напомнил о ситуации в стране в начале 1990-х годов, связанной с развалом национальной экономики и рисками возникновения межэтнических конфликтов.
@@ -5580,48 +5511,48 @@
 Пресс-служба Первого Президента РК – Елбасы</t>
         </is>
       </c>
-      <c r="J82" s="4" t="inlineStr">
+      <c r="J81" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>21.06.19 Almaty Konferenciya PGM SKJ-5  166_0243.1</t>
         </is>
       </c>
-      <c r="B83" s="5" t="n">
+      <c r="B82" s="5" t="n">
         <v>43637</v>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Международная научно-практическая конференция «30 лет лидерства» с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Выступление Елбасы. г. Алматы (по имени файла). PGM (программный микс).</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>PGM (программный микс)</t>
         </is>
       </c>
-      <c r="E83" s="4" t="n"/>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>Дата 21.06.2019 подтверждена: на сайте в этот день конференция «30 лет лидерства».</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/pervyy-prezident-kazakhstana-prinyal-uchastie-v-mezhdunarodnoy-nauchno-prakticheskoy</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана принял участие в Международной научно-практической конференции «30 лет лидерства»</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>Выступая перед участниками конференции, Елбасы отметил, что вся его деятельность на посту первого руководителя страны была посвящена развитию Казахстана.
 Нурсултан Назарбаев рассказал о трудностях на пути строительства и становления Независимости. В частности, Первый Президент Казахстана напомнил о ситуации в стране в начале 1990-х годов, связанной с развалом национальной экономики и рисками возникновения межэтнических конфликтов.
@@ -5634,7 +5565,7 @@
 Пресс-служба Первого Президента РК – Елбасы</t>
         </is>
       </c>
-      <c r="J83" s="4" t="inlineStr">
+      <c r="J82" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>

--- a/output/Каталог_2019_май.xlsx
+++ b/output/Каталог_2019_май.xlsx
@@ -475,7 +475,14 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Первый Президент РК – Елбасы Н.А.Назарбаев на народных гуляниях по случаю Дня единства народа Казахстана. Выступление Елбасы перед жителями и гостями столицы. Оператор: Джаватаров.</t>
+          <t>Елбасы Нурсултан Назарбаев посетил народные гуляния по случаю празднования Дня единства народа Казахстана.
+Выступая перед жителями и гостями столицы, Первый Президент Нурсултан Назарбаев поздравил всех казахстанцев с праздником единства народа Казахстана.
+- Благодаря единству наши предки преодолели все трудности, сохранив для нас Великую степь. Мы вместе создали независимый Казахстан, тем самым исполнив мечту наших прадедов, - сказал Нурсултан Назарбаев.
+Елбасы отметил, что все успехи современного Казахстана достигнуты благодаря сплоченности общества, и призвал всех ценить и беречь мирную жизнь и стабильность.
+- Мы – счастливый народ. Нам необходимо беречь наше единство и уважать Независимость. Осуществление наших программ развития приведет страну к еще более светлому будущему, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана рассказал о современных вызовах, возникающих в мире на почве межэтнических конфликтов.
+- Желаю каждому дому, каждой семье крепкого здоровья, благополучия, счастья и уверенности в завтрашнем дне. С праздником! - заключил Елбасы.
+Оператор: Джаватаров.</t>
         </is>
       </c>
     </row>
@@ -490,7 +497,14 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Первый Президент РК – Елбасы Н.А.Назарбаев на народных гуляниях по случаю Дня единства народа Казахстана. Выступление Елбасы перед жителями и гостями столицы. Оператор: Кульманов.</t>
+          <t>Елбасы Нурсултан Назарбаев посетил народные гуляния по случаю празднования Дня единства народа Казахстана.
+Выступая перед жителями и гостями столицы, Первый Президент Нурсултан Назарбаев поздравил всех казахстанцев с праздником единства народа Казахстана.
+- Благодаря единству наши предки преодолели все трудности, сохранив для нас Великую степь. Мы вместе создали независимый Казахстан, тем самым исполнив мечту наших прадедов, - сказал Нурсултан Назарбаев.
+Елбасы отметил, что все успехи современного Казахстана достигнуты благодаря сплоченности общества, и призвал всех ценить и беречь мирную жизнь и стабильность.
+- Мы – счастливый народ. Нам необходимо беречь наше единство и уважать Независимость. Осуществление наших программ развития приведет страну к еще более светлому будущему, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана рассказал о современных вызовах, возникающих в мире на почве межэтнических конфликтов.
+- Желаю каждому дому, каждой семье крепкого здоровья, благополучия, счастья и уверенности в завтрашнем дне. С праздником! - заключил Елбасы.
+Оператор: Кульманов.</t>
         </is>
       </c>
     </row>
@@ -505,7 +519,10 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с академиком, учёным-литературоведом С.Кирабаевым. Обсуждение развития отечественной литературы, вопросов образования и науки. Оператор: Х.О.</t>
+          <t>Елбасы Нурсултан Назарбаев принял академика Серика Кирабаева.
+Первый Президент Казахстана и известный ученый-литературовед обсудили текущее состояние и перспективы развития отечественной литературы. Особое внимание было уделено актуальным вопросам образования и науки.
+В ходе беседы С. Кирабаев выразил поддержку решению Нурсултана Назарбаева о сложении полномочий Президента и пожелал Елбасы успехов в дальнейшей деятельности.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -520,7 +537,10 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с академиком, учёным-литературоведом С.Кирабаевым. Обсуждение развития отечественной литературы, вопросов образования и науки. Оператор: Д.Али.</t>
+          <t>Елбасы Нурсултан Назарбаев принял академика Серика Кирабаева.
+Первый Президент Казахстана и известный ученый-литературовед обсудили текущее состояние и перспективы развития отечественной литературы. Особое внимание было уделено актуальным вопросам образования и науки.
+В ходе беседы С. Кирабаев выразил поддержку решению Нурсултана Назарбаева о сложении полномочий Президента и пожелал Елбасы успехов в дальнейшей деятельности.
+Оператор: Д.Али.</t>
         </is>
       </c>
     </row>
@@ -535,7 +555,10 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с академиком, учёным-литературоведом С.Кирабаевым. Обсуждение развития отечественной литературы, вопросов образования и науки. Оператор: Д.Тлеспаев.</t>
+          <t>Елбасы Нурсултан Назарбаев принял академика Серика Кирабаева.
+Первый Президент Казахстана и известный ученый-литературовед обсудили текущее состояние и перспективы развития отечественной литературы. Особое внимание было уделено актуальным вопросам образования и науки.
+В ходе беседы С. Кирабаев выразил поддержку решению Нурсултана Назарбаева о сложении полномочий Президента и пожелал Елбасы успехов в дальнейшей деятельности.
+Оператор: Д.Тлеспаев.</t>
         </is>
       </c>
     </row>
@@ -550,7 +573,10 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с академиком У.Калижановым. Информация о деятельности Института литературы и искусства им. М.О.Ауэзова. Оператор: Д.Али.</t>
+          <t>Первый Президент Казахстана принял академика Уалихана Калижанова.
+Нурсултану Назарбаеву была представлена информация о текущей научно-исследовательской деятельности Института литературы и искусства им. М.О.Ауэзова.
+Елбасы отметил вклад академика в развитие отечественной литературы и искусства, и поблагодарил за плодотворную работу во имя процветания Казахстана.
+Оператор: Д.Али.</t>
         </is>
       </c>
     </row>
@@ -565,7 +591,10 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с академиком У.Калижановым. Информация о деятельности Института литературы и искусства им. М.О.Ауэзова. Оператор: Д.Тлеспаев.</t>
+          <t>Первый Президент Казахстана принял академика Уалихана Калижанова.
+Нурсултану Назарбаеву была представлена информация о текущей научно-исследовательской деятельности Института литературы и искусства им. М.О.Ауэзова.
+Елбасы отметил вклад академика в развитие отечественной литературы и искусства, и поблагодарил за плодотворную работу во имя процветания Казахстана.
+Оператор: Д.Тлеспаев.</t>
         </is>
       </c>
     </row>
@@ -580,7 +609,10 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с академиком У.Калижановым. Информация о деятельности Института литературы и искусства им. М.О.Ауэзова. Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана принял академика Уалихана Калижанова.
+Нурсултану Назарбаеву была представлена информация о текущей научно-исследовательской деятельности Института литературы и искусства им. М.О.Ауэзова.
+Елбасы отметил вклад академика в развитие отечественной литературы и искусства, и поблагодарил за плодотворную работу во имя процветания Казахстана.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -655,7 +687,11 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с управляющим Международным финансовым центром «Астана» К.Келимбетовым. Оператор: А.И.</t>
+          <t>Первый Президент Казахстана принял Управляющего Международным финансовым центром «Астана» Кайрата Келимбетова.
+В ходе встречи Елбасы Н.Назарбаеву была представлена информация о текущей деятельности и дальнейших планах работы МФЦА.
+Нурсултан Назарбаев подчеркнул важность проводимой работы по развитию Международного финансового центра «Астана».
+- МФЦА – один из наших крупнейших и важных проектов. Мы возлагаем на него большие надежды, связанные с тем, что он станет финансовым центром не только Казахстана, но и всего региона. МФЦА будет развиваться по пути других финансовых центров мира. Я хочу, чтобы мы добились здесь успеха, - сказал Первый Президент Казахстана.
+Оператор: А.И.</t>
         </is>
       </c>
     </row>
@@ -670,7 +706,11 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с управляющим Международным финансовым центром «Астана» К.Келимбетовым. Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана принял Управляющего Международным финансовым центром «Астана» Кайрата Келимбетова.
+В ходе встречи Елбасы Н.Назарбаеву была представлена информация о текущей деятельности и дальнейших планах работы МФЦА.
+Нурсултан Назарбаев подчеркнул важность проводимой работы по развитию Международного финансового центра «Астана».
+- МФЦА – один из наших крупнейших и важных проектов. Мы возлагаем на него большие надежды, связанные с тем, что он станет финансовым центром не только Казахстана, но и всего региона. МФЦА будет развиваться по пути других финансовых центров мира. Я хочу, чтобы мы добились здесь успеха, - сказал Первый Президент Казахстана.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -685,7 +725,11 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с управляющим Международным финансовым центром «Астана» К.Келимбетовым. Оператор: Н.Баткеев.</t>
+          <t>Первый Президент Казахстана принял Управляющего Международным финансовым центром «Астана» Кайрата Келимбетова.
+В ходе встречи Елбасы Н.Назарбаеву была представлена информация о текущей деятельности и дальнейших планах работы МФЦА.
+Нурсултан Назарбаев подчеркнул важность проводимой работы по развитию Международного финансового центра «Астана».
+- МФЦА – один из наших крупнейших и важных проектов. Мы возлагаем на него большие надежды, связанные с тем, что он станет финансовым центром не только Казахстана, но и всего региона. МФЦА будет развиваться по пути других финансовых центров мира. Я хочу, чтобы мы добились здесь успеха, - сказал Первый Президент Казахстана.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
     </row>
@@ -700,7 +744,13 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Чрезвычайным и Полномочным Послом США в Казахстане У.Мозером. Посол передал Елбасы письмо Президента США Д.Трампа. Оператор: А.И.</t>
+          <t>Нурсултан Назарбаев встретился с Чрезвычайным и Полномочным Послом Соединенных Штатов Америки в Казахстане Уильямом Мозером.
+Елбасы поздравил У. Мозера с началом дипломатической миссии в Казахстане, пожелав успехов и достижений на ответственном посту.
+- За все эти годы мы построили с США отношения, основанные на взаимопонимании и дружбе. В Казахстан пришли большие инвестиции из США. Работают 420 совместных предприятий. Мой визит в Вашингтон в прошлом году, в рамках которого состоялись переговоры с Президентом Трампом и встречи с бизнесменами, создал условия для дальнейшего развития нашего сотрудничества, - сказал Первый Президент Казахстана.
+В свою очередь Уильям Мозер поделился своими воспоминаниями о его первом визите в Казахстан. Посол США отметил достигнутые за относительно короткий период впечатляющие результаты в строительстве и позиционировании столицы страны – Нур-Султана.
+Кроме того, Посол США передал Нурсултану Назарбаеву письмо Дональда Трампа, в котором Президент США выражает поддержку принятому Елбасы решению о сложении полномочий и мирной передаче управления страной новому поколению политиков.
+- Я получил письмо Президента Трампа. Он выразил намерение встречаться и советоваться со мной в будущем по ситуации в нашем регионе. С Дональдом Трампом у нас сложились хорошие отношения, я готов поддерживать такие контакты. США являются для нас важным партнером. Все эти годы у нас были только дружеские отношения. Уверен, что политика подобного сотрудничества будет продолжена, – заключил Нурсултан Назарбаев.
+Оператор: А.И.</t>
         </is>
       </c>
     </row>
@@ -715,7 +765,13 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Чрезвычайным и Полномочным Послом США в Казахстане У.Мозером. Посол передал Елбасы письмо Президента США Д.Трампа. Оператор: Х.О.</t>
+          <t>Нурсултан Назарбаев встретился с Чрезвычайным и Полномочным Послом Соединенных Штатов Америки в Казахстане Уильямом Мозером.
+Елбасы поздравил У. Мозера с началом дипломатической миссии в Казахстане, пожелав успехов и достижений на ответственном посту.
+- За все эти годы мы построили с США отношения, основанные на взаимопонимании и дружбе. В Казахстан пришли большие инвестиции из США. Работают 420 совместных предприятий. Мой визит в Вашингтон в прошлом году, в рамках которого состоялись переговоры с Президентом Трампом и встречи с бизнесменами, создал условия для дальнейшего развития нашего сотрудничества, - сказал Первый Президент Казахстана.
+В свою очередь Уильям Мозер поделился своими воспоминаниями о его первом визите в Казахстан. Посол США отметил достигнутые за относительно короткий период впечатляющие результаты в строительстве и позиционировании столицы страны – Нур-Султана.
+Кроме того, Посол США передал Нурсултану Назарбаеву письмо Дональда Трампа, в котором Президент США выражает поддержку принятому Елбасы решению о сложении полномочий и мирной передаче управления страной новому поколению политиков.
+- Я получил письмо Президента Трампа. Он выразил намерение встречаться и советоваться со мной в будущем по ситуации в нашем регионе. С Дональдом Трампом у нас сложились хорошие отношения, я готов поддерживать такие контакты. США являются для нас важным партнером. Все эти годы у нас были только дружеские отношения. Уверен, что политика подобного сотрудничества будет продолжена, – заключил Нурсултан Назарбаев.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -730,7 +786,13 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Чрезвычайным и Полномочным Послом США в Казахстане У.Мозером. Посол передал Елбасы письмо Президента США Д.Трампа. Оператор: Н.Баткеев.</t>
+          <t>Нурсултан Назарбаев встретился с Чрезвычайным и Полномочным Послом Соединенных Штатов Америки в Казахстане Уильямом Мозером.
+Елбасы поздравил У. Мозера с началом дипломатической миссии в Казахстане, пожелав успехов и достижений на ответственном посту.
+- За все эти годы мы построили с США отношения, основанные на взаимопонимании и дружбе. В Казахстан пришли большие инвестиции из США. Работают 420 совместных предприятий. Мой визит в Вашингтон в прошлом году, в рамках которого состоялись переговоры с Президентом Трампом и встречи с бизнесменами, создал условия для дальнейшего развития нашего сотрудничества, - сказал Первый Президент Казахстана.
+В свою очередь Уильям Мозер поделился своими воспоминаниями о его первом визите в Казахстан. Посол США отметил достигнутые за относительно короткий период впечатляющие результаты в строительстве и позиционировании столицы страны – Нур-Султана.
+Кроме того, Посол США передал Нурсултану Назарбаеву письмо Дональда Трампа, в котором Президент США выражает поддержку принятому Елбасы решению о сложении полномочий и мирной передаче управления страной новому поколению политиков.
+- Я получил письмо Президента Трампа. Он выразил намерение встречаться и советоваться со мной в будущем по ситуации в нашем регионе. С Дональдом Трампом у нас сложились хорошие отношения, я готов поддерживать такие контакты. США являются для нас важным партнером. Все эти годы у нас были только дружеские отношения. Уверен, что политика подобного сотрудничества будет продолжена, – заключил Нурсултан Назарбаев.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
     </row>
@@ -745,7 +807,14 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Посещение Первым Президентом РК – Елбасы Н.А.Назарбаевым Международного центра зелёных технологий и инвестиционных проектов. Презентация цифровой площадки по возобновляемым источникам энергии, проектов казахстанских вузов. Исходник SBS.</t>
+          <t>Елбасы Нурсултан Назарбаев посетил Международный центр зеленых технологий и инвестиционных проектов.
+В ходе посещения Первому Президенту Казахстана была представлена информация по основным направлениям работы Центра в сфере развития зеленой экономики и обеспечения безопасности окружающей среды.
+Елбасы Н. Назарбаеву был презентован прототип цифровой площадки, объединяющей информацию о потенциале ветровых, солнечных, гидро- и геотермальных ресурсов, расположении полигонов ТБО и биомассы.
+Нурсултан Назарбаев подчеркнул необходимость обеспечения экологической безопасности и развития возобновляемых источников энергии в стране.
+Елбасы акцентировал внимание на вопросах внедрения передовых технологий в сфере переработки ТБО и привлечения инвесторов в данную отрасль.
+Первый Президент Казахстана также ознакомился с рядом проектов и перспективными разработками казахстанских вузов в сфере возобновляемых источников энергии.
+НАО «Международный центр зеленых технологий и инвестиционных проектов» (IGTIC) был создан в апреле 2018 года на базе инфраструктуры и наследия выставки «Астана – ЭКСПО 2017».
+Исходник SBS.</t>
         </is>
       </c>
     </row>
@@ -760,7 +829,14 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Посещение Первым Президентом РК – Елбасы Н.А.Назарбаевым Международного центра зелёных технологий и инвестиционных проектов. Презентация цифровой площадки по возобновляемым источникам энергии, проектов казахстанских вузов. Исходник SBS.</t>
+          <t>Елбасы Нурсултан Назарбаев посетил Международный центр зеленых технологий и инвестиционных проектов.
+В ходе посещения Первому Президенту Казахстана была представлена информация по основным направлениям работы Центра в сфере развития зеленой экономики и обеспечения безопасности окружающей среды.
+Елбасы Н. Назарбаеву был презентован прототип цифровой площадки, объединяющей информацию о потенциале ветровых, солнечных, гидро- и геотермальных ресурсов, расположении полигонов ТБО и биомассы.
+Нурсултан Назарбаев подчеркнул необходимость обеспечения экологической безопасности и развития возобновляемых источников энергии в стране.
+Елбасы акцентировал внимание на вопросах внедрения передовых технологий в сфере переработки ТБО и привлечения инвесторов в данную отрасль.
+Первый Президент Казахстана также ознакомился с рядом проектов и перспективными разработками казахстанских вузов в сфере возобновляемых источников энергии.
+НАО «Международный центр зеленых технологий и инвестиционных проектов» (IGTIC) был создан в апреле 2018 года на базе инфраструктуры и наследия выставки «Астана – ЭКСПО 2017».
+Исходник SBS.</t>
         </is>
       </c>
     </row>
@@ -775,7 +851,14 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Посещение Первым Президентом РК – Елбасы Н.А.Назарбаевым Международного центра зелёных технологий и инвестиционных проектов. Презентация цифровой площадки по возобновляемым источникам энергии, проектов казахстанских вузов. Исходник SBS.</t>
+          <t>Елбасы Нурсултан Назарбаев посетил Международный центр зеленых технологий и инвестиционных проектов.
+В ходе посещения Первому Президенту Казахстана была представлена информация по основным направлениям работы Центра в сфере развития зеленой экономики и обеспечения безопасности окружающей среды.
+Елбасы Н. Назарбаеву был презентован прототип цифровой площадки, объединяющей информацию о потенциале ветровых, солнечных, гидро- и геотермальных ресурсов, расположении полигонов ТБО и биомассы.
+Нурсултан Назарбаев подчеркнул необходимость обеспечения экологической безопасности и развития возобновляемых источников энергии в стране.
+Елбасы акцентировал внимание на вопросах внедрения передовых технологий в сфере переработки ТБО и привлечения инвесторов в данную отрасль.
+Первый Президент Казахстана также ознакомился с рядом проектов и перспективными разработками казахстанских вузов в сфере возобновляемых источников энергии.
+НАО «Международный центр зеленых технологий и инвестиционных проектов» (IGTIC) был создан в апреле 2018 года на базе инфраструктуры и наследия выставки «Астана – ЭКСПО 2017».
+Исходник SBS.</t>
         </is>
       </c>
     </row>
@@ -790,7 +873,14 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Посещение Первым Президентом РК – Елбасы Н.А.Назарбаевым Международного центра зелёных технологий и инвестиционных проектов. Презентация цифровой площадки по возобновляемым источникам энергии, проектов казахстанских вузов. Исходник XDCAM.</t>
+          <t>Елбасы Нурсултан Назарбаев посетил Международный центр зеленых технологий и инвестиционных проектов.
+В ходе посещения Первому Президенту Казахстана была представлена информация по основным направлениям работы Центра в сфере развития зеленой экономики и обеспечения безопасности окружающей среды.
+Елбасы Н. Назарбаеву был презентован прототип цифровой площадки, объединяющей информацию о потенциале ветровых, солнечных, гидро- и геотермальных ресурсов, расположении полигонов ТБО и биомассы.
+Нурсултан Назарбаев подчеркнул необходимость обеспечения экологической безопасности и развития возобновляемых источников энергии в стране.
+Елбасы акцентировал внимание на вопросах внедрения передовых технологий в сфере переработки ТБО и привлечения инвесторов в данную отрасль.
+Первый Президент Казахстана также ознакомился с рядом проектов и перспективными разработками казахстанских вузов в сфере возобновляемых источников энергии.
+НАО «Международный центр зеленых технологий и инвестиционных проектов» (IGTIC) был создан в апреле 2018 года на базе инфраструктуры и наследия выставки «Астана – ЭКСПО 2017».
+Исходник XDCAM.</t>
         </is>
       </c>
     </row>
@@ -805,7 +895,15 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. Крупный план.</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+Крупный план.</t>
         </is>
       </c>
     </row>
@@ -820,7 +918,15 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. Крупный план.</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+Крупный план.</t>
         </is>
       </c>
     </row>
@@ -835,7 +941,15 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. PGM (программный микс).</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+PGM (программный микс).</t>
         </is>
       </c>
     </row>
@@ -850,7 +964,15 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. PGM (программный микс).</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+PGM (программный микс).</t>
         </is>
       </c>
     </row>
@@ -865,7 +987,15 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. Исходник камеры; без Елбасы.</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+Исходник камеры; без Елбасы.</t>
         </is>
       </c>
     </row>
@@ -880,7 +1010,15 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. Исходник камеры; без Елбасы.</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+Исходник камеры; без Елбасы.</t>
         </is>
       </c>
     </row>
@@ -895,7 +1033,15 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. Личники.</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+Личники.</t>
         </is>
       </c>
     </row>
@@ -910,7 +1056,16 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум. Церемония фотографирования Первого Президента РК – Елбасы Н.А.Назарбаева и Президента РК К.-Ж.Токаева. Оператор: Абилов.</t>
+          <t>XII Астанинский экономический форум. Церемония фотографирования Первого Президента РК – Елбасы Н.А.Назарбаева и Президента РК К.-Ж.Токаева.
+Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+Оператор: Абилов.</t>
         </is>
       </c>
     </row>
@@ -925,7 +1080,11 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Верховного суда РК Ж.Асановым. Доклад о модернизации судебной системы. Оператор: А.И.</t>
+          <t>Первый Президент Казахстана принял председателя Верховного суда Жакипа Асанова.
+Елбасы Н.Назарбаев был проинформирован о ходе модернизации судебной системы.
+Председатель Верховного суда, в частности, доложил, что на сегодняшний день разработано 15 законопроектов, направленных на улучшение качества деятельности судов и повышение доверия населения к работе судей.
+В ходе встречи были также обсуждены вопросы исполнения поручений, данных на совещании от 19 ноября 2018 года.
+Оператор: А.И.</t>
         </is>
       </c>
     </row>
@@ -940,7 +1099,11 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Верховного суда РК Ж.Асановым. Доклад о модернизации судебной системы. Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана принял председателя Верховного суда Жакипа Асанова.
+Елбасы Н.Назарбаев был проинформирован о ходе модернизации судебной системы.
+Председатель Верховного суда, в частности, доложил, что на сегодняшний день разработано 15 законопроектов, направленных на улучшение качества деятельности судов и повышение доверия населения к работе судей.
+В ходе встречи были также обсуждены вопросы исполнения поручений, данных на совещании от 19 ноября 2018 года.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -955,7 +1118,11 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Верховного суда РК Ж.Асановым. Доклад о модернизации судебной системы. Оператор: Н.Баткеев.</t>
+          <t>Первый Президент Казахстана принял председателя Верховного суда Жакипа Асанова.
+Елбасы Н.Назарбаев был проинформирован о ходе модернизации судебной системы.
+Председатель Верховного суда, в частности, доложил, что на сегодняшний день разработано 15 законопроектов, направленных на улучшение качества деятельности судов и повышение доверия населения к работе судей.
+В ходе встречи были также обсуждены вопросы исполнения поручений, данных на совещании от 19 ноября 2018 года.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
     </row>
@@ -970,7 +1137,8 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум, второй день. Без участия Елбасы. Конгресс-центр. Крупный план; без Елбасы.</t>
+          <t>XII Астанинский экономический форум, второй день. Конгресс-центр.
+Крупный план; без Елбасы.</t>
         </is>
       </c>
     </row>
@@ -985,7 +1153,8 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум, второй день. Без участия Елбасы. Конгресс-центр. Крупный план; без Елбасы.</t>
+          <t>XII Астанинский экономический форум, второй день. Конгресс-центр.
+Крупный план; без Елбасы.</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1169,8 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум, второй день. Без участия Елбасы. Конгресс-центр. PGM (программный микс); без Елбасы.</t>
+          <t>XII Астанинский экономический форум, второй день. Конгресс-центр.
+PGM (программный микс); без Елбасы.</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1185,8 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум, второй день. Без участия Елбасы. Конгресс-центр. PGM (программный микс); без Елбасы.</t>
+          <t>XII Астанинский экономический форум, второй день. Конгресс-центр.
+PGM (программный микс); без Елбасы.</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1201,11 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с президентом АОО «Назарбаев Университет» Ш.Катсу. Доклад о развитии университета и подготовке к церемонии вручения дипломов. СНХ (уточнить расшифровку). Оператор: Н.Баткеев.</t>
+          <t>Елбасы принял президента АОО «Назарбаев Университет» Шигео Катсу.
+В ходе встречи Первому Президенту Казахстана было доложено о текущем развитии «Назарбаев Университета» и ходе подготовки к пятой церемонии вручения дипломов выпускникам вуза.
+- Многие не верили, что у нас будет университет международного уровня. И вот Вы уже долгие годы являетесь ректором такого университета. У вуза есть интеллектуальный потенциал – ученые, которые поднимают уровень учебного заведения. «Назарбаев Университет» стал одним из брендов Казахстана, - сказал Елбасы.
+По итогам встречи Нурсултан Назарбаев дал ряд поручений.
+СНХ (уточнить расшифровку). Оператор: Н.Баткеев.</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1220,11 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с президентом АОО «Назарбаев Университет» Ш.Катсу. Доклад о развитии университета и подготовке к церемонии вручения дипломов. Оператор: А.И.</t>
+          <t>Елбасы принял президента АОО «Назарбаев Университет» Шигео Катсу.
+В ходе встречи Первому Президенту Казахстана было доложено о текущем развитии «Назарбаев Университета» и ходе подготовки к пятой церемонии вручения дипломов выпускникам вуза.
+- Многие не верили, что у нас будет университет международного уровня. И вот Вы уже долгие годы являетесь ректором такого университета. У вуза есть интеллектуальный потенциал – ученые, которые поднимают уровень учебного заведения. «Назарбаев Университет» стал одним из брендов Казахстана, - сказал Елбасы.
+По итогам встречи Нурсултан Назарбаев дал ряд поручений.
+Оператор: А.И.</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1239,11 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с президентом АОО «Назарбаев Университет» Ш.Катсу. Доклад о развитии университета и подготовке к церемонии вручения дипломов. Оператор: Х.О.</t>
+          <t>Елбасы принял президента АОО «Назарбаев Университет» Шигео Катсу.
+В ходе встречи Первому Президенту Казахстана было доложено о текущем развитии «Назарбаев Университета» и ходе подготовки к пятой церемонии вручения дипломов выпускникам вуза.
+- Многие не верили, что у нас будет университет международного уровня. И вот Вы уже долгие годы являетесь ректором такого университета. У вуза есть интеллектуальный потенциал – ученые, которые поднимают уровень учебного заведения. «Назарбаев Университет» стал одним из брендов Казахстана, - сказал Елбасы.
+По итогам встречи Нурсултан Назарбаев дал ряд поручений.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1258,11 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с президентом АОО «Назарбаев Университет» Ш.Катсу. Доклад о развитии университета и подготовке к церемонии вручения дипломов. Оператор: Н.Баткеев.</t>
+          <t>Елбасы принял президента АОО «Назарбаев Университет» Шигео Катсу.
+В ходе встречи Первому Президенту Казахстана было доложено о текущем развитии «Назарбаев Университета» и ходе подготовки к пятой церемонии вручения дипломов выпускникам вуза.
+- Многие не верили, что у нас будет университет международного уровня. И вот Вы уже долгие годы являетесь ректором такого университета. У вуза есть интеллектуальный потенциал – ученые, которые поднимают уровень учебного заведения. «Назарбаев Университет» стал одним из брендов Казахстана, - сказал Елбасы.
+По итогам встречи Нурсултан Назарбаев дал ряд поручений.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1277,16 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с министром труда и социальной защиты населения РК Б.Сапарбаевым. Оператор: А.И.</t>
+          <t>Елбасы Нурсултан Назарбаев принял министра труда и социальной защиты населения Бердибека Сапарбаева.
+В ходе встречи Елбасы был проинформирован о деятельности Правительственной рабочей группы по разъяснению новых социальных мер «Әлеуметтік қамқорлық».
+Первый Президент Казахстана отметил, что Б.Сапарбаев обладает достаточным опытом и управленческими навыками для решения поставленных перед министерством задач.
+- У вас большой опыт. Работали на важных участках. Руководили в трех областях. Показывали хорошую работу. Подняли показатели Актюбинской области по многим отраслям. Вы были назначены в министерство, так как была необходимость подтянуть этот фронт работы. Нужен был опытный человек. Необходимо решить все поставленные вопросы до конца во благо нашего народа, - отметил Елбасы.
+Б.Сапарбаев рассказал Нурсултану Назарбаеву о проводимой министерством работе по реализации новых социальных мер, направленных на повышение уровня жизни казахстанцев. В частности, министр представил информацию о порядке начисления адресной социальной помощи и предпринимаемых шагах по созданию новых рабочих мест.
+Первый Президент Казахстана указал на необходимость обеспечения соответствующего контроля и систематизации процесса оказания помощи нуждающимся категориям населения.
+- Сейчас социальные расходы составляют почти половину доходов государства. Важно систематизировать всю работу. Прежде всего, люди должны быть обеспечены рабочими местами. Конечно, есть те, кто в виду объективных причин, не может работать. Им мы должны помогать, - сказал Елбасы.
+Кроме того, Б.Сапарбаев доложил о работе по решению жилищных вопросов в регионах и поддержке лиц с особыми потребностями. Министр рассказал о принимаемых совместно с предпринимателями мерах в рамках реализации принципа социальной ответственности бизнеса. Бердибек Сапарбаев также остановился на вопросах миграции и поддержки многодетных семей и оралманов.
+В завершение Нурсултан Назарбаев подчеркнул важность проводимой министерством работы и отметил необходимость эффективного решения поставленных задач.
+Оператор: А.И.</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1301,16 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с министром труда и социальной защиты населения РК Б.Сапарбаевым. Оператор: Х.О.</t>
+          <t>Елбасы Нурсултан Назарбаев принял министра труда и социальной защиты населения Бердибека Сапарбаева.
+В ходе встречи Елбасы был проинформирован о деятельности Правительственной рабочей группы по разъяснению новых социальных мер «Әлеуметтік қамқорлық».
+Первый Президент Казахстана отметил, что Б.Сапарбаев обладает достаточным опытом и управленческими навыками для решения поставленных перед министерством задач.
+- У вас большой опыт. Работали на важных участках. Руководили в трех областях. Показывали хорошую работу. Подняли показатели Актюбинской области по многим отраслям. Вы были назначены в министерство, так как была необходимость подтянуть этот фронт работы. Нужен был опытный человек. Необходимо решить все поставленные вопросы до конца во благо нашего народа, - отметил Елбасы.
+Б.Сапарбаев рассказал Нурсултану Назарбаеву о проводимой министерством работе по реализации новых социальных мер, направленных на повышение уровня жизни казахстанцев. В частности, министр представил информацию о порядке начисления адресной социальной помощи и предпринимаемых шагах по созданию новых рабочих мест.
+Первый Президент Казахстана указал на необходимость обеспечения соответствующего контроля и систематизации процесса оказания помощи нуждающимся категориям населения.
+- Сейчас социальные расходы составляют почти половину доходов государства. Важно систематизировать всю работу. Прежде всего, люди должны быть обеспечены рабочими местами. Конечно, есть те, кто в виду объективных причин, не может работать. Им мы должны помогать, - сказал Елбасы.
+Кроме того, Б.Сапарбаев доложил о работе по решению жилищных вопросов в регионах и поддержке лиц с особыми потребностями. Министр рассказал о принимаемых совместно с предпринимателями мерах в рамках реализации принципа социальной ответственности бизнеса. Бердибек Сапарбаев также остановился на вопросах миграции и поддержки многодетных семей и оралманов.
+В завершение Нурсултан Назарбаев подчеркнул важность проводимой министерством работы и отметил необходимость эффективного решения поставленных задач.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1325,16 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с министром труда и социальной защиты населения РК Б.Сапарбаевым. Оператор: Н.Баткеев.</t>
+          <t>Елбасы Нурсултан Назарбаев принял министра труда и социальной защиты населения Бердибека Сапарбаева.
+В ходе встречи Елбасы был проинформирован о деятельности Правительственной рабочей группы по разъяснению новых социальных мер «Әлеуметтік қамқорлық».
+Первый Президент Казахстана отметил, что Б.Сапарбаев обладает достаточным опытом и управленческими навыками для решения поставленных перед министерством задач.
+- У вас большой опыт. Работали на важных участках. Руководили в трех областях. Показывали хорошую работу. Подняли показатели Актюбинской области по многим отраслям. Вы были назначены в министерство, так как была необходимость подтянуть этот фронт работы. Нужен был опытный человек. Необходимо решить все поставленные вопросы до конца во благо нашего народа, - отметил Елбасы.
+Б.Сапарбаев рассказал Нурсултану Назарбаеву о проводимой министерством работе по реализации новых социальных мер, направленных на повышение уровня жизни казахстанцев. В частности, министр представил информацию о порядке начисления адресной социальной помощи и предпринимаемых шагах по созданию новых рабочих мест.
+Первый Президент Казахстана указал на необходимость обеспечения соответствующего контроля и систематизации процесса оказания помощи нуждающимся категориям населения.
+- Сейчас социальные расходы составляют почти половину доходов государства. Важно систематизировать всю работу. Прежде всего, люди должны быть обеспечены рабочими местами. Конечно, есть те, кто в виду объективных причин, не может работать. Им мы должны помогать, - сказал Елбасы.
+Кроме того, Б.Сапарбаев доложил о работе по решению жилищных вопросов в регионах и поддержке лиц с особыми потребностями. Министр рассказал о принимаемых совместно с предпринимателями мерах в рамках реализации принципа социальной ответственности бизнеса. Бердибек Сапарбаев также остановился на вопросах миграции и поддержки многодетных семей и оралманов.
+В завершение Нурсултан Назарбаев подчеркнул важность проводимой министерством работы и отметил необходимость эффективного решения поставленных задач.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1349,11 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с молодым композитором Р.Абдысагиным, победителем проекта «100 новых лиц Казахстана». Презентация оперы «Путь, освещённый солнцем». Оператор: А.И.</t>
+          <t>Елбасы принял молодого композитора Рахат-Би Абдысагина.
+В ходе встречи талантливый композитор, один из победителей конкурса «100 новых лиц Казахстана» представил Нурсултану Назарбаеву свою новую оперу «Путь, освещенный солнцем».
+Музыкальное произведение будет посвящено истории становления и развития Независимого Казахстана.
+Нурсултан Назарбаев пожелал Р.Абдысагину творческих успехов и новых свершений.
+Оператор: А.И.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1368,11 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с молодым композитором Р.Абдысагиным, победителем проекта «100 новых лиц Казахстана». Презентация оперы «Путь, освещённый солнцем». Оператор: Х.О.</t>
+          <t>Елбасы принял молодого композитора Рахат-Би Абдысагина.
+В ходе встречи талантливый композитор, один из победителей конкурса «100 новых лиц Казахстана» представил Нурсултану Назарбаеву свою новую оперу «Путь, освещенный солнцем».
+Музыкальное произведение будет посвящено истории становления и развития Независимого Казахстана.
+Нурсултан Назарбаев пожелал Р.Абдысагину творческих успехов и новых свершений.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1387,11 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с молодым композитором Р.Абдысагиным, победителем проекта «100 новых лиц Казахстана». Презентация оперы «Путь, освещённый солнцем». Оператор: Н.Баткеев.</t>
+          <t>Елбасы принял молодого композитора Рахат-Би Абдысагина.
+В ходе встречи талантливый композитор, один из победителей конкурса «100 новых лиц Казахстана» представил Нурсултану Назарбаеву свою новую оперу «Путь, освещенный солнцем».
+Музыкальное произведение будет посвящено истории становления и развития Независимого Казахстана.
+Нурсултан Назарбаев пожелал Р.Абдысагину творческих успехов и новых свершений.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1406,16 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с министром иностранных дел Турецкой Республики М.Чавушоглу. Оператор: А.И.</t>
+          <t>Елбасы Нурсултан Назарбаев встретился с министром иностранных дел Турецкой Республики Мевлютом Чавушоглу.
+В ходе встречи Первый Президент Казахстана отметил важность сохранения и дальнейшего углубления сотрудничества между двумя братскими странами.
+- С первых дней независимости Турция всегда поддерживала нас. Наши государства и народы очень близки друг к другу. Мы ввели безвизовый режим между двумя странами. Отношения Казахстана и Турции крепнут год от года. Уверен, что этот курс будет продолжен, - сказал Елбасы.
+Нурсултан Назарбаев также подчеркнул необходимость развития межгосударственных связей в рамках Тюркского совета.
+- Совет сотрудничества тюркоязычных государств был создан в целях развития и укрепления связей между тюркскими народами. Данную работу следует продолжать. Я буду оказывать всестороннюю поддержку, - сказал Первый Президент Казахстана.
+В свою очередь, М.Чавушоглу поприветствовал Елбасы и от имени Президента Реджепа Эрдогана пригласил Нурсултана Назарбаева посетить Турцию в ближайшее время.
+- Мы приветствуем, что Вы в качестве Елбасы, председателя Совета Безопасности, руководителя партии «Nur Otan» продолжаете активно работать во благо народа Казахстана. Нам хорошо известно, какой колоссальный труд Вы вложили во имя процветания своей страны и развитие двусторонних отношений, - отметил министр иностранных дел Турецкой Республики.
+В ходе беседы стороны также обсудили актуальные вопросы международной и региональной повестки дня.
+В завершение встречи глава МИД Турецкой Республики сообщил, что в соответствии с принятым решением лидеров государств Тюркского совета за значительный вклад в развитие стран тюркского мира Нурсултану Назарбаеву был присвоен пожизненный статус Почетного председателя Совета сотрудничества тюркоязычных государств.
+Оператор: А.И.</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1430,16 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с министром иностранных дел Турецкой Республики М.Чавушоглу. Оператор: Х.О.</t>
+          <t>Елбасы Нурсултан Назарбаев встретился с министром иностранных дел Турецкой Республики Мевлютом Чавушоглу.
+В ходе встречи Первый Президент Казахстана отметил важность сохранения и дальнейшего углубления сотрудничества между двумя братскими странами.
+- С первых дней независимости Турция всегда поддерживала нас. Наши государства и народы очень близки друг к другу. Мы ввели безвизовый режим между двумя странами. Отношения Казахстана и Турции крепнут год от года. Уверен, что этот курс будет продолжен, - сказал Елбасы.
+Нурсултан Назарбаев также подчеркнул необходимость развития межгосударственных связей в рамках Тюркского совета.
+- Совет сотрудничества тюркоязычных государств был создан в целях развития и укрепления связей между тюркскими народами. Данную работу следует продолжать. Я буду оказывать всестороннюю поддержку, - сказал Первый Президент Казахстана.
+В свою очередь, М.Чавушоглу поприветствовал Елбасы и от имени Президента Реджепа Эрдогана пригласил Нурсултана Назарбаева посетить Турцию в ближайшее время.
+- Мы приветствуем, что Вы в качестве Елбасы, председателя Совета Безопасности, руководителя партии «Nur Otan» продолжаете активно работать во благо народа Казахстана. Нам хорошо известно, какой колоссальный труд Вы вложили во имя процветания своей страны и развитие двусторонних отношений, - отметил министр иностранных дел Турецкой Республики.
+В ходе беседы стороны также обсудили актуальные вопросы международной и региональной повестки дня.
+В завершение встречи глава МИД Турецкой Республики сообщил, что в соответствии с принятым решением лидеров государств Тюркского совета за значительный вклад в развитие стран тюркского мира Нурсултану Назарбаеву был присвоен пожизненный статус Почетного председателя Совета сотрудничества тюркоязычных государств.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1454,16 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с министром иностранных дел Турецкой Республики М.Чавушоглу. Оператор: Н.Баткеев.</t>
+          <t>Елбасы Нурсултан Назарбаев встретился с министром иностранных дел Турецкой Республики Мевлютом Чавушоглу.
+В ходе встречи Первый Президент Казахстана отметил важность сохранения и дальнейшего углубления сотрудничества между двумя братскими странами.
+- С первых дней независимости Турция всегда поддерживала нас. Наши государства и народы очень близки друг к другу. Мы ввели безвизовый режим между двумя странами. Отношения Казахстана и Турции крепнут год от года. Уверен, что этот курс будет продолжен, - сказал Елбасы.
+Нурсултан Назарбаев также подчеркнул необходимость развития межгосударственных связей в рамках Тюркского совета.
+- Совет сотрудничества тюркоязычных государств был создан в целях развития и укрепления связей между тюркскими народами. Данную работу следует продолжать. Я буду оказывать всестороннюю поддержку, - сказал Первый Президент Казахстана.
+В свою очередь, М.Чавушоглу поприветствовал Елбасы и от имени Президента Реджепа Эрдогана пригласил Нурсултана Назарбаева посетить Турцию в ближайшее время.
+- Мы приветствуем, что Вы в качестве Елбасы, председателя Совета Безопасности, руководителя партии «Nur Otan» продолжаете активно работать во благо народа Казахстана. Нам хорошо известно, какой колоссальный труд Вы вложили во имя процветания своей страны и развитие двусторонних отношений, - отметил министр иностранных дел Турецкой Республики.
+В ходе беседы стороны также обсудили актуальные вопросы международной и региональной повестки дня.
+В завершение встречи глава МИД Турецкой Республики сообщил, что в соответствии с принятым решением лидеров государств Тюркского совета за значительный вклад в развитие стран тюркского мира Нурсултану Назарбаеву был присвоен пожизненный статус Почетного председателя Совета сотрудничества тюркоязычных государств.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1478,13 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Коллегии Евразийской экономической комиссии Т.Саркисяном. Крупный план.</t>
+          <t>Первый Президент Казахстана принял председателя Коллегии Евразийской экономической комиссии Тиграна Саркисяна.
+В ходе встречи стороны обсудили текущее состояние и перспективы развития Евразийского экономического союза.
+Нурсултан Назарбаев подчеркнул, что многие страны и организации заинтересованы в налаживании сотрудничества с ЕАЭС и указал на необходимость расширения географии экономических партнеров союза.
+- Завтра здесь состоится юбилейное заседание ВЕЭС. Вы председательствуете в исполнительном органе союза, успешно справляясь с поставленными задачами. Нужно продолжать двигаться вперед, - сказал Первый Президент Казахстана.
+В свою очередь Тигран Саркисян отметил достижения в развитии экономического союза.
+- Благодарю Вас за возможность обсудить вопросы интеграции и практическую реализацию идеи, предложенную Вами 25 лет назад. Вот уже 5 лет мы реализуем этот проект. Мудрость, проявленная Вами четверть века назад, была жизненно необходима нашим странам, - сказал председатель Коллегии Евразийской экономической комиссии.
+Крупный план.</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1499,13 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Республики Таджикистан Э.Рахмоном. Крупный план.</t>
+          <t>Нурсултан Назарбаев встретился с Президентом Республики Таджикистан Эмомали Рахмоном.
+В ходе переговоров Елбасы отметил, что с первых дней сотрудничества Казахстан и Таджикистан построили крепкие дружественные и доверительные отношения.
+- Наша дружба крепнет год от года. Вы возглавляете Таджикистан в условиях сложной ситуации в мире. Вы поступательно развиваетесь, в стране обеспечивается стабильность, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана также подчеркнул, что двусторонние отношения будут и впредь укрепляться во благо двух братских народов.
+В свою очередь Эмомали Рахмон отметил высокие темпы развития Казахстана, достигнутые под руководством Елбасы.
+- Я свидетель того, как менялся облик Казахстана. Я помню первые встречи в столице и вижу, как она преобразилась. Позитивные изменения охватили не только город, но и всю страну. Это результат Вашей плодотворной работы, мудрой и дальновидной политики, - сказал Президент Таджикистана.
+Крупный план.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1520,13 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Республики Таджикистан Э.Рахмоном. Стационар.</t>
+          <t>Нурсултан Назарбаев встретился с Президентом Республики Таджикистан Эмомали Рахмоном.
+В ходе переговоров Елбасы отметил, что с первых дней сотрудничества Казахстан и Таджикистан построили крепкие дружественные и доверительные отношения.
+- Наша дружба крепнет год от года. Вы возглавляете Таджикистан в условиях сложной ситуации в мире. Вы поступательно развиваетесь, в стране обеспечивается стабильность, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана также подчеркнул, что двусторонние отношения будут и впредь укрепляться во благо двух братских народов.
+В свою очередь Эмомали Рахмон отметил высокие темпы развития Казахстана, достигнутые под руководством Елбасы.
+- Я свидетель того, как менялся облик Казахстана. Я помню первые встречи в столице и вижу, как она преобразилась. Позитивные изменения охватили не только город, но и всю страну. Это результат Вашей плодотворной работы, мудрой и дальновидной политики, - сказал Президент Таджикистана.
+Стационар.</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1541,13 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Республики Таджикистан Э.Рахмоном. Оператор: Х.О.</t>
+          <t>Нурсултан Назарбаев встретился с Президентом Республики Таджикистан Эмомали Рахмоном.
+В ходе переговоров Елбасы отметил, что с первых дней сотрудничества Казахстан и Таджикистан построили крепкие дружественные и доверительные отношения.
+- Наша дружба крепнет год от года. Вы возглавляете Таджикистан в условиях сложной ситуации в мире. Вы поступательно развиваетесь, в стране обеспечивается стабильность, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана также подчеркнул, что двусторонние отношения будут и впредь укрепляться во благо двух братских народов.
+В свою очередь Эмомали Рахмон отметил высокие темпы развития Казахстана, достигнутые под руководством Елбасы.
+- Я свидетель того, как менялся облик Казахстана. Я помню первые встречи в столице и вижу, как она преобразилась. Позитивные изменения охватили не только город, но и всю страну. Это результат Вашей плодотворной работы, мудрой и дальновидной политики, - сказал Президент Таджикистана.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1562,15 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Республики Беларусь А.Лукашенко. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Стационар.</t>
+          <t>Первый Президент Казахстана встретился с Президентом Республики Беларусь Александром Лукашенко.
+В ходе встречи Елбасы вручил высокому гостю орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана особо отметил роль и вклад Александра Лукашенко в развитие интеграционных процессов и становление Евразийского экономического союза.
+- Этот год ознаменован пятилетием создания здесь Евразийского экономического союза и 25-летием идеи евразийской интеграции, предложенной мною. И без вашей поддержки не было бы этой организации, - сказал Нурсултан Назарбаев.
+Елбасы подчеркнул, что всегда будет готов оказать поддержку народу Беларуси во главе с ее лидером А. Лукашенко.
+- Я всегда буду готов помочь и поддержать Вас по любому направлению. Вам удается держать Беларусь на высоком уровне. Также, пользуясь случаем, приглашаю Вас посетить красивейшие места Казахстана, - сказал Первый Президент Казахстана.
+В свою очередь Александр Лукашенко поблагодарил Нурсултана Назарбаева за оказанный прием и врученную ему награду.
+- Спасибо за уважение к белорусскому народу. Я понимаю, что это не только моя заслуга. Это Ваша любовь и отношение к моему народу. Президент Казахстана – очень достойный человек. Вы приняли мудрое решение. Уверен, что казахстанцы ценят стабильность, как и другие народы. Самое главное – труд. Будешь трудиться, будет и результат, - сказал Президент Республики Беларусь.
+Стационар.</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1585,15 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Республики Беларусь А.Лукашенко. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана встретился с Президентом Республики Беларусь Александром Лукашенко.
+В ходе встречи Елбасы вручил высокому гостю орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана особо отметил роль и вклад Александра Лукашенко в развитие интеграционных процессов и становление Евразийского экономического союза.
+- Этот год ознаменован пятилетием создания здесь Евразийского экономического союза и 25-летием идеи евразийской интеграции, предложенной мною. И без вашей поддержки не было бы этой организации, - сказал Нурсултан Назарбаев.
+Елбасы подчеркнул, что всегда будет готов оказать поддержку народу Беларуси во главе с ее лидером А. Лукашенко.
+- Я всегда буду готов помочь и поддержать Вас по любому направлению. Вам удается держать Беларусь на высоком уровне. Также, пользуясь случаем, приглашаю Вас посетить красивейшие места Казахстана, - сказал Первый Президент Казахстана.
+В свою очередь Александр Лукашенко поблагодарил Нурсултана Назарбаева за оказанный прием и врученную ему награду.
+- Спасибо за уважение к белорусскому народу. Я понимаю, что это не только моя заслуга. Это Ваша любовь и отношение к моему народу. Президент Казахстана – очень достойный человек. Вы приняли мудрое решение. Уверен, что казахстанцы ценят стабильность, как и другие народы. Самое главное – труд. Будешь трудиться, будет и результат, - сказал Президент Республики Беларусь.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1608,15 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Республики Беларусь А.Лукашенко. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Крупный план.</t>
+          <t>Первый Президент Казахстана встретился с Президентом Республики Беларусь Александром Лукашенко.
+В ходе встречи Елбасы вручил высокому гостю орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана особо отметил роль и вклад Александра Лукашенко в развитие интеграционных процессов и становление Евразийского экономического союза.
+- Этот год ознаменован пятилетием создания здесь Евразийского экономического союза и 25-летием идеи евразийской интеграции, предложенной мною. И без вашей поддержки не было бы этой организации, - сказал Нурсултан Назарбаев.
+Елбасы подчеркнул, что всегда будет готов оказать поддержку народу Беларуси во главе с ее лидером А. Лукашенко.
+- Я всегда буду готов помочь и поддержать Вас по любому направлению. Вам удается держать Беларусь на высоком уровне. Также, пользуясь случаем, приглашаю Вас посетить красивейшие места Казахстана, - сказал Первый Президент Казахстана.
+В свою очередь Александр Лукашенко поблагодарил Нурсултана Назарбаева за оказанный прием и врученную ему награду.
+- Спасибо за уважение к белорусскому народу. Я понимаю, что это не только моя заслуга. Это Ваша любовь и отношение к моему народу. Президент Казахстана – очень достойный человек. Вы приняли мудрое решение. Уверен, что казахстанцы ценят стабильность, как и другие народы. Самое главное – труд. Будешь трудиться, будет и результат, - сказал Президент Республики Беларусь.
+Крупный план.</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1631,13 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Премьер-министром Республики Армения Н.Пашиняном. Стационар.</t>
+          <t>Елбасы встретился с Премьер-Министром Республики Армения Николом Пашиняном.
+Поприветствовав высокого гостя, Нурсултан Назарбаев отметил важность развития и укрепления двусторонних торгово-экономических отношений.
+- Между Казахстаном и Арменией всегда были добрые отношения. Армянская диаспора в Казахстане является мостом между нашими странами, - сказал Елбасы.
+Никол Пашинян подчеркнул особый вклад Первого Президента Казахстана в развитие межгосударственных связей и интеграционных процессов на континенте.
+Премьер-Министр Армении выразил уверенность в дальнейшем углублении двустороннего экономического сотрудничества.
+- Я думаю, что у нас есть возможность поработать в сфере экономики. Главное, у правительств двух стран есть политическая воля развивать отношения, потому что наши народы связаны исторически, - сказал Н.Пашинян.
+Стационар.</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1652,13 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Премьер-министром Республики Армения Н.Пашиняном. Оператор: Х.О.</t>
+          <t>Елбасы встретился с Премьер-Министром Республики Армения Николом Пашиняном.
+Поприветствовав высокого гостя, Нурсултан Назарбаев отметил важность развития и укрепления двусторонних торгово-экономических отношений.
+- Между Казахстаном и Арменией всегда были добрые отношения. Армянская диаспора в Казахстане является мостом между нашими странами, - сказал Елбасы.
+Никол Пашинян подчеркнул особый вклад Первого Президента Казахстана в развитие межгосударственных связей и интеграционных процессов на континенте.
+Премьер-Министр Армении выразил уверенность в дальнейшем углублении двустороннего экономического сотрудничества.
+- Я думаю, что у нас есть возможность поработать в сфере экономики. Главное, у правительств двух стран есть политическая воля развивать отношения, потому что наши народы связаны исторически, - сказал Н.Пашинян.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1673,13 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Премьер-министром Республики Армения Н.Пашиняном. Крупный план.</t>
+          <t>Елбасы встретился с Премьер-Министром Республики Армения Николом Пашиняном.
+Поприветствовав высокого гостя, Нурсултан Назарбаев отметил важность развития и укрепления двусторонних торгово-экономических отношений.
+- Между Казахстаном и Арменией всегда были добрые отношения. Армянская диаспора в Казахстане является мостом между нашими странами, - сказал Елбасы.
+Никол Пашинян подчеркнул особый вклад Первого Президента Казахстана в развитие межгосударственных связей и интеграционных процессов на континенте.
+Премьер-Министр Армении выразил уверенность в дальнейшем углублении двустороннего экономического сотрудничества.
+- Я думаю, что у нас есть возможность поработать в сфере экономики. Главное, у правительств двух стран есть политическая воля развивать отношения, потому что наши народы связаны исторически, - сказал Н.Пашинян.
+Крупный план.</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1694,13 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Российской Федерации В.Путиным. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Оператор: Маликов.</t>
+          <t>Нурсултан Назарбаев встретился с Президентом Российской Федерации Владимиром Путиным.
+В ходе встречи Елбасы лично вручил Владимиру Путину орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана отметил текущие результаты и перспективы дальнейшего развития Евразийского экономического союза.
+- Пять лет назад Вы, я и Александр Лукашенко создали этот союз. 25 лет назад в стенах МГУ мною была предложена эта идея, которую мы реализовали. Несмотря на непростые времена, взаимная торговля между нами растет. Увеличивается количество совместных предприятий. Считаю, что ЕАЭС должен идти по пути интеграции с ЕС, ШОС, АСЕАН и другими организациями. И нам необходимо работать над этим, - сказал Нурсултан Назарбаев.
+Владимир Путин поблагодарил Елбасы за врученную ему награду и выразил уверенность в дальнейшем укреплении всестороннего диалога.
+- Хотел бы поблагодарить Вас за награду и за то, что было сделано в деле интеграции, двусторонних отношениях и развитии стратегического взаимодействия России и Казахстана. В этом имеется огромная Ваша заслуга, - сказал Президент России.
+Оператор: Маликов.</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1715,13 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Российской Федерации В.Путиным. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Оператор: Тлеспаев.</t>
+          <t>Нурсултан Назарбаев встретился с Президентом Российской Федерации Владимиром Путиным.
+В ходе встречи Елбасы лично вручил Владимиру Путину орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана отметил текущие результаты и перспективы дальнейшего развития Евразийского экономического союза.
+- Пять лет назад Вы, я и Александр Лукашенко создали этот союз. 25 лет назад в стенах МГУ мною была предложена эта идея, которую мы реализовали. Несмотря на непростые времена, взаимная торговля между нами растет. Увеличивается количество совместных предприятий. Считаю, что ЕАЭС должен идти по пути интеграции с ЕС, ШОС, АСЕАН и другими организациями. И нам необходимо работать над этим, - сказал Нурсултан Назарбаев.
+Владимир Путин поблагодарил Елбасы за врученную ему награду и выразил уверенность в дальнейшем укреплении всестороннего диалога.
+- Хотел бы поблагодарить Вас за награду и за то, что было сделано в деле интеграции, двусторонних отношениях и развитии стратегического взаимодействия России и Казахстана. В этом имеется огромная Ваша заслуга, - сказал Президент России.
+Оператор: Тлеспаев.</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1736,13 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Российской Федерации В.Путиным. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Оператор: Х.О.</t>
+          <t>Нурсултан Назарбаев встретился с Президентом Российской Федерации Владимиром Путиным.
+В ходе встречи Елбасы лично вручил Владимиру Путину орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана отметил текущие результаты и перспективы дальнейшего развития Евразийского экономического союза.
+- Пять лет назад Вы, я и Александр Лукашенко создали этот союз. 25 лет назад в стенах МГУ мною была предложена эта идея, которую мы реализовали. Несмотря на непростые времена, взаимная торговля между нами растет. Увеличивается количество совместных предприятий. Считаю, что ЕАЭС должен идти по пути интеграции с ЕС, ШОС, АСЕАН и другими организациями. И нам необходимо работать над этим, - сказал Нурсултан Назарбаев.
+Владимир Путин поблагодарил Елбасы за врученную ему награду и выразил уверенность в дальнейшем укреплении всестороннего диалога.
+- Хотел бы поблагодарить Вас за награду и за то, что было сделано в деле интеграции, двусторонних отношениях и развитии стратегического взаимодействия России и Казахстана. В этом имеется огромная Ваша заслуга, - сказал Президент России.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1757,13 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Коллегии Евразийской экономической комиссии Т.Саркисяном. Стационар.</t>
+          <t>Первый Президент Казахстана принял председателя Коллегии Евразийской экономической комиссии Тиграна Саркисяна.
+В ходе встречи стороны обсудили текущее состояние и перспективы развития Евразийского экономического союза.
+Нурсултан Назарбаев подчеркнул, что многие страны и организации заинтересованы в налаживании сотрудничества с ЕАЭС и указал на необходимость расширения географии экономических партнеров союза.
+- Завтра здесь состоится юбилейное заседание ВЕЭС. Вы председательствуете в исполнительном органе союза, успешно справляясь с поставленными задачами. Нужно продолжать двигаться вперед, - сказал Первый Президент Казахстана.
+В свою очередь Тигран Саркисян отметил достижения в развитии экономического союза.
+- Благодарю Вас за возможность обсудить вопросы интеграции и практическую реализацию идеи, предложенную Вами 25 лет назад. Вот уже 5 лет мы реализуем этот проект. Мудрость, проявленная Вами четверть века назад, была жизненно необходима нашим странам, - сказал председатель Коллегии Евразийской экономической комиссии.
+Стационар.</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1778,13 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Коллегии Евразийской экономической комиссии Т.Саркисяном. Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана принял председателя Коллегии Евразийской экономической комиссии Тиграна Саркисяна.
+В ходе встречи стороны обсудили текущее состояние и перспективы развития Евразийского экономического союза.
+Нурсултан Назарбаев подчеркнул, что многие страны и организации заинтересованы в налаживании сотрудничества с ЕАЭС и указал на необходимость расширения географии экономических партнеров союза.
+- Завтра здесь состоится юбилейное заседание ВЕЭС. Вы председательствуете в исполнительном органе союза, успешно справляясь с поставленными задачами. Нужно продолжать двигаться вперед, - сказал Первый Президент Казахстана.
+В свою очередь Тигран Саркисян отметил достижения в развитии экономического союза.
+- Благодарю Вас за возможность обсудить вопросы интеграции и практическую реализацию идеи, предложенную Вами 25 лет назад. Вот уже 5 лет мы реализуем этот проект. Мудрость, проявленная Вами четверть века назад, была жизненно необходима нашим странам, - сказал председатель Коллегии Евразийской экономической комиссии.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1799,13 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Кыргызской Республики С.Жээнбековым. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Стационар.</t>
+          <t>Елбасы встретился с Президентом Кыргызской Республики Сооронбаем Жээнбековым.
+В ходе встречи Нурсултан Назарбаев вручил Сооронбаю Жээнбекову орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана подчеркнул высокий уровень отношений между двумя братскими народами.
+- Мы – близкие друг к другу, братские народы. Я очень хорошо знаю и хорошо отношусь к Вашему народу. Уверен, что Казахстан и впредь будет поддерживать Вас, - сказал Елбасы.
+В свою очередь Сооронбай Жээнбеков поблагодарил Нурсултана Назарбаева за врученную высокую награду и отметил особую роль Елбасы в укреплении дружбы народов Центральной Азии.
+- Вы являетесь лидером Тюркского мира. Вы внесли свой значительный вклад в укрепление дружбы стран Центральной Азии. Для меня честь получить этот орден из рук Елбасы казахского народа. И я благодарен Вам за это, - отметил Президент Кыргызской Республики.
+Стационар.</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1820,13 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Кыргызской Республики С.Жээнбековым. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Оператор: Х.О.</t>
+          <t>Елбасы встретился с Президентом Кыргызской Республики Сооронбаем Жээнбековым.
+В ходе встречи Нурсултан Назарбаев вручил Сооронбаю Жээнбекову орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана подчеркнул высокий уровень отношений между двумя братскими народами.
+- Мы – близкие друг к другу, братские народы. Я очень хорошо знаю и хорошо отношусь к Вашему народу. Уверен, что Казахстан и впредь будет поддерживать Вас, - сказал Елбасы.
+В свою очередь Сооронбай Жээнбеков поблагодарил Нурсултана Назарбаева за врученную высокую награду и отметил особую роль Елбасы в укреплении дружбы народов Центральной Азии.
+- Вы являетесь лидером Тюркского мира. Вы внесли свой значительный вклад в укрепление дружбы стран Центральной Азии. Для меня честь получить этот орден из рук Елбасы казахского народа. И я благодарен Вам за это, - отметил Президент Кыргызской Республики.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1841,13 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Кыргызской Республики С.Жээнбековым. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Крупный план.</t>
+          <t>Елбасы встретился с Президентом Кыргызской Республики Сооронбаем Жээнбековым.
+В ходе встречи Нурсултан Назарбаев вручил Сооронбаю Жээнбекову орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана подчеркнул высокий уровень отношений между двумя братскими народами.
+- Мы – близкие друг к другу, братские народы. Я очень хорошо знаю и хорошо отношусь к Вашему народу. Уверен, что Казахстан и впредь будет поддерживать Вас, - сказал Елбасы.
+В свою очередь Сооронбай Жээнбеков поблагодарил Нурсултана Назарбаева за врученную высокую награду и отметил особую роль Елбасы в укреплении дружбы народов Центральной Азии.
+- Вы являетесь лидером Тюркского мира. Вы внесли свой значительный вклад в укрепление дружбы стран Центральной Азии. Для меня честь получить этот орден из рук Елбасы казахского народа. И я благодарен Вам за это, - отметил Президент Кыргызской Республики.
+Крупный план.</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1862,21 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Вручение дипломов выпускникам Назарбаев Университета и открытие нового Атлетического центра НУ с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета.
+Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
+- Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана отметил результаты и достижения учащихся Университета в научно-исследовательской деятельности.
+- В прошлом году в Бостоне студенческая команда Школы наук и технологий получила золотую медаль на Международном конкурсе генно-инженерных машин. В качестве проекта по коммерциализации можно отметить проект EGIStic, - сказал Елбасы.
+Нурсултан Назарбаев указал, что сегодня высококвалифицированные кадры Университета вносят значительный вклад в технологическое развитие Казахстана.
+- 2019 год объявлен Годом молодежи. Образование молодежи является ключевым фактором конкурентоспособности нашей страны в современном мире. Именно от вас, ваших знаний, энергии и патриотизма зависит будущее Казахстана. Мы принимаем все меры для того, чтобы вы смогли в полной мере реализовать свой потенциал и возможности, - обратился к выпускникам Первый Президент Казахстана.
+Елбасы подчеркнул, что брэнд «NU – Назарбаев Университет» стал широко узнаваем не только в мировом академическом сообществе, но и в сферах госуправления, бизнеса, медицины, инноваций, IT-технологий.
+- Проект стал прорывным и лидером в своей области не только в Казахстане, но и на всем постсоветском пространстве. За небольшой срок университет вырос в элитное учебное заведение по подготовке профессиональных кадров, развитию отечественных научных исследований и разработок. Главным активом университета, конечно же, является его интеллектуальный потенциал – преподаватели, студенты, управленческий персонал, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана призвал выпускников принимать активное участие в жизни страны и общества.
+- Вы должны быть не только высококлассными специалистами, но и активно участвовать в общественной жизни, проявляя свою гражданскую ответственность. Какой бы путь вы ни избрали – продолжить дальнейшее обучение, трудиться на благо страны, представлять Казахстан за рубежом или начать свое дело, желаю вам светлой дороги и реализации намеченных планов, - заключил Елбасы.
+Елбасы принял участие в церемонии открытия нового Атлетического центра Назарбаев Университета.
+Первый Президент Казахстана посетил новое многофункциональное спортивное сооружение Назарбаев Университета.
+В Атлетическом центре учебного заведения предусмотрена все необходимая спортивная инфраструктура, в том числе олимпийский бассейн, паркетная арена на 660 зрителей, тренажерный зал и зал единоборств. Объект оснащен передовыми технологиями спортивной индустрии.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1891,10 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Открытие нового Атлетического центра Назарбаев Университета с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Осмотр спортивного комплекса. Оператор: Ахметов.</t>
+          <t>Елбасы принял участие в церемонии открытия нового Атлетического центра Назарбаев Университета.
+Первый Президент Казахстана посетил новое многофункциональное спортивное сооружение Назарбаев Университета.
+В Атлетическом центре учебного заведения предусмотрена все необходимая спортивная инфраструктура, в том числе олимпийский бассейн, паркетная арена на 660 зрителей, тренажерный зал и зал единоборств. Объект оснащен передовыми технологиями спортивной индустрии.
+Оператор: Ахметов.</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1909,10 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Открытие нового Атлетического центра Назарбаев Университета с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Осмотр спортивного комплекса. Оператор: Джаватаров.</t>
+          <t>Елбасы принял участие в церемонии открытия нового Атлетического центра Назарбаев Университета.
+Первый Президент Казахстана посетил новое многофункциональное спортивное сооружение Назарбаев Университета.
+В Атлетическом центре учебного заведения предусмотрена все необходимая спортивная инфраструктура, в том числе олимпийский бассейн, паркетная арена на 660 зрителей, тренажерный зал и зал единоборств. Объект оснащен передовыми технологиями спортивной индустрии.
+Оператор: Джаватаров.</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1927,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Абилов.</t>
+          <t>Первый Президент Казахстана встретился с Председателем Европейского совета Дональдом Туском.
+Поприветствовав гостя, Нурсултан Назарбаев отметил высокий уровень развития взаимоотношений между Казахстаном и Европейским союзом.
+- Мы встречались с вами несколько раз. В период вашего председательства было заключено Соглашение о расширенном партнерстве и сотрудничестве между Европейским Союзом и Республикой Казахстан. В этом году ожидается завершение его ратификации. В целом, у нас хорошие перспективы, - сказал Елбасы.
+В свою очередь Дональд Туск подчеркнул особую роль Нурсултана Назарбаева в становлении и развитии Казахстана, укреплении международного авторитета страны.
+- Ваша роль в регионе особая и важная. Я очень рад встретиться с Вами. Мы высоко ценим Ваш разумный и ответственный подход в транзите власти. Думаю, что вся Европа была впечатлена этим шагом, - отметил Председатель Европейского совета.
+Оператор: Абилов.</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1947,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Н.Кульманов.</t>
+          <t>Первый Президент Казахстана встретился с Председателем Европейского совета Дональдом Туском.
+Поприветствовав гостя, Нурсултан Назарбаев отметил высокий уровень развития взаимоотношений между Казахстаном и Европейским союзом.
+- Мы встречались с вами несколько раз. В период вашего председательства было заключено Соглашение о расширенном партнерстве и сотрудничестве между Европейским Союзом и Республикой Казахстан. В этом году ожидается завершение его ратификации. В целом, у нас хорошие перспективы, - сказал Елбасы.
+В свою очередь Дональд Туск подчеркнул особую роль Нурсултана Назарбаева в становлении и развитии Казахстана, укреплении международного авторитета страны.
+- Ваша роль в регионе особая и важная. Я очень рад встретиться с Вами. Мы высоко ценим Ваш разумный и ответственный подход в транзите власти. Думаю, что вся Европа была впечатлена этим шагом, - отметил Председатель Европейского совета.
+Оператор: Н.Кульманов.</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1967,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Проходка. Оператор: Абилов.</t>
+          <t>Первый Президент Казахстана встретился с Председателем Европейского совета Дональдом Туском.
+Поприветствовав гостя, Нурсултан Назарбаев отметил высокий уровень развития взаимоотношений между Казахстаном и Европейским союзом.
+- Мы встречались с вами несколько раз. В период вашего председательства было заключено Соглашение о расширенном партнерстве и сотрудничестве между Европейским Союзом и Республикой Казахстан. В этом году ожидается завершение его ратификации. В целом, у нас хорошие перспективы, - сказал Елбасы.
+В свою очередь Дональд Туск подчеркнул особую роль Нурсултана Назарбаева в становлении и развитии Казахстана, укреплении международного авторитета страны.
+- Ваша роль в регионе особая и важная. Я очень рад встретиться с Вами. Мы высоко ценим Ваш разумный и ответственный подход в транзите власти. Думаю, что вся Европа была впечатлена этим шагом, - отметил Председатель Европейского совета.
+Проходка. Оператор: Абилов.</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1987,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана встретился с Председателем Европейского совета Дональдом Туском.
+Поприветствовав гостя, Нурсултан Назарбаев отметил высокий уровень развития взаимоотношений между Казахстаном и Европейским союзом.
+- Мы встречались с вами несколько раз. В период вашего председательства было заключено Соглашение о расширенном партнерстве и сотрудничестве между Европейским Союзом и Республикой Казахстан. В этом году ожидается завершение его ратификации. В целом, у нас хорошие перспективы, - сказал Елбасы.
+В свою очередь Дональд Туск подчеркнул особую роль Нурсултана Назарбаева в становлении и развитии Казахстана, укреплении международного авторитета страны.
+- Ваша роль в регионе особая и важная. Я очень рад встретиться с Вами. Мы высоко ценим Ваш разумный и ответственный подход в транзите власти. Думаю, что вся Европа была впечатлена этим шагом, - отметил Председатель Европейского совета.
+Оператор: Х.О.</t>
         </is>
       </c>
     </row>
@@ -1600,7 +2007,18 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. Крупный план.</t>
+          <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета.
+Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
+- Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана отметил результаты и достижения учащихся Университета в научно-исследовательской деятельности.
+- В прошлом году в Бостоне студенческая команда Школы наук и технологий получила золотую медаль на Международном конкурсе генно-инженерных машин. В качестве проекта по коммерциализации можно отметить проект EGIStic, - сказал Елбасы.
+Нурсултан Назарбаев указал, что сегодня высококвалифицированные кадры Университета вносят значительный вклад в технологическое развитие Казахстана.
+- 2019 год объявлен Годом молодежи. Образование молодежи является ключевым фактором конкурентоспособности нашей страны в современном мире. Именно от вас, ваших знаний, энергии и патриотизма зависит будущее Казахстана. Мы принимаем все меры для того, чтобы вы смогли в полной мере реализовать свой потенциал и возможности, - обратился к выпускникам Первый Президент Казахстана.
+Елбасы подчеркнул, что брэнд «NU – Назарбаев Университет» стал широко узнаваем не только в мировом академическом сообществе, но и в сферах госуправления, бизнеса, медицины, инноваций, IT-технологий.
+- Проект стал прорывным и лидером в своей области не только в Казахстане, но и на всем постсоветском пространстве. За небольшой срок университет вырос в элитное учебное заведение по подготовке профессиональных кадров, развитию отечественных научных исследований и разработок. Главным активом университета, конечно же, является его интеллектуальный потенциал – преподаватели, студенты, управленческий персонал, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана призвал выпускников принимать активное участие в жизни страны и общества.
+- Вы должны быть не только высококлассными специалистами, но и активно участвовать в общественной жизни, проявляя свою гражданскую ответственность. Какой бы путь вы ни избрали – продолжить дальнейшее обучение, трудиться на благо страны, представлять Казахстан за рубежом или начать свое дело, желаю вам светлой дороги и реализации намеченных планов, - заключил Елбасы.
+Крупный план.</t>
         </is>
       </c>
     </row>
@@ -1615,7 +2033,18 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. PGM (программный микс).</t>
+          <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета.
+Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
+- Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана отметил результаты и достижения учащихся Университета в научно-исследовательской деятельности.
+- В прошлом году в Бостоне студенческая команда Школы наук и технологий получила золотую медаль на Международном конкурсе генно-инженерных машин. В качестве проекта по коммерциализации можно отметить проект EGIStic, - сказал Елбасы.
+Нурсултан Назарбаев указал, что сегодня высококвалифицированные кадры Университета вносят значительный вклад в технологическое развитие Казахстана.
+- 2019 год объявлен Годом молодежи. Образование молодежи является ключевым фактором конкурентоспособности нашей страны в современном мире. Именно от вас, ваших знаний, энергии и патриотизма зависит будущее Казахстана. Мы принимаем все меры для того, чтобы вы смогли в полной мере реализовать свой потенциал и возможности, - обратился к выпускникам Первый Президент Казахстана.
+Елбасы подчеркнул, что брэнд «NU – Назарбаев Университет» стал широко узнаваем не только в мировом академическом сообществе, но и в сферах госуправления, бизнеса, медицины, инноваций, IT-технологий.
+- Проект стал прорывным и лидером в своей области не только в Казахстане, но и на всем постсоветском пространстве. За небольшой срок университет вырос в элитное учебное заведение по подготовке профессиональных кадров, развитию отечественных научных исследований и разработок. Главным активом университета, конечно же, является его интеллектуальный потенциал – преподаватели, студенты, управленческий персонал, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана призвал выпускников принимать активное участие в жизни страны и общества.
+- Вы должны быть не только высококлассными специалистами, но и активно участвовать в общественной жизни, проявляя свою гражданскую ответственность. Какой бы путь вы ни избрали – продолжить дальнейшее обучение, трудиться на благо страны, представлять Казахстан за рубежом или начать свое дело, желаю вам светлой дороги и реализации намеченных планов, - заключил Елбасы.
+PGM (программный микс).</t>
         </is>
       </c>
     </row>
@@ -1630,7 +2059,18 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. Крупный план; без Елбасы.</t>
+          <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета.
+Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
+- Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана отметил результаты и достижения учащихся Университета в научно-исследовательской деятельности.
+- В прошлом году в Бостоне студенческая команда Школы наук и технологий получила золотую медаль на Международном конкурсе генно-инженерных машин. В качестве проекта по коммерциализации можно отметить проект EGIStic, - сказал Елбасы.
+Нурсултан Назарбаев указал, что сегодня высококвалифицированные кадры Университета вносят значительный вклад в технологическое развитие Казахстана.
+- 2019 год объявлен Годом молодежи. Образование молодежи является ключевым фактором конкурентоспособности нашей страны в современном мире. Именно от вас, ваших знаний, энергии и патриотизма зависит будущее Казахстана. Мы принимаем все меры для того, чтобы вы смогли в полной мере реализовать свой потенциал и возможности, - обратился к выпускникам Первый Президент Казахстана.
+Елбасы подчеркнул, что брэнд «NU – Назарбаев Университет» стал широко узнаваем не только в мировом академическом сообществе, но и в сферах госуправления, бизнеса, медицины, инноваций, IT-технологий.
+- Проект стал прорывным и лидером в своей области не только в Казахстане, но и на всем постсоветском пространстве. За небольшой срок университет вырос в элитное учебное заведение по подготовке профессиональных кадров, развитию отечественных научных исследований и разработок. Главным активом университета, конечно же, является его интеллектуальный потенциал – преподаватели, студенты, управленческий персонал, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана призвал выпускников принимать активное участие в жизни страны и общества.
+- Вы должны быть не только высококлассными специалистами, но и активно участвовать в общественной жизни, проявляя свою гражданскую ответственность. Какой бы путь вы ни избрали – продолжить дальнейшее обучение, трудиться на благо страны, представлять Казахстан за рубежом или начать свое дело, желаю вам светлой дороги и реализации намеченных планов, - заключил Елбасы.
+Крупный план; без Елбасы.</t>
         </is>
       </c>
     </row>
@@ -1645,7 +2085,18 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. PGM (программный микс); без Елбасы.</t>
+          <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета.
+Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
+- Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана отметил результаты и достижения учащихся Университета в научно-исследовательской деятельности.
+- В прошлом году в Бостоне студенческая команда Школы наук и технологий получила золотую медаль на Международном конкурсе генно-инженерных машин. В качестве проекта по коммерциализации можно отметить проект EGIStic, - сказал Елбасы.
+Нурсултан Назарбаев указал, что сегодня высококвалифицированные кадры Университета вносят значительный вклад в технологическое развитие Казахстана.
+- 2019 год объявлен Годом молодежи. Образование молодежи является ключевым фактором конкурентоспособности нашей страны в современном мире. Именно от вас, ваших знаний, энергии и патриотизма зависит будущее Казахстана. Мы принимаем все меры для того, чтобы вы смогли в полной мере реализовать свой потенциал и возможности, - обратился к выпускникам Первый Президент Казахстана.
+Елбасы подчеркнул, что брэнд «NU – Назарбаев Университет» стал широко узнаваем не только в мировом академическом сообществе, но и в сферах госуправления, бизнеса, медицины, инноваций, IT-технологий.
+- Проект стал прорывным и лидером в своей области не только в Казахстане, но и на всем постсоветском пространстве. За небольшой срок университет вырос в элитное учебное заведение по подготовке профессиональных кадров, развитию отечественных научных исследований и разработок. Главным активом университета, конечно же, является его интеллектуальный потенциал – преподаватели, студенты, управленческий персонал, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана призвал выпускников принимать активное участие в жизни страны и общества.
+- Вы должны быть не только высококлассными специалистами, но и активно участвовать в общественной жизни, проявляя свою гражданскую ответственность. Какой бы путь вы ни избрали – продолжить дальнейшее обучение, трудиться на благо страны, представлять Казахстан за рубежом или начать свое дело, желаю вам светлой дороги и реализации намеченных планов, - заключил Елбасы.
+PGM (программный микс); без Елбасы.</t>
         </is>
       </c>
     </row>
@@ -1660,7 +2111,16 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Международная научно-практическая конференция «30 лет лидерства» с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Выступление Елбасы. г. Алматы (по имени файла). Крупный план.</t>
+          <t>Первый Президент Казахстана принял участие в Международной научно-практической конференции «30 лет лидерства».
+Выступая перед участниками конференции, Елбасы отметил, что вся его деятельность на посту первого руководителя страны была посвящена развитию Казахстана.
+Нурсултан Назарбаев рассказал о трудностях на пути строительства и становления Независимости. В частности, Первый Президент Казахстана напомнил о ситуации в стране в начале 1990-х годов, связанной с развалом национальной экономики и рисками возникновения межэтнических конфликтов.
+- Казахстан стоял на пороге демографической катастрофы. Согласно переписи населения 1989 года, коренное население – казахи – составляли 39% или немногим более 6,5 миллионов человек. Тяжелейшая экономическая ситуация того периода вызвала масштабную эмиграцию населения из Казахстана. Средняя продолжительность жизни в те годы уменьшилась на пять лет, резко упала рождаемость, - сказал Елбасы.
+Нурсултан Назарбаев также подчеркнул, что в начале пути Казахстан был в числе самых технологически отсталых республик, в которой наблюдалась несбалансированность транспортных маршрутов и были серьезные проблемы с экологией.
+Первый Президент Казахстана остановился на результатах осуществления принятых в стране программ и стратегий развития, направленных на решение острых социально-экономических проблем.
+В своем выступлении Елбасы указал на несколько стратегических вызовов, влияющих на мировое развитие. Среди них, динамичная и непрерывная технологическая волна, смена экономической парадигмы, вызванная очередной индустриальной революцией, изменения в мировом геополитическом раскладе, столкновение разных глобальных реалий.
+- Народ и Президент должны быть всегда вместе. Только так мы достигали успеха. Я обращаюсь к нашему старшему поколению. Ваша мудрость должна помочь молодым людям идти по верному пути, любить Родину, крепить государство, защищать Независимость и работать ради будущего. Я обращаюсь к среднему поколению. Ваш приобретенный опыт – это неоценимый капитал, который поможет всем нам пройти сквозь невзгоды. И наконец, я обращаюсь к нашей молодежи. Чтобы лучше жить есть лишь один путь – трудиться. Дальнейший путь страны определять вам, - сказал Елбасы.
+С полным текстом выступления Первого Президента Казахстан можно ознакомиться здесь.
+Крупный план.</t>
         </is>
       </c>
     </row>
@@ -1675,7 +2135,16 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Международная научно-практическая конференция «30 лет лидерства» с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Выступление Елбасы. г. Алматы (по имени файла). PGM (программный микс).</t>
+          <t>Первый Президент Казахстана принял участие в Международной научно-практической конференции «30 лет лидерства».
+Выступая перед участниками конференции, Елбасы отметил, что вся его деятельность на посту первого руководителя страны была посвящена развитию Казахстана.
+Нурсултан Назарбаев рассказал о трудностях на пути строительства и становления Независимости. В частности, Первый Президент Казахстана напомнил о ситуации в стране в начале 1990-х годов, связанной с развалом национальной экономики и рисками возникновения межэтнических конфликтов.
+- Казахстан стоял на пороге демографической катастрофы. Согласно переписи населения 1989 года, коренное население – казахи – составляли 39% или немногим более 6,5 миллионов человек. Тяжелейшая экономическая ситуация того периода вызвала масштабную эмиграцию населения из Казахстана. Средняя продолжительность жизни в те годы уменьшилась на пять лет, резко упала рождаемость, - сказал Елбасы.
+Нурсултан Назарбаев также подчеркнул, что в начале пути Казахстан был в числе самых технологически отсталых республик, в которой наблюдалась несбалансированность транспортных маршрутов и были серьезные проблемы с экологией.
+Первый Президент Казахстана остановился на результатах осуществления принятых в стране программ и стратегий развития, направленных на решение острых социально-экономических проблем.
+В своем выступлении Елбасы указал на несколько стратегических вызовов, влияющих на мировое развитие. Среди них, динамичная и непрерывная технологическая волна, смена экономической парадигмы, вызванная очередной индустриальной революцией, изменения в мировом геополитическом раскладе, столкновение разных глобальных реалий.
+- Народ и Президент должны быть всегда вместе. Только так мы достигали успеха. Я обращаюсь к нашему старшему поколению. Ваша мудрость должна помочь молодым людям идти по верному пути, любить Родину, крепить государство, защищать Независимость и работать ради будущего. Я обращаюсь к среднему поколению. Ваш приобретенный опыт – это неоценимый капитал, который поможет всем нам пройти сквозь невзгоды. И наконец, я обращаюсь к нашей молодежи. Чтобы лучше жить есть лишь один путь – трудиться. Дальнейший путь страны определять вам, - сказал Елбасы.
+С полным текстом выступления Первого Президента Казахстан можно ознакомиться здесь.
+PGM (программный микс).</t>
         </is>
       </c>
     </row>
@@ -1768,7 +2237,14 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Первый Президент РК – Елбасы Н.А.Назарбаев на народных гуляниях по случаю Дня единства народа Казахстана. Выступление Елбасы перед жителями и гостями столицы. Оператор: Джаватаров.</t>
+          <t>Елбасы Нурсултан Назарбаев посетил народные гуляния по случаю празднования Дня единства народа Казахстана.
+Выступая перед жителями и гостями столицы, Первый Президент Нурсултан Назарбаев поздравил всех казахстанцев с праздником единства народа Казахстана.
+- Благодаря единству наши предки преодолели все трудности, сохранив для нас Великую степь. Мы вместе создали независимый Казахстан, тем самым исполнив мечту наших прадедов, - сказал Нурсултан Назарбаев.
+Елбасы отметил, что все успехи современного Казахстана достигнуты благодаря сплоченности общества, и призвал всех ценить и беречь мирную жизнь и стабильность.
+- Мы – счастливый народ. Нам необходимо беречь наше единство и уважать Независимость. Осуществление наших программ развития приведет страну к еще более светлому будущему, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана рассказал о современных вызовах, возникающих в мире на почве межэтнических конфликтов.
+- Желаю каждому дому, каждой семье крепкого здоровья, благополучия, счастья и уверенности в завтрашнем дне. С праздником! - заключил Елбасы.
+Оператор: Джаватаров.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -1815,7 +2291,14 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Первый Президент РК – Елбасы Н.А.Назарбаев на народных гуляниях по случаю Дня единства народа Казахстана. Выступление Елбасы перед жителями и гостями столицы. Оператор: Кульманов.</t>
+          <t>Елбасы Нурсултан Назарбаев посетил народные гуляния по случаю празднования Дня единства народа Казахстана.
+Выступая перед жителями и гостями столицы, Первый Президент Нурсултан Назарбаев поздравил всех казахстанцев с праздником единства народа Казахстана.
+- Благодаря единству наши предки преодолели все трудности, сохранив для нас Великую степь. Мы вместе создали независимый Казахстан, тем самым исполнив мечту наших прадедов, - сказал Нурсултан Назарбаев.
+Елбасы отметил, что все успехи современного Казахстана достигнуты благодаря сплоченности общества, и призвал всех ценить и беречь мирную жизнь и стабильность.
+- Мы – счастливый народ. Нам необходимо беречь наше единство и уважать Независимость. Осуществление наших программ развития приведет страну к еще более светлому будущему, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана рассказал о современных вызовах, возникающих в мире на почве межэтнических конфликтов.
+- Желаю каждому дому, каждой семье крепкого здоровья, благополучия, счастья и уверенности в завтрашнем дне. С праздником! - заключил Елбасы.
+Оператор: Кульманов.</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -1862,7 +2345,10 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с академиком, учёным-литературоведом С.Кирабаевым. Обсуждение развития отечественной литературы, вопросов образования и науки. Оператор: Х.О.</t>
+          <t>Елбасы Нурсултан Назарбаев принял академика Серика Кирабаева.
+Первый Президент Казахстана и известный ученый-литературовед обсудили текущее состояние и перспективы развития отечественной литературы. Особое внимание было уделено актуальным вопросам образования и науки.
+В ходе беседы С. Кирабаев выразил поддержку решению Нурсултана Назарбаева о сложении полномочий Президента и пожелал Елбасы успехов в дальнейшей деятельности.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D4" s="4" t="n"/>
@@ -1909,7 +2395,10 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с академиком, учёным-литературоведом С.Кирабаевым. Обсуждение развития отечественной литературы, вопросов образования и науки. Оператор: Д.Али.</t>
+          <t>Елбасы Нурсултан Назарбаев принял академика Серика Кирабаева.
+Первый Президент Казахстана и известный ученый-литературовед обсудили текущее состояние и перспективы развития отечественной литературы. Особое внимание было уделено актуальным вопросам образования и науки.
+В ходе беседы С. Кирабаев выразил поддержку решению Нурсултана Назарбаева о сложении полномочий Президента и пожелал Елбасы успехов в дальнейшей деятельности.
+Оператор: Д.Али.</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
@@ -1956,7 +2445,10 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с академиком, учёным-литературоведом С.Кирабаевым. Обсуждение развития отечественной литературы, вопросов образования и науки. Оператор: Д.Тлеспаев.</t>
+          <t>Елбасы Нурсултан Назарбаев принял академика Серика Кирабаева.
+Первый Президент Казахстана и известный ученый-литературовед обсудили текущее состояние и перспективы развития отечественной литературы. Особое внимание было уделено актуальным вопросам образования и науки.
+В ходе беседы С. Кирабаев выразил поддержку решению Нурсултана Назарбаева о сложении полномочий Президента и пожелал Елбасы успехов в дальнейшей деятельности.
+Оператор: Д.Тлеспаев.</t>
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
@@ -2003,7 +2495,10 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с академиком У.Калижановым. Информация о деятельности Института литературы и искусства им. М.О.Ауэзова. Оператор: Д.Али.</t>
+          <t>Первый Президент Казахстана принял академика Уалихана Калижанова.
+Нурсултану Назарбаеву была представлена информация о текущей научно-исследовательской деятельности Института литературы и искусства им. М.О.Ауэзова.
+Елбасы отметил вклад академика в развитие отечественной литературы и искусства, и поблагодарил за плодотворную работу во имя процветания Казахстана.
+Оператор: Д.Али.</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -2046,7 +2541,10 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с академиком У.Калижановым. Информация о деятельности Института литературы и искусства им. М.О.Ауэзова. Оператор: Д.Тлеспаев.</t>
+          <t>Первый Президент Казахстана принял академика Уалихана Калижанова.
+Нурсултану Назарбаеву была представлена информация о текущей научно-исследовательской деятельности Института литературы и искусства им. М.О.Ауэзова.
+Елбасы отметил вклад академика в развитие отечественной литературы и искусства, и поблагодарил за плодотворную работу во имя процветания Казахстана.
+Оператор: Д.Тлеспаев.</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -2089,7 +2587,10 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с академиком У.Калижановым. Информация о деятельности Института литературы и искусства им. М.О.Ауэзова. Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана принял академика Уалихана Калижанова.
+Нурсултану Назарбаеву была представлена информация о текущей научно-исследовательской деятельности Института литературы и искусства им. М.О.Ауэзова.
+Елбасы отметил вклад академика в развитие отечественной литературы и искусства, и поблагодарил за плодотворную работу во имя процветания Казахстана.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
@@ -2264,7 +2765,11 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с управляющим Международным финансовым центром «Астана» К.Келимбетовым. Оператор: А.И.</t>
+          <t>Первый Президент Казахстана принял Управляющего Международным финансовым центром «Астана» Кайрата Келимбетова.
+В ходе встречи Елбасы Н.Назарбаеву была представлена информация о текущей деятельности и дальнейших планах работы МФЦА.
+Нурсултан Назарбаев подчеркнул важность проводимой работы по развитию Международного финансового центра «Астана».
+- МФЦА – один из наших крупнейших и важных проектов. Мы возлагаем на него большие надежды, связанные с тем, что он станет финансовым центром не только Казахстана, но и всего региона. МФЦА будет развиваться по пути других финансовых центров мира. Я хочу, чтобы мы добились здесь успеха, - сказал Первый Президент Казахстана.
+Оператор: А.И.</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
@@ -2308,7 +2813,11 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с управляющим Международным финансовым центром «Астана» К.Келимбетовым. Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана принял Управляющего Международным финансовым центром «Астана» Кайрата Келимбетова.
+В ходе встречи Елбасы Н.Назарбаеву была представлена информация о текущей деятельности и дальнейших планах работы МФЦА.
+Нурсултан Назарбаев подчеркнул важность проводимой работы по развитию Международного финансового центра «Астана».
+- МФЦА – один из наших крупнейших и важных проектов. Мы возлагаем на него большие надежды, связанные с тем, что он станет финансовым центром не только Казахстана, но и всего региона. МФЦА будет развиваться по пути других финансовых центров мира. Я хочу, чтобы мы добились здесь успеха, - сказал Первый Президент Казахстана.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
@@ -2352,7 +2861,11 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с управляющим Международным финансовым центром «Астана» К.Келимбетовым. Оператор: Н.Баткеев.</t>
+          <t>Первый Президент Казахстана принял Управляющего Международным финансовым центром «Астана» Кайрата Келимбетова.
+В ходе встречи Елбасы Н.Назарбаеву была представлена информация о текущей деятельности и дальнейших планах работы МФЦА.
+Нурсултан Назарбаев подчеркнул важность проводимой работы по развитию Международного финансового центра «Астана».
+- МФЦА – один из наших крупнейших и важных проектов. Мы возлагаем на него большие надежды, связанные с тем, что он станет финансовым центром не только Казахстана, но и всего региона. МФЦА будет развиваться по пути других финансовых центров мира. Я хочу, чтобы мы добились здесь успеха, - сказал Первый Президент Казахстана.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -2396,7 +2909,13 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Чрезвычайным и Полномочным Послом США в Казахстане У.Мозером. Посол передал Елбасы письмо Президента США Д.Трампа. Оператор: А.И.</t>
+          <t>Нурсултан Назарбаев встретился с Чрезвычайным и Полномочным Послом Соединенных Штатов Америки в Казахстане Уильямом Мозером.
+Елбасы поздравил У. Мозера с началом дипломатической миссии в Казахстане, пожелав успехов и достижений на ответственном посту.
+- За все эти годы мы построили с США отношения, основанные на взаимопонимании и дружбе. В Казахстан пришли большие инвестиции из США. Работают 420 совместных предприятий. Мой визит в Вашингтон в прошлом году, в рамках которого состоялись переговоры с Президентом Трампом и встречи с бизнесменами, создал условия для дальнейшего развития нашего сотрудничества, - сказал Первый Президент Казахстана.
+В свою очередь Уильям Мозер поделился своими воспоминаниями о его первом визите в Казахстан. Посол США отметил достигнутые за относительно короткий период впечатляющие результаты в строительстве и позиционировании столицы страны – Нур-Султана.
+Кроме того, Посол США передал Нурсултану Назарбаеву письмо Дональда Трампа, в котором Президент США выражает поддержку принятому Елбасы решению о сложении полномочий и мирной передаче управления страной новому поколению политиков.
+- Я получил письмо Президента Трампа. Он выразил намерение встречаться и советоваться со мной в будущем по ситуации в нашем регионе. С Дональдом Трампом у нас сложились хорошие отношения, я готов поддерживать такие контакты. США являются для нас важным партнером. Все эти годы у нас были только дружеские отношения. Уверен, что политика подобного сотрудничества будет продолжена, – заключил Нурсултан Назарбаев.
+Оператор: А.И.</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
@@ -2442,7 +2961,13 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Чрезвычайным и Полномочным Послом США в Казахстане У.Мозером. Посол передал Елбасы письмо Президента США Д.Трампа. Оператор: Х.О.</t>
+          <t>Нурсултан Назарбаев встретился с Чрезвычайным и Полномочным Послом Соединенных Штатов Америки в Казахстане Уильямом Мозером.
+Елбасы поздравил У. Мозера с началом дипломатической миссии в Казахстане, пожелав успехов и достижений на ответственном посту.
+- За все эти годы мы построили с США отношения, основанные на взаимопонимании и дружбе. В Казахстан пришли большие инвестиции из США. Работают 420 совместных предприятий. Мой визит в Вашингтон в прошлом году, в рамках которого состоялись переговоры с Президентом Трампом и встречи с бизнесменами, создал условия для дальнейшего развития нашего сотрудничества, - сказал Первый Президент Казахстана.
+В свою очередь Уильям Мозер поделился своими воспоминаниями о его первом визите в Казахстан. Посол США отметил достигнутые за относительно короткий период впечатляющие результаты в строительстве и позиционировании столицы страны – Нур-Султана.
+Кроме того, Посол США передал Нурсултану Назарбаеву письмо Дональда Трампа, в котором Президент США выражает поддержку принятому Елбасы решению о сложении полномочий и мирной передаче управления страной новому поколению политиков.
+- Я получил письмо Президента Трампа. Он выразил намерение встречаться и советоваться со мной в будущем по ситуации в нашем регионе. С Дональдом Трампом у нас сложились хорошие отношения, я готов поддерживать такие контакты. США являются для нас важным партнером. Все эти годы у нас были только дружеские отношения. Уверен, что политика подобного сотрудничества будет продолжена, – заключил Нурсултан Назарбаев.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -2488,7 +3013,13 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Чрезвычайным и Полномочным Послом США в Казахстане У.Мозером. Посол передал Елбасы письмо Президента США Д.Трампа. Оператор: Н.Баткеев.</t>
+          <t>Нурсултан Назарбаев встретился с Чрезвычайным и Полномочным Послом Соединенных Штатов Америки в Казахстане Уильямом Мозером.
+Елбасы поздравил У. Мозера с началом дипломатической миссии в Казахстане, пожелав успехов и достижений на ответственном посту.
+- За все эти годы мы построили с США отношения, основанные на взаимопонимании и дружбе. В Казахстан пришли большие инвестиции из США. Работают 420 совместных предприятий. Мой визит в Вашингтон в прошлом году, в рамках которого состоялись переговоры с Президентом Трампом и встречи с бизнесменами, создал условия для дальнейшего развития нашего сотрудничества, - сказал Первый Президент Казахстана.
+В свою очередь Уильям Мозер поделился своими воспоминаниями о его первом визите в Казахстан. Посол США отметил достигнутые за относительно короткий период впечатляющие результаты в строительстве и позиционировании столицы страны – Нур-Султана.
+Кроме того, Посол США передал Нурсултану Назарбаеву письмо Дональда Трампа, в котором Президент США выражает поддержку принятому Елбасы решению о сложении полномочий и мирной передаче управления страной новому поколению политиков.
+- Я получил письмо Президента Трампа. Он выразил намерение встречаться и советоваться со мной в будущем по ситуации в нашем регионе. С Дональдом Трампом у нас сложились хорошие отношения, я готов поддерживать такие контакты. США являются для нас важным партнером. Все эти годы у нас были только дружеские отношения. Уверен, что политика подобного сотрудничества будет продолжена, – заключил Нурсултан Назарбаев.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
       <c r="D19" s="2" t="n"/>
@@ -2534,7 +3065,14 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Посещение Первым Президентом РК – Елбасы Н.А.Назарбаевым Международного центра зелёных технологий и инвестиционных проектов. Презентация цифровой площадки по возобновляемым источникам энергии, проектов казахстанских вузов. Исходник SBS.</t>
+          <t>Елбасы Нурсултан Назарбаев посетил Международный центр зеленых технологий и инвестиционных проектов.
+В ходе посещения Первому Президенту Казахстана была представлена информация по основным направлениям работы Центра в сфере развития зеленой экономики и обеспечения безопасности окружающей среды.
+Елбасы Н. Назарбаеву был презентован прототип цифровой площадки, объединяющей информацию о потенциале ветровых, солнечных, гидро- и геотермальных ресурсов, расположении полигонов ТБО и биомассы.
+Нурсултан Назарбаев подчеркнул необходимость обеспечения экологической безопасности и развития возобновляемых источников энергии в стране.
+Елбасы акцентировал внимание на вопросах внедрения передовых технологий в сфере переработки ТБО и привлечения инвесторов в данную отрасль.
+Первый Президент Казахстана также ознакомился с рядом проектов и перспективными разработками казахстанских вузов в сфере возобновляемых источников энергии.
+НАО «Международный центр зеленых технологий и инвестиционных проектов» (IGTIC) был создан в апреле 2018 года на базе инфраструктуры и наследия выставки «Астана – ЭКСПО 2017».
+Исходник SBS.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2581,7 +3119,14 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Посещение Первым Президентом РК – Елбасы Н.А.Назарбаевым Международного центра зелёных технологий и инвестиционных проектов. Презентация цифровой площадки по возобновляемым источникам энергии, проектов казахстанских вузов. Исходник SBS.</t>
+          <t>Елбасы Нурсултан Назарбаев посетил Международный центр зеленых технологий и инвестиционных проектов.
+В ходе посещения Первому Президенту Казахстана была представлена информация по основным направлениям работы Центра в сфере развития зеленой экономики и обеспечения безопасности окружающей среды.
+Елбасы Н. Назарбаеву был презентован прототип цифровой площадки, объединяющей информацию о потенциале ветровых, солнечных, гидро- и геотермальных ресурсов, расположении полигонов ТБО и биомассы.
+Нурсултан Назарбаев подчеркнул необходимость обеспечения экологической безопасности и развития возобновляемых источников энергии в стране.
+Елбасы акцентировал внимание на вопросах внедрения передовых технологий в сфере переработки ТБО и привлечения инвесторов в данную отрасль.
+Первый Президент Казахстана также ознакомился с рядом проектов и перспективными разработками казахстанских вузов в сфере возобновляемых источников энергии.
+НАО «Международный центр зеленых технологий и инвестиционных проектов» (IGTIC) был создан в апреле 2018 года на базе инфраструктуры и наследия выставки «Астана – ЭКСПО 2017».
+Исходник SBS.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2628,7 +3173,14 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Посещение Первым Президентом РК – Елбасы Н.А.Назарбаевым Международного центра зелёных технологий и инвестиционных проектов. Презентация цифровой площадки по возобновляемым источникам энергии, проектов казахстанских вузов. Исходник SBS.</t>
+          <t>Елбасы Нурсултан Назарбаев посетил Международный центр зеленых технологий и инвестиционных проектов.
+В ходе посещения Первому Президенту Казахстана была представлена информация по основным направлениям работы Центра в сфере развития зеленой экономики и обеспечения безопасности окружающей среды.
+Елбасы Н. Назарбаеву был презентован прототип цифровой площадки, объединяющей информацию о потенциале ветровых, солнечных, гидро- и геотермальных ресурсов, расположении полигонов ТБО и биомассы.
+Нурсултан Назарбаев подчеркнул необходимость обеспечения экологической безопасности и развития возобновляемых источников энергии в стране.
+Елбасы акцентировал внимание на вопросах внедрения передовых технологий в сфере переработки ТБО и привлечения инвесторов в данную отрасль.
+Первый Президент Казахстана также ознакомился с рядом проектов и перспективными разработками казахстанских вузов в сфере возобновляемых источников энергии.
+НАО «Международный центр зеленых технологий и инвестиционных проектов» (IGTIC) был создан в апреле 2018 года на базе инфраструктуры и наследия выставки «Астана – ЭКСПО 2017».
+Исходник SBS.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2675,7 +3227,14 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Посещение Первым Президентом РК – Елбасы Н.А.Назарбаевым Международного центра зелёных технологий и инвестиционных проектов. Презентация цифровой площадки по возобновляемым источникам энергии, проектов казахстанских вузов. Исходник XDCAM.</t>
+          <t>Елбасы Нурсултан Назарбаев посетил Международный центр зеленых технологий и инвестиционных проектов.
+В ходе посещения Первому Президенту Казахстана была представлена информация по основным направлениям работы Центра в сфере развития зеленой экономики и обеспечения безопасности окружающей среды.
+Елбасы Н. Назарбаеву был презентован прототип цифровой площадки, объединяющей информацию о потенциале ветровых, солнечных, гидро- и геотермальных ресурсов, расположении полигонов ТБО и биомассы.
+Нурсултан Назарбаев подчеркнул необходимость обеспечения экологической безопасности и развития возобновляемых источников энергии в стране.
+Елбасы акцентировал внимание на вопросах внедрения передовых технологий в сфере переработки ТБО и привлечения инвесторов в данную отрасль.
+Первый Президент Казахстана также ознакомился с рядом проектов и перспективными разработками казахстанских вузов в сфере возобновляемых источников энергии.
+НАО «Международный центр зеленых технологий и инвестиционных проектов» (IGTIC) был создан в апреле 2018 года на базе инфраструктуры и наследия выставки «Астана – ЭКСПО 2017».
+Исходник XDCAM.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2722,7 +3281,15 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. Крупный план.</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+Крупный план.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2770,7 +3337,15 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. Крупный план.</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+Крупный план.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2818,7 +3393,15 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. PGM (программный микс).</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+PGM (программный микс).</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2866,7 +3449,15 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. PGM (программный микс).</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+PGM (программный микс).</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2914,7 +3505,15 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. Исходник камеры; без Елбасы.</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+Исходник камеры; без Елбасы.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2962,7 +3561,15 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. Исходник камеры; без Елбасы.</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+Исходник камеры; без Елбасы.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3010,7 +3617,15 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум «Вдохновляющий рост: люди, города, экономики». Выступление Первого Президента РК – Елбасы Н.А.Назарбаева на пленарном заседании. Конгресс-центр. Личники.</t>
+          <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+Личники.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3058,7 +3673,16 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум. Церемония фотографирования Первого Президента РК – Елбасы Н.А.Назарбаева и Президента РК К.-Ж.Токаева. Оператор: Абилов.</t>
+          <t>XII Астанинский экономический форум. Церемония фотографирования Первого Президента РК – Елбасы Н.А.Назарбаева и Президента РК К.-Ж.Токаева.
+Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики».
+Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
+- Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
+В ходе пленарного заседания Елбасы поделился своим мнением относительно последних изменений в глобальной экономике и предложил ряд идей по улучшению межгосударственного диалога. В своем выступлении Первый Президент Казахстана остановился на вопросах развития мировой экономики, цифровизации, трансформации образовательных процессов, повышения требований к человеческому капиталу, а также перспективах урбанизации.
+- Как видите, горизонты экономического планирования сильно сужаются. Пути выхода из сложных ситуаций можно и нужно находить в рамках международных организаций и форумов, таких как ООН, G-20, Всемирная торговая организация. Пришло время переходить к совместному обсуждению и управлению. Недавно на втором Форуме «Один пояс, один путь» в Пекине я предложил формировать устойчивую глобальную архитектуру на основе новой геополитической реальности «Три Д», которая подразумевает налаживание диалога на трех уровнях, - подчеркнул Нурсултан Назарбаев.
+Кроме того, Елбасы предложил принять меры по расширению формата международного диалога на площадке АЭФ.
+- У меня нет сомнений, что высказанные здесь идеи будут способствовать поиску решений на самые сложные и актуальные вопросы мировой политики и экономики, - отметил Первый Президент Казахстана.
+С полным текстом выступления можно ознакомиться здесь.
+Оператор: Абилов.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3110,7 +3734,11 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Верховного суда РК Ж.Асановым. Доклад о модернизации судебной системы. Оператор: А.И.</t>
+          <t>Первый Президент Казахстана принял председателя Верховного суда Жакипа Асанова.
+Елбасы Н.Назарбаев был проинформирован о ходе модернизации судебной системы.
+Председатель Верховного суда, в частности, доложил, что на сегодняшний день разработано 15 законопроектов, направленных на улучшение качества деятельности судов и повышение доверия населения к работе судей.
+В ходе встречи были также обсуждены вопросы исполнения поручений, данных на совещании от 19 ноября 2018 года.
+Оператор: А.И.</t>
         </is>
       </c>
       <c r="D32" s="2" t="n"/>
@@ -3154,7 +3782,11 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Верховного суда РК Ж.Асановым. Доклад о модернизации судебной системы. Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана принял председателя Верховного суда Жакипа Асанова.
+Елбасы Н.Назарбаев был проинформирован о ходе модернизации судебной системы.
+Председатель Верховного суда, в частности, доложил, что на сегодняшний день разработано 15 законопроектов, направленных на улучшение качества деятельности судов и повышение доверия населения к работе судей.
+В ходе встречи были также обсуждены вопросы исполнения поручений, данных на совещании от 19 ноября 2018 года.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -3198,7 +3830,11 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Верховного суда РК Ж.Асановым. Доклад о модернизации судебной системы. Оператор: Н.Баткеев.</t>
+          <t>Первый Президент Казахстана принял председателя Верховного суда Жакипа Асанова.
+Елбасы Н.Назарбаев был проинформирован о ходе модернизации судебной системы.
+Председатель Верховного суда, в частности, доложил, что на сегодняшний день разработано 15 законопроектов, направленных на улучшение качества деятельности судов и повышение доверия населения к работе судей.
+В ходе встречи были также обсуждены вопросы исполнения поручений, данных на совещании от 19 ноября 2018 года.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
       <c r="D34" s="2" t="n"/>
@@ -3242,7 +3878,8 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум, второй день. Без участия Елбасы. Конгресс-центр. Крупный план; без Елбасы.</t>
+          <t>XII Астанинский экономический форум, второй день. Конгресс-центр.
+Крупный план; без Елбасы.</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -3294,7 +3931,8 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум, второй день. Без участия Елбасы. Конгресс-центр. Крупный план; без Елбасы.</t>
+          <t>XII Астанинский экономический форум, второй день. Конгресс-центр.
+Крупный план; без Елбасы.</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -3346,7 +3984,8 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум, второй день. Без участия Елбасы. Конгресс-центр. PGM (программный микс); без Елбасы.</t>
+          <t>XII Астанинский экономический форум, второй день. Конгресс-центр.
+PGM (программный микс); без Елбасы.</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3398,7 +4037,8 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>XII Астанинский экономический форум, второй день. Без участия Елбасы. Конгресс-центр. PGM (программный микс); без Елбасы.</t>
+          <t>XII Астанинский экономический форум, второй день. Конгресс-центр.
+PGM (программный микс); без Елбасы.</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -3450,7 +4090,11 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с президентом АОО «Назарбаев Университет» Ш.Катсу. Доклад о развитии университета и подготовке к церемонии вручения дипломов. СНХ (уточнить расшифровку). Оператор: Н.Баткеев.</t>
+          <t>Елбасы принял президента АОО «Назарбаев Университет» Шигео Катсу.
+В ходе встречи Первому Президенту Казахстана было доложено о текущем развитии «Назарбаев Университета» и ходе подготовки к пятой церемонии вручения дипломов выпускникам вуза.
+- Многие не верили, что у нас будет университет международного уровня. И вот Вы уже долгие годы являетесь ректором такого университета. У вуза есть интеллектуальный потенциал – ученые, которые поднимают уровень учебного заведения. «Назарбаев Университет» стал одним из брендов Казахстана, - сказал Елбасы.
+По итогам встречи Нурсултан Назарбаев дал ряд поручений.
+СНХ (уточнить расшифровку). Оператор: Н.Баткеев.</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3502,7 +4146,11 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с президентом АОО «Назарбаев Университет» Ш.Катсу. Доклад о развитии университета и подготовке к церемонии вручения дипломов. Оператор: А.И.</t>
+          <t>Елбасы принял президента АОО «Назарбаев Университет» Шигео Катсу.
+В ходе встречи Первому Президенту Казахстана было доложено о текущем развитии «Назарбаев Университета» и ходе подготовки к пятой церемонии вручения дипломов выпускникам вуза.
+- Многие не верили, что у нас будет университет международного уровня. И вот Вы уже долгие годы являетесь ректором такого университета. У вуза есть интеллектуальный потенциал – ученые, которые поднимают уровень учебного заведения. «Назарбаев Университет» стал одним из брендов Казахстана, - сказал Елбасы.
+По итогам встречи Нурсултан Назарбаев дал ряд поручений.
+Оператор: А.И.</t>
         </is>
       </c>
       <c r="D40" s="4" t="n"/>
@@ -3550,7 +4198,11 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с президентом АОО «Назарбаев Университет» Ш.Катсу. Доклад о развитии университета и подготовке к церемонии вручения дипломов. Оператор: Х.О.</t>
+          <t>Елбасы принял президента АОО «Назарбаев Университет» Шигео Катсу.
+В ходе встречи Первому Президенту Казахстана было доложено о текущем развитии «Назарбаев Университета» и ходе подготовки к пятой церемонии вручения дипломов выпускникам вуза.
+- Многие не верили, что у нас будет университет международного уровня. И вот Вы уже долгие годы являетесь ректором такого университета. У вуза есть интеллектуальный потенциал – ученые, которые поднимают уровень учебного заведения. «Назарбаев Университет» стал одним из брендов Казахстана, - сказал Елбасы.
+По итогам встречи Нурсултан Назарбаев дал ряд поручений.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D41" s="4" t="n"/>
@@ -3598,7 +4250,11 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с президентом АОО «Назарбаев Университет» Ш.Катсу. Доклад о развитии университета и подготовке к церемонии вручения дипломов. Оператор: Н.Баткеев.</t>
+          <t>Елбасы принял президента АОО «Назарбаев Университет» Шигео Катсу.
+В ходе встречи Первому Президенту Казахстана было доложено о текущем развитии «Назарбаев Университета» и ходе подготовки к пятой церемонии вручения дипломов выпускникам вуза.
+- Многие не верили, что у нас будет университет международного уровня. И вот Вы уже долгие годы являетесь ректором такого университета. У вуза есть интеллектуальный потенциал – ученые, которые поднимают уровень учебного заведения. «Назарбаев Университет» стал одним из брендов Казахстана, - сказал Елбасы.
+По итогам встречи Нурсултан Назарбаев дал ряд поручений.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
       <c r="D42" s="4" t="n"/>
@@ -3646,7 +4302,16 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с министром труда и социальной защиты населения РК Б.Сапарбаевым. Оператор: А.И.</t>
+          <t>Елбасы Нурсултан Назарбаев принял министра труда и социальной защиты населения Бердибека Сапарбаева.
+В ходе встречи Елбасы был проинформирован о деятельности Правительственной рабочей группы по разъяснению новых социальных мер «Әлеуметтік қамқорлық».
+Первый Президент Казахстана отметил, что Б.Сапарбаев обладает достаточным опытом и управленческими навыками для решения поставленных перед министерством задач.
+- У вас большой опыт. Работали на важных участках. Руководили в трех областях. Показывали хорошую работу. Подняли показатели Актюбинской области по многим отраслям. Вы были назначены в министерство, так как была необходимость подтянуть этот фронт работы. Нужен был опытный человек. Необходимо решить все поставленные вопросы до конца во благо нашего народа, - отметил Елбасы.
+Б.Сапарбаев рассказал Нурсултану Назарбаеву о проводимой министерством работе по реализации новых социальных мер, направленных на повышение уровня жизни казахстанцев. В частности, министр представил информацию о порядке начисления адресной социальной помощи и предпринимаемых шагах по созданию новых рабочих мест.
+Первый Президент Казахстана указал на необходимость обеспечения соответствующего контроля и систематизации процесса оказания помощи нуждающимся категориям населения.
+- Сейчас социальные расходы составляют почти половину доходов государства. Важно систематизировать всю работу. Прежде всего, люди должны быть обеспечены рабочими местами. Конечно, есть те, кто в виду объективных причин, не может работать. Им мы должны помогать, - сказал Елбасы.
+Кроме того, Б.Сапарбаев доложил о работе по решению жилищных вопросов в регионах и поддержке лиц с особыми потребностями. Министр рассказал о принимаемых совместно с предпринимателями мерах в рамках реализации принципа социальной ответственности бизнеса. Бердибек Сапарбаев также остановился на вопросах миграции и поддержки многодетных семей и оралманов.
+В завершение Нурсултан Назарбаев подчеркнул важность проводимой министерством работы и отметил необходимость эффективного решения поставленных задач.
+Оператор: А.И.</t>
         </is>
       </c>
       <c r="D43" s="4" t="n"/>
@@ -3699,7 +4364,16 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с министром труда и социальной защиты населения РК Б.Сапарбаевым. Оператор: Х.О.</t>
+          <t>Елбасы Нурсултан Назарбаев принял министра труда и социальной защиты населения Бердибека Сапарбаева.
+В ходе встречи Елбасы был проинформирован о деятельности Правительственной рабочей группы по разъяснению новых социальных мер «Әлеуметтік қамқорлық».
+Первый Президент Казахстана отметил, что Б.Сапарбаев обладает достаточным опытом и управленческими навыками для решения поставленных перед министерством задач.
+- У вас большой опыт. Работали на важных участках. Руководили в трех областях. Показывали хорошую работу. Подняли показатели Актюбинской области по многим отраслям. Вы были назначены в министерство, так как была необходимость подтянуть этот фронт работы. Нужен был опытный человек. Необходимо решить все поставленные вопросы до конца во благо нашего народа, - отметил Елбасы.
+Б.Сапарбаев рассказал Нурсултану Назарбаеву о проводимой министерством работе по реализации новых социальных мер, направленных на повышение уровня жизни казахстанцев. В частности, министр представил информацию о порядке начисления адресной социальной помощи и предпринимаемых шагах по созданию новых рабочих мест.
+Первый Президент Казахстана указал на необходимость обеспечения соответствующего контроля и систематизации процесса оказания помощи нуждающимся категориям населения.
+- Сейчас социальные расходы составляют почти половину доходов государства. Важно систематизировать всю работу. Прежде всего, люди должны быть обеспечены рабочими местами. Конечно, есть те, кто в виду объективных причин, не может работать. Им мы должны помогать, - сказал Елбасы.
+Кроме того, Б.Сапарбаев доложил о работе по решению жилищных вопросов в регионах и поддержке лиц с особыми потребностями. Министр рассказал о принимаемых совместно с предпринимателями мерах в рамках реализации принципа социальной ответственности бизнеса. Бердибек Сапарбаев также остановился на вопросах миграции и поддержки многодетных семей и оралманов.
+В завершение Нурсултан Назарбаев подчеркнул важность проводимой министерством работы и отметил необходимость эффективного решения поставленных задач.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D44" s="4" t="n"/>
@@ -3752,7 +4426,16 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с министром труда и социальной защиты населения РК Б.Сапарбаевым. Оператор: Н.Баткеев.</t>
+          <t>Елбасы Нурсултан Назарбаев принял министра труда и социальной защиты населения Бердибека Сапарбаева.
+В ходе встречи Елбасы был проинформирован о деятельности Правительственной рабочей группы по разъяснению новых социальных мер «Әлеуметтік қамқорлық».
+Первый Президент Казахстана отметил, что Б.Сапарбаев обладает достаточным опытом и управленческими навыками для решения поставленных перед министерством задач.
+- У вас большой опыт. Работали на важных участках. Руководили в трех областях. Показывали хорошую работу. Подняли показатели Актюбинской области по многим отраслям. Вы были назначены в министерство, так как была необходимость подтянуть этот фронт работы. Нужен был опытный человек. Необходимо решить все поставленные вопросы до конца во благо нашего народа, - отметил Елбасы.
+Б.Сапарбаев рассказал Нурсултану Назарбаеву о проводимой министерством работе по реализации новых социальных мер, направленных на повышение уровня жизни казахстанцев. В частности, министр представил информацию о порядке начисления адресной социальной помощи и предпринимаемых шагах по созданию новых рабочих мест.
+Первый Президент Казахстана указал на необходимость обеспечения соответствующего контроля и систематизации процесса оказания помощи нуждающимся категориям населения.
+- Сейчас социальные расходы составляют почти половину доходов государства. Важно систематизировать всю работу. Прежде всего, люди должны быть обеспечены рабочими местами. Конечно, есть те, кто в виду объективных причин, не может работать. Им мы должны помогать, - сказал Елбасы.
+Кроме того, Б.Сапарбаев доложил о работе по решению жилищных вопросов в регионах и поддержке лиц с особыми потребностями. Министр рассказал о принимаемых совместно с предпринимателями мерах в рамках реализации принципа социальной ответственности бизнеса. Бердибек Сапарбаев также остановился на вопросах миграции и поддержки многодетных семей и оралманов.
+В завершение Нурсултан Назарбаев подчеркнул важность проводимой министерством работы и отметил необходимость эффективного решения поставленных задач.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
       <c r="D45" s="4" t="n"/>
@@ -3805,7 +4488,11 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с молодым композитором Р.Абдысагиным, победителем проекта «100 новых лиц Казахстана». Презентация оперы «Путь, освещённый солнцем». Оператор: А.И.</t>
+          <t>Елбасы принял молодого композитора Рахат-Би Абдысагина.
+В ходе встречи талантливый композитор, один из победителей конкурса «100 новых лиц Казахстана» представил Нурсултану Назарбаеву свою новую оперу «Путь, освещенный солнцем».
+Музыкальное произведение будет посвящено истории становления и развития Независимого Казахстана.
+Нурсултан Назарбаев пожелал Р.Абдысагину творческих успехов и новых свершений.
+Оператор: А.И.</t>
         </is>
       </c>
       <c r="D46" s="2" t="n"/>
@@ -3849,7 +4536,11 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с молодым композитором Р.Абдысагиным, победителем проекта «100 новых лиц Казахстана». Презентация оперы «Путь, освещённый солнцем». Оператор: Х.О.</t>
+          <t>Елбасы принял молодого композитора Рахат-Би Абдысагина.
+В ходе встречи талантливый композитор, один из победителей конкурса «100 новых лиц Казахстана» представил Нурсултану Назарбаеву свою новую оперу «Путь, освещенный солнцем».
+Музыкальное произведение будет посвящено истории становления и развития Независимого Казахстана.
+Нурсултан Назарбаев пожелал Р.Абдысагину творческих успехов и новых свершений.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D47" s="2" t="n"/>
@@ -3893,7 +4584,11 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с молодым композитором Р.Абдысагиным, победителем проекта «100 новых лиц Казахстана». Презентация оперы «Путь, освещённый солнцем». Оператор: Н.Баткеев.</t>
+          <t>Елбасы принял молодого композитора Рахат-Би Абдысагина.
+В ходе встречи талантливый композитор, один из победителей конкурса «100 новых лиц Казахстана» представил Нурсултану Назарбаеву свою новую оперу «Путь, освещенный солнцем».
+Музыкальное произведение будет посвящено истории становления и развития Независимого Казахстана.
+Нурсултан Назарбаев пожелал Р.Абдысагину творческих успехов и новых свершений.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
       <c r="D48" s="2" t="n"/>
@@ -3937,7 +4632,16 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с министром иностранных дел Турецкой Республики М.Чавушоглу. Оператор: А.И.</t>
+          <t>Елбасы Нурсултан Назарбаев встретился с министром иностранных дел Турецкой Республики Мевлютом Чавушоглу.
+В ходе встречи Первый Президент Казахстана отметил важность сохранения и дальнейшего углубления сотрудничества между двумя братскими странами.
+- С первых дней независимости Турция всегда поддерживала нас. Наши государства и народы очень близки друг к другу. Мы ввели безвизовый режим между двумя странами. Отношения Казахстана и Турции крепнут год от года. Уверен, что этот курс будет продолжен, - сказал Елбасы.
+Нурсултан Назарбаев также подчеркнул необходимость развития межгосударственных связей в рамках Тюркского совета.
+- Совет сотрудничества тюркоязычных государств был создан в целях развития и укрепления связей между тюркскими народами. Данную работу следует продолжать. Я буду оказывать всестороннюю поддержку, - сказал Первый Президент Казахстана.
+В свою очередь, М.Чавушоглу поприветствовал Елбасы и от имени Президента Реджепа Эрдогана пригласил Нурсултана Назарбаева посетить Турцию в ближайшее время.
+- Мы приветствуем, что Вы в качестве Елбасы, председателя Совета Безопасности, руководителя партии «Nur Otan» продолжаете активно работать во благо народа Казахстана. Нам хорошо известно, какой колоссальный труд Вы вложили во имя процветания своей страны и развитие двусторонних отношений, - отметил министр иностранных дел Турецкой Республики.
+В ходе беседы стороны также обсудили актуальные вопросы международной и региональной повестки дня.
+В завершение встречи глава МИД Турецкой Республики сообщил, что в соответствии с принятым решением лидеров государств Тюркского совета за значительный вклад в развитие стран тюркского мира Нурсултану Назарбаеву был присвоен пожизненный статус Почетного председателя Совета сотрудничества тюркоязычных государств.
+Оператор: А.И.</t>
         </is>
       </c>
       <c r="D49" s="2" t="n"/>
@@ -3986,7 +4690,16 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с министром иностранных дел Турецкой Республики М.Чавушоглу. Оператор: Х.О.</t>
+          <t>Елбасы Нурсултан Назарбаев встретился с министром иностранных дел Турецкой Республики Мевлютом Чавушоглу.
+В ходе встречи Первый Президент Казахстана отметил важность сохранения и дальнейшего углубления сотрудничества между двумя братскими странами.
+- С первых дней независимости Турция всегда поддерживала нас. Наши государства и народы очень близки друг к другу. Мы ввели безвизовый режим между двумя странами. Отношения Казахстана и Турции крепнут год от года. Уверен, что этот курс будет продолжен, - сказал Елбасы.
+Нурсултан Назарбаев также подчеркнул необходимость развития межгосударственных связей в рамках Тюркского совета.
+- Совет сотрудничества тюркоязычных государств был создан в целях развития и укрепления связей между тюркскими народами. Данную работу следует продолжать. Я буду оказывать всестороннюю поддержку, - сказал Первый Президент Казахстана.
+В свою очередь, М.Чавушоглу поприветствовал Елбасы и от имени Президента Реджепа Эрдогана пригласил Нурсултана Назарбаева посетить Турцию в ближайшее время.
+- Мы приветствуем, что Вы в качестве Елбасы, председателя Совета Безопасности, руководителя партии «Nur Otan» продолжаете активно работать во благо народа Казахстана. Нам хорошо известно, какой колоссальный труд Вы вложили во имя процветания своей страны и развитие двусторонних отношений, - отметил министр иностранных дел Турецкой Республики.
+В ходе беседы стороны также обсудили актуальные вопросы международной и региональной повестки дня.
+В завершение встречи глава МИД Турецкой Республики сообщил, что в соответствии с принятым решением лидеров государств Тюркского совета за значительный вклад в развитие стран тюркского мира Нурсултану Назарбаеву был присвоен пожизненный статус Почетного председателя Совета сотрудничества тюркоязычных государств.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D50" s="2" t="n"/>
@@ -4035,7 +4748,16 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с министром иностранных дел Турецкой Республики М.Чавушоглу. Оператор: Н.Баткеев.</t>
+          <t>Елбасы Нурсултан Назарбаев встретился с министром иностранных дел Турецкой Республики Мевлютом Чавушоглу.
+В ходе встречи Первый Президент Казахстана отметил важность сохранения и дальнейшего углубления сотрудничества между двумя братскими странами.
+- С первых дней независимости Турция всегда поддерживала нас. Наши государства и народы очень близки друг к другу. Мы ввели безвизовый режим между двумя странами. Отношения Казахстана и Турции крепнут год от года. Уверен, что этот курс будет продолжен, - сказал Елбасы.
+Нурсултан Назарбаев также подчеркнул необходимость развития межгосударственных связей в рамках Тюркского совета.
+- Совет сотрудничества тюркоязычных государств был создан в целях развития и укрепления связей между тюркскими народами. Данную работу следует продолжать. Я буду оказывать всестороннюю поддержку, - сказал Первый Президент Казахстана.
+В свою очередь, М.Чавушоглу поприветствовал Елбасы и от имени Президента Реджепа Эрдогана пригласил Нурсултана Назарбаева посетить Турцию в ближайшее время.
+- Мы приветствуем, что Вы в качестве Елбасы, председателя Совета Безопасности, руководителя партии «Nur Otan» продолжаете активно работать во благо народа Казахстана. Нам хорошо известно, какой колоссальный труд Вы вложили во имя процветания своей страны и развитие двусторонних отношений, - отметил министр иностранных дел Турецкой Республики.
+В ходе беседы стороны также обсудили актуальные вопросы международной и региональной повестки дня.
+В завершение встречи глава МИД Турецкой Республики сообщил, что в соответствии с принятым решением лидеров государств Тюркского совета за значительный вклад в развитие стран тюркского мира Нурсултану Назарбаеву был присвоен пожизненный статус Почетного председателя Совета сотрудничества тюркоязычных государств.
+Оператор: Н.Баткеев.</t>
         </is>
       </c>
       <c r="D51" s="2" t="n"/>
@@ -4084,7 +4806,13 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Коллегии Евразийской экономической комиссии Т.Саркисяном. Крупный план.</t>
+          <t>Первый Президент Казахстана принял председателя Коллегии Евразийской экономической комиссии Тиграна Саркисяна.
+В ходе встречи стороны обсудили текущее состояние и перспективы развития Евразийского экономического союза.
+Нурсултан Назарбаев подчеркнул, что многие страны и организации заинтересованы в налаживании сотрудничества с ЕАЭС и указал на необходимость расширения географии экономических партнеров союза.
+- Завтра здесь состоится юбилейное заседание ВЕЭС. Вы председательствуете в исполнительном органе союза, успешно справляясь с поставленными задачами. Нужно продолжать двигаться вперед, - сказал Первый Президент Казахстана.
+В свою очередь Тигран Саркисян отметил достижения в развитии экономического союза.
+- Благодарю Вас за возможность обсудить вопросы интеграции и практическую реализацию идеи, предложенную Вами 25 лет назад. Вот уже 5 лет мы реализуем этот проект. Мудрость, проявленная Вами четверть века назад, была жизненно необходима нашим странам, - сказал председатель Коллегии Евразийской экономической комиссии.
+Крупный план.</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -4134,7 +4862,13 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Республики Таджикистан Э.Рахмоном. Крупный план.</t>
+          <t>Нурсултан Назарбаев встретился с Президентом Республики Таджикистан Эмомали Рахмоном.
+В ходе переговоров Елбасы отметил, что с первых дней сотрудничества Казахстан и Таджикистан построили крепкие дружественные и доверительные отношения.
+- Наша дружба крепнет год от года. Вы возглавляете Таджикистан в условиях сложной ситуации в мире. Вы поступательно развиваетесь, в стране обеспечивается стабильность, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана также подчеркнул, что двусторонние отношения будут и впредь укрепляться во благо двух братских народов.
+В свою очередь Эмомали Рахмон отметил высокие темпы развития Казахстана, достигнутые под руководством Елбасы.
+- Я свидетель того, как менялся облик Казахстана. Я помню первые встречи в столице и вижу, как она преобразилась. Позитивные изменения охватили не только город, но и всю страну. Это результат Вашей плодотворной работы, мудрой и дальновидной политики, - сказал Президент Таджикистана.
+Крупный план.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -4180,7 +4914,13 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Республики Таджикистан Э.Рахмоном. Стационар.</t>
+          <t>Нурсултан Назарбаев встретился с Президентом Республики Таджикистан Эмомали Рахмоном.
+В ходе переговоров Елбасы отметил, что с первых дней сотрудничества Казахстан и Таджикистан построили крепкие дружественные и доверительные отношения.
+- Наша дружба крепнет год от года. Вы возглавляете Таджикистан в условиях сложной ситуации в мире. Вы поступательно развиваетесь, в стране обеспечивается стабильность, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана также подчеркнул, что двусторонние отношения будут и впредь укрепляться во благо двух братских народов.
+В свою очередь Эмомали Рахмон отметил высокие темпы развития Казахстана, достигнутые под руководством Елбасы.
+- Я свидетель того, как менялся облик Казахстана. Я помню первые встречи в столице и вижу, как она преобразилась. Позитивные изменения охватили не только город, но и всю страну. Это результат Вашей плодотворной работы, мудрой и дальновидной политики, - сказал Президент Таджикистана.
+Стационар.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -4226,7 +4966,13 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Республики Таджикистан Э.Рахмоном. Оператор: Х.О.</t>
+          <t>Нурсултан Назарбаев встретился с Президентом Республики Таджикистан Эмомали Рахмоном.
+В ходе переговоров Елбасы отметил, что с первых дней сотрудничества Казахстан и Таджикистан построили крепкие дружественные и доверительные отношения.
+- Наша дружба крепнет год от года. Вы возглавляете Таджикистан в условиях сложной ситуации в мире. Вы поступательно развиваетесь, в стране обеспечивается стабильность, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана также подчеркнул, что двусторонние отношения будут и впредь укрепляться во благо двух братских народов.
+В свою очередь Эмомали Рахмон отметил высокие темпы развития Казахстана, достигнутые под руководством Елбасы.
+- Я свидетель того, как менялся облик Казахстана. Я помню первые встречи в столице и вижу, как она преобразилась. Позитивные изменения охватили не только город, но и всю страну. Это результат Вашей плодотворной работы, мудрой и дальновидной политики, - сказал Президент Таджикистана.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D55" s="2" t="n"/>
@@ -4272,7 +5018,15 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Республики Беларусь А.Лукашенко. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Стационар.</t>
+          <t>Первый Президент Казахстана встретился с Президентом Республики Беларусь Александром Лукашенко.
+В ходе встречи Елбасы вручил высокому гостю орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана особо отметил роль и вклад Александра Лукашенко в развитие интеграционных процессов и становление Евразийского экономического союза.
+- Этот год ознаменован пятилетием создания здесь Евразийского экономического союза и 25-летием идеи евразийской интеграции, предложенной мною. И без вашей поддержки не было бы этой организации, - сказал Нурсултан Назарбаев.
+Елбасы подчеркнул, что всегда будет готов оказать поддержку народу Беларуси во главе с ее лидером А. Лукашенко.
+- Я всегда буду готов помочь и поддержать Вас по любому направлению. Вам удается держать Беларусь на высоком уровне. Также, пользуясь случаем, приглашаю Вас посетить красивейшие места Казахстана, - сказал Первый Президент Казахстана.
+В свою очередь Александр Лукашенко поблагодарил Нурсултана Назарбаева за оказанный прием и врученную ему награду.
+- Спасибо за уважение к белорусскому народу. Я понимаю, что это не только моя заслуга. Это Ваша любовь и отношение к моему народу. Президент Казахстана – очень достойный человек. Вы приняли мудрое решение. Уверен, что казахстанцы ценят стабильность, как и другие народы. Самое главное – труд. Будешь трудиться, будет и результат, - сказал Президент Республики Беларусь.
+Стационар.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4320,7 +5074,15 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Республики Беларусь А.Лукашенко. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана встретился с Президентом Республики Беларусь Александром Лукашенко.
+В ходе встречи Елбасы вручил высокому гостю орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана особо отметил роль и вклад Александра Лукашенко в развитие интеграционных процессов и становление Евразийского экономического союза.
+- Этот год ознаменован пятилетием создания здесь Евразийского экономического союза и 25-летием идеи евразийской интеграции, предложенной мною. И без вашей поддержки не было бы этой организации, - сказал Нурсултан Назарбаев.
+Елбасы подчеркнул, что всегда будет готов оказать поддержку народу Беларуси во главе с ее лидером А. Лукашенко.
+- Я всегда буду готов помочь и поддержать Вас по любому направлению. Вам удается держать Беларусь на высоком уровне. Также, пользуясь случаем, приглашаю Вас посетить красивейшие места Казахстана, - сказал Первый Президент Казахстана.
+В свою очередь Александр Лукашенко поблагодарил Нурсултана Назарбаева за оказанный прием и врученную ему награду.
+- Спасибо за уважение к белорусскому народу. Я понимаю, что это не только моя заслуга. Это Ваша любовь и отношение к моему народу. Президент Казахстана – очень достойный человек. Вы приняли мудрое решение. Уверен, что казахстанцы ценят стабильность, как и другие народы. Самое главное – труд. Будешь трудиться, будет и результат, - сказал Президент Республики Беларусь.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D57" s="2" t="n"/>
@@ -4368,7 +5130,15 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Республики Беларусь А.Лукашенко. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Крупный план.</t>
+          <t>Первый Президент Казахстана встретился с Президентом Республики Беларусь Александром Лукашенко.
+В ходе встречи Елбасы вручил высокому гостю орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана особо отметил роль и вклад Александра Лукашенко в развитие интеграционных процессов и становление Евразийского экономического союза.
+- Этот год ознаменован пятилетием создания здесь Евразийского экономического союза и 25-летием идеи евразийской интеграции, предложенной мною. И без вашей поддержки не было бы этой организации, - сказал Нурсултан Назарбаев.
+Елбасы подчеркнул, что всегда будет готов оказать поддержку народу Беларуси во главе с ее лидером А. Лукашенко.
+- Я всегда буду готов помочь и поддержать Вас по любому направлению. Вам удается держать Беларусь на высоком уровне. Также, пользуясь случаем, приглашаю Вас посетить красивейшие места Казахстана, - сказал Первый Президент Казахстана.
+В свою очередь Александр Лукашенко поблагодарил Нурсултана Назарбаева за оказанный прием и врученную ему награду.
+- Спасибо за уважение к белорусскому народу. Я понимаю, что это не только моя заслуга. Это Ваша любовь и отношение к моему народу. Президент Казахстана – очень достойный человек. Вы приняли мудрое решение. Уверен, что казахстанцы ценят стабильность, как и другие народы. Самое главное – труд. Будешь трудиться, будет и результат, - сказал Президент Республики Беларусь.
+Крупный план.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4416,7 +5186,13 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Премьер-министром Республики Армения Н.Пашиняном. Стационар.</t>
+          <t>Елбасы встретился с Премьер-Министром Республики Армения Николом Пашиняном.
+Поприветствовав высокого гостя, Нурсултан Назарбаев отметил важность развития и укрепления двусторонних торгово-экономических отношений.
+- Между Казахстаном и Арменией всегда были добрые отношения. Армянская диаспора в Казахстане является мостом между нашими странами, - сказал Елбасы.
+Никол Пашинян подчеркнул особый вклад Первого Президента Казахстана в развитие межгосударственных связей и интеграционных процессов на континенте.
+Премьер-Министр Армении выразил уверенность в дальнейшем углублении двустороннего экономического сотрудничества.
+- Я думаю, что у нас есть возможность поработать в сфере экономики. Главное, у правительств двух стран есть политическая воля развивать отношения, потому что наши народы связаны исторически, - сказал Н.Пашинян.
+Стационар.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -4462,7 +5238,13 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Премьер-министром Республики Армения Н.Пашиняном. Оператор: Х.О.</t>
+          <t>Елбасы встретился с Премьер-Министром Республики Армения Николом Пашиняном.
+Поприветствовав высокого гостя, Нурсултан Назарбаев отметил важность развития и укрепления двусторонних торгово-экономических отношений.
+- Между Казахстаном и Арменией всегда были добрые отношения. Армянская диаспора в Казахстане является мостом между нашими странами, - сказал Елбасы.
+Никол Пашинян подчеркнул особый вклад Первого Президента Казахстана в развитие межгосударственных связей и интеграционных процессов на континенте.
+Премьер-Министр Армении выразил уверенность в дальнейшем углублении двустороннего экономического сотрудничества.
+- Я думаю, что у нас есть возможность поработать в сфере экономики. Главное, у правительств двух стран есть политическая воля развивать отношения, потому что наши народы связаны исторически, - сказал Н.Пашинян.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D60" s="2" t="n"/>
@@ -4508,7 +5290,13 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Премьер-министром Республики Армения Н.Пашиняном. Крупный план.</t>
+          <t>Елбасы встретился с Премьер-Министром Республики Армения Николом Пашиняном.
+Поприветствовав высокого гостя, Нурсултан Назарбаев отметил важность развития и укрепления двусторонних торгово-экономических отношений.
+- Между Казахстаном и Арменией всегда были добрые отношения. Армянская диаспора в Казахстане является мостом между нашими странами, - сказал Елбасы.
+Никол Пашинян подчеркнул особый вклад Первого Президента Казахстана в развитие межгосударственных связей и интеграционных процессов на континенте.
+Премьер-Министр Армении выразил уверенность в дальнейшем углублении двустороннего экономического сотрудничества.
+- Я думаю, что у нас есть возможность поработать в сфере экономики. Главное, у правительств двух стран есть политическая воля развивать отношения, потому что наши народы связаны исторически, - сказал Н.Пашинян.
+Крупный план.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4554,7 +5342,13 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Российской Федерации В.Путиным. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Оператор: Маликов.</t>
+          <t>Нурсултан Назарбаев встретился с Президентом Российской Федерации Владимиром Путиным.
+В ходе встречи Елбасы лично вручил Владимиру Путину орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана отметил текущие результаты и перспективы дальнейшего развития Евразийского экономического союза.
+- Пять лет назад Вы, я и Александр Лукашенко создали этот союз. 25 лет назад в стенах МГУ мною была предложена эта идея, которую мы реализовали. Несмотря на непростые времена, взаимная торговля между нами растет. Увеличивается количество совместных предприятий. Считаю, что ЕАЭС должен идти по пути интеграции с ЕС, ШОС, АСЕАН и другими организациями. И нам необходимо работать над этим, - сказал Нурсултан Назарбаев.
+Владимир Путин поблагодарил Елбасы за врученную ему награду и выразил уверенность в дальнейшем укреплении всестороннего диалога.
+- Хотел бы поблагодарить Вас за награду и за то, что было сделано в деле интеграции, двусторонних отношениях и развитии стратегического взаимодействия России и Казахстана. В этом имеется огромная Ваша заслуга, - сказал Президент России.
+Оператор: Маликов.</t>
         </is>
       </c>
       <c r="D62" s="2" t="n"/>
@@ -4600,7 +5394,13 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Российской Федерации В.Путиным. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Оператор: Тлеспаев.</t>
+          <t>Нурсултан Назарбаев встретился с Президентом Российской Федерации Владимиром Путиным.
+В ходе встречи Елбасы лично вручил Владимиру Путину орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана отметил текущие результаты и перспективы дальнейшего развития Евразийского экономического союза.
+- Пять лет назад Вы, я и Александр Лукашенко создали этот союз. 25 лет назад в стенах МГУ мною была предложена эта идея, которую мы реализовали. Несмотря на непростые времена, взаимная торговля между нами растет. Увеличивается количество совместных предприятий. Считаю, что ЕАЭС должен идти по пути интеграции с ЕС, ШОС, АСЕАН и другими организациями. И нам необходимо работать над этим, - сказал Нурсултан Назарбаев.
+Владимир Путин поблагодарил Елбасы за врученную ему награду и выразил уверенность в дальнейшем укреплении всестороннего диалога.
+- Хотел бы поблагодарить Вас за награду и за то, что было сделано в деле интеграции, двусторонних отношениях и развитии стратегического взаимодействия России и Казахстана. В этом имеется огромная Ваша заслуга, - сказал Президент России.
+Оператор: Тлеспаев.</t>
         </is>
       </c>
       <c r="D63" s="2" t="n"/>
@@ -4646,7 +5446,13 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Российской Федерации В.Путиным. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Оператор: Х.О.</t>
+          <t>Нурсултан Назарбаев встретился с Президентом Российской Федерации Владимиром Путиным.
+В ходе встречи Елбасы лично вручил Владимиру Путину орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана отметил текущие результаты и перспективы дальнейшего развития Евразийского экономического союза.
+- Пять лет назад Вы, я и Александр Лукашенко создали этот союз. 25 лет назад в стенах МГУ мною была предложена эта идея, которую мы реализовали. Несмотря на непростые времена, взаимная торговля между нами растет. Увеличивается количество совместных предприятий. Считаю, что ЕАЭС должен идти по пути интеграции с ЕС, ШОС, АСЕАН и другими организациями. И нам необходимо работать над этим, - сказал Нурсултан Назарбаев.
+Владимир Путин поблагодарил Елбасы за врученную ему награду и выразил уверенность в дальнейшем укреплении всестороннего диалога.
+- Хотел бы поблагодарить Вас за награду и за то, что было сделано в деле интеграции, двусторонних отношениях и развитии стратегического взаимодействия России и Казахстана. В этом имеется огромная Ваша заслуга, - сказал Президент России.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D64" s="2" t="n"/>
@@ -4692,7 +5498,13 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Коллегии Евразийской экономической комиссии Т.Саркисяном. Стационар.</t>
+          <t>Первый Президент Казахстана принял председателя Коллегии Евразийской экономической комиссии Тиграна Саркисяна.
+В ходе встречи стороны обсудили текущее состояние и перспективы развития Евразийского экономического союза.
+Нурсултан Назарбаев подчеркнул, что многие страны и организации заинтересованы в налаживании сотрудничества с ЕАЭС и указал на необходимость расширения географии экономических партнеров союза.
+- Завтра здесь состоится юбилейное заседание ВЕЭС. Вы председательствуете в исполнительном органе союза, успешно справляясь с поставленными задачами. Нужно продолжать двигаться вперед, - сказал Первый Президент Казахстана.
+В свою очередь Тигран Саркисян отметил достижения в развитии экономического союза.
+- Благодарю Вас за возможность обсудить вопросы интеграции и практическую реализацию идеи, предложенную Вами 25 лет назад. Вот уже 5 лет мы реализуем этот проект. Мудрость, проявленная Вами четверть века назад, была жизненно необходима нашим странам, - сказал председатель Коллегии Евразийской экономической комиссии.
+Стационар.</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -4742,7 +5554,13 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Коллегии Евразийской экономической комиссии Т.Саркисяном. Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана принял председателя Коллегии Евразийской экономической комиссии Тиграна Саркисяна.
+В ходе встречи стороны обсудили текущее состояние и перспективы развития Евразийского экономического союза.
+Нурсултан Назарбаев подчеркнул, что многие страны и организации заинтересованы в налаживании сотрудничества с ЕАЭС и указал на необходимость расширения географии экономических партнеров союза.
+- Завтра здесь состоится юбилейное заседание ВЕЭС. Вы председательствуете в исполнительном органе союза, успешно справляясь с поставленными задачами. Нужно продолжать двигаться вперед, - сказал Первый Президент Казахстана.
+В свою очередь Тигран Саркисян отметил достижения в развитии экономического союза.
+- Благодарю Вас за возможность обсудить вопросы интеграции и практическую реализацию идеи, предложенную Вами 25 лет назад. Вот уже 5 лет мы реализуем этот проект. Мудрость, проявленная Вами четверть века назад, была жизненно необходима нашим странам, - сказал председатель Коллегии Евразийской экономической комиссии.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D66" s="4" t="n"/>
@@ -4792,7 +5610,13 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Кыргызской Республики С.Жээнбековым. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Стационар.</t>
+          <t>Елбасы встретился с Президентом Кыргызской Республики Сооронбаем Жээнбековым.
+В ходе встречи Нурсултан Назарбаев вручил Сооронбаю Жээнбекову орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана подчеркнул высокий уровень отношений между двумя братскими народами.
+- Мы – близкие друг к другу, братские народы. Я очень хорошо знаю и хорошо отношусь к Вашему народу. Уверен, что Казахстан и впредь будет поддерживать Вас, - сказал Елбасы.
+В свою очередь Сооронбай Жээнбеков поблагодарил Нурсултана Назарбаева за врученную высокую награду и отметил особую роль Елбасы в укреплении дружбы народов Центральной Азии.
+- Вы являетесь лидером Тюркского мира. Вы внесли свой значительный вклад в укрепление дружбы стран Центральной Азии. Для меня честь получить этот орден из рук Елбасы казахского народа. И я благодарен Вам за это, - отметил Президент Кыргызской Республики.
+Стационар.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4838,7 +5662,13 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Кыргызской Республики С.Жээнбековым. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Оператор: Х.О.</t>
+          <t>Елбасы встретился с Президентом Кыргызской Республики Сооронбаем Жээнбековым.
+В ходе встречи Нурсултан Назарбаев вручил Сооронбаю Жээнбекову орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана подчеркнул высокий уровень отношений между двумя братскими народами.
+- Мы – близкие друг к другу, братские народы. Я очень хорошо знаю и хорошо отношусь к Вашему народу. Уверен, что Казахстан и впредь будет поддерживать Вас, - сказал Елбасы.
+В свою очередь Сооронбай Жээнбеков поблагодарил Нурсултана Назарбаева за врученную высокую награду и отметил особую роль Елбасы в укреплении дружбы народов Центральной Азии.
+- Вы являетесь лидером Тюркского мира. Вы внесли свой значительный вклад в укрепление дружбы стран Центральной Азии. Для меня честь получить этот орден из рук Елбасы казахского народа. И я благодарен Вам за это, - отметил Президент Кыргызской Республики.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D68" s="2" t="n"/>
@@ -4884,7 +5714,13 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Президентом Кыргызской Республики С.Жээнбековым. Вручение ордена «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев». Крупный план.</t>
+          <t>Елбасы встретился с Президентом Кыргызской Республики Сооронбаем Жээнбековым.
+В ходе встречи Нурсултан Назарбаев вручил Сооронбаю Жээнбекову орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
+Первый Президент Казахстана подчеркнул высокий уровень отношений между двумя братскими народами.
+- Мы – близкие друг к другу, братские народы. Я очень хорошо знаю и хорошо отношусь к Вашему народу. Уверен, что Казахстан и впредь будет поддерживать Вас, - сказал Елбасы.
+В свою очередь Сооронбай Жээнбеков поблагодарил Нурсултана Назарбаева за врученную высокую награду и отметил особую роль Елбасы в укреплении дружбы народов Центральной Азии.
+- Вы являетесь лидером Тюркского мира. Вы внесли свой значительный вклад в укрепление дружбы стран Центральной Азии. Для меня честь получить этот орден из рук Елбасы казахского народа. И я благодарен Вам за это, - отметил Президент Кыргызской Республики.
+Крупный план.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4930,7 +5766,21 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Вручение дипломов выпускникам Назарбаев Университета и открытие нового Атлетического центра НУ с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета.
+Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
+- Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана отметил результаты и достижения учащихся Университета в научно-исследовательской деятельности.
+- В прошлом году в Бостоне студенческая команда Школы наук и технологий получила золотую медаль на Международном конкурсе генно-инженерных машин. В качестве проекта по коммерциализации можно отметить проект EGIStic, - сказал Елбасы.
+Нурсултан Назарбаев указал, что сегодня высококвалифицированные кадры Университета вносят значительный вклад в технологическое развитие Казахстана.
+- 2019 год объявлен Годом молодежи. Образование молодежи является ключевым фактором конкурентоспособности нашей страны в современном мире. Именно от вас, ваших знаний, энергии и патриотизма зависит будущее Казахстана. Мы принимаем все меры для того, чтобы вы смогли в полной мере реализовать свой потенциал и возможности, - обратился к выпускникам Первый Президент Казахстана.
+Елбасы подчеркнул, что брэнд «NU – Назарбаев Университет» стал широко узнаваем не только в мировом академическом сообществе, но и в сферах госуправления, бизнеса, медицины, инноваций, IT-технологий.
+- Проект стал прорывным и лидером в своей области не только в Казахстане, но и на всем постсоветском пространстве. За небольшой срок университет вырос в элитное учебное заведение по подготовке профессиональных кадров, развитию отечественных научных исследований и разработок. Главным активом университета, конечно же, является его интеллектуальный потенциал – преподаватели, студенты, управленческий персонал, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана призвал выпускников принимать активное участие в жизни страны и общества.
+- Вы должны быть не только высококлассными специалистами, но и активно участвовать в общественной жизни, проявляя свою гражданскую ответственность. Какой бы путь вы ни избрали – продолжить дальнейшее обучение, трудиться на благо страны, представлять Казахстан за рубежом или начать свое дело, желаю вам светлой дороги и реализации намеченных планов, - заключил Елбасы.
+Елбасы принял участие в церемонии открытия нового Атлетического центра Назарбаев Университета.
+Первый Президент Казахстана посетил новое многофункциональное спортивное сооружение Назарбаев Университета.
+В Атлетическом центре учебного заведения предусмотрена все необходимая спортивная инфраструктура, в том числе олимпийский бассейн, паркетная арена на 660 зрителей, тренажерный зал и зал единоборств. Объект оснащен передовыми технологиями спортивной индустрии.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D70" s="4" t="n"/>
@@ -4990,7 +5840,10 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Открытие нового Атлетического центра Назарбаев Университета с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Осмотр спортивного комплекса. Оператор: Ахметов.</t>
+          <t>Елбасы принял участие в церемонии открытия нового Атлетического центра Назарбаев Университета.
+Первый Президент Казахстана посетил новое многофункциональное спортивное сооружение Назарбаев Университета.
+В Атлетическом центре учебного заведения предусмотрена все необходимая спортивная инфраструктура, в том числе олимпийский бассейн, паркетная арена на 660 зрителей, тренажерный зал и зал единоборств. Объект оснащен передовыми технологиями спортивной индустрии.
+Оператор: Ахметов.</t>
         </is>
       </c>
       <c r="D71" s="2" t="n"/>
@@ -5034,7 +5887,10 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Открытие нового Атлетического центра Назарбаев Университета с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Осмотр спортивного комплекса. Оператор: Джаватаров.</t>
+          <t>Елбасы принял участие в церемонии открытия нового Атлетического центра Назарбаев Университета.
+Первый Президент Казахстана посетил новое многофункциональное спортивное сооружение Назарбаев Университета.
+В Атлетическом центре учебного заведения предусмотрена все необходимая спортивная инфраструктура, в том числе олимпийский бассейн, паркетная арена на 660 зрителей, тренажерный зал и зал единоборств. Объект оснащен передовыми технологиями спортивной индустрии.
+Оператор: Джаватаров.</t>
         </is>
       </c>
       <c r="D72" s="2" t="n"/>
@@ -5078,7 +5934,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Абилов.</t>
+          <t>Первый Президент Казахстана встретился с Председателем Европейского совета Дональдом Туском.
+Поприветствовав гостя, Нурсултан Назарбаев отметил высокий уровень развития взаимоотношений между Казахстаном и Европейским союзом.
+- Мы встречались с вами несколько раз. В период вашего председательства было заключено Соглашение о расширенном партнерстве и сотрудничестве между Европейским Союзом и Республикой Казахстан. В этом году ожидается завершение его ратификации. В целом, у нас хорошие перспективы, - сказал Елбасы.
+В свою очередь Дональд Туск подчеркнул особую роль Нурсултана Назарбаева в становлении и развитии Казахстана, укреплении международного авторитета страны.
+- Ваша роль в регионе особая и важная. Я очень рад встретиться с Вами. Мы высоко ценим Ваш разумный и ответственный подход в транзите власти. Думаю, что вся Европа была впечатлена этим шагом, - отметил Председатель Европейского совета.
+Оператор: Абилов.</t>
         </is>
       </c>
       <c r="D73" s="2" t="n"/>
@@ -5124,7 +5985,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Н.Кульманов.</t>
+          <t>Первый Президент Казахстана встретился с Председателем Европейского совета Дональдом Туском.
+Поприветствовав гостя, Нурсултан Назарбаев отметил высокий уровень развития взаимоотношений между Казахстаном и Европейским союзом.
+- Мы встречались с вами несколько раз. В период вашего председательства было заключено Соглашение о расширенном партнерстве и сотрудничестве между Европейским Союзом и Республикой Казахстан. В этом году ожидается завершение его ратификации. В целом, у нас хорошие перспективы, - сказал Елбасы.
+В свою очередь Дональд Туск подчеркнул особую роль Нурсултана Назарбаева в становлении и развитии Казахстана, укреплении международного авторитета страны.
+- Ваша роль в регионе особая и важная. Я очень рад встретиться с Вами. Мы высоко ценим Ваш разумный и ответственный подход в транзите власти. Думаю, что вся Европа была впечатлена этим шагом, - отметил Председатель Европейского совета.
+Оператор: Н.Кульманов.</t>
         </is>
       </c>
       <c r="D74" s="2" t="n"/>
@@ -5170,7 +6036,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Проходка. Оператор: Абилов.</t>
+          <t>Первый Президент Казахстана встретился с Председателем Европейского совета Дональдом Туском.
+Поприветствовав гостя, Нурсултан Назарбаев отметил высокий уровень развития взаимоотношений между Казахстаном и Европейским союзом.
+- Мы встречались с вами несколько раз. В период вашего председательства было заключено Соглашение о расширенном партнерстве и сотрудничестве между Европейским Союзом и Республикой Казахстан. В этом году ожидается завершение его ратификации. В целом, у нас хорошие перспективы, - сказал Елбасы.
+В свою очередь Дональд Туск подчеркнул особую роль Нурсултана Назарбаева в становлении и развитии Казахстана, укреплении международного авторитета страны.
+- Ваша роль в регионе особая и важная. Я очень рад встретиться с Вами. Мы высоко ценим Ваш разумный и ответственный подход в транзите власти. Думаю, что вся Европа была впечатлена этим шагом, - отметил Председатель Европейского совета.
+Проходка. Оператор: Абилов.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5220,7 +6091,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Встреча Первого Президента РК – Елбасы Н.А.Назарбаева с Председателем Европейского совета Д.Туском. Оператор: Х.О.</t>
+          <t>Первый Президент Казахстана встретился с Председателем Европейского совета Дональдом Туском.
+Поприветствовав гостя, Нурсултан Назарбаев отметил высокий уровень развития взаимоотношений между Казахстаном и Европейским союзом.
+- Мы встречались с вами несколько раз. В период вашего председательства было заключено Соглашение о расширенном партнерстве и сотрудничестве между Европейским Союзом и Республикой Казахстан. В этом году ожидается завершение его ратификации. В целом, у нас хорошие перспективы, - сказал Елбасы.
+В свою очередь Дональд Туск подчеркнул особую роль Нурсултана Назарбаева в становлении и развитии Казахстана, укреплении международного авторитета страны.
+- Ваша роль в регионе особая и важная. Я очень рад встретиться с Вами. Мы высоко ценим Ваш разумный и ответственный подход в транзите власти. Думаю, что вся Европа была впечатлена этим шагом, - отметил Председатель Европейского совета.
+Оператор: Х.О.</t>
         </is>
       </c>
       <c r="D76" s="2" t="n"/>
@@ -5266,7 +6142,18 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. Крупный план.</t>
+          <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета.
+Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
+- Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана отметил результаты и достижения учащихся Университета в научно-исследовательской деятельности.
+- В прошлом году в Бостоне студенческая команда Школы наук и технологий получила золотую медаль на Международном конкурсе генно-инженерных машин. В качестве проекта по коммерциализации можно отметить проект EGIStic, - сказал Елбасы.
+Нурсултан Назарбаев указал, что сегодня высококвалифицированные кадры Университета вносят значительный вклад в технологическое развитие Казахстана.
+- 2019 год объявлен Годом молодежи. Образование молодежи является ключевым фактором конкурентоспособности нашей страны в современном мире. Именно от вас, ваших знаний, энергии и патриотизма зависит будущее Казахстана. Мы принимаем все меры для того, чтобы вы смогли в полной мере реализовать свой потенциал и возможности, - обратился к выпускникам Первый Президент Казахстана.
+Елбасы подчеркнул, что брэнд «NU – Назарбаев Университет» стал широко узнаваем не только в мировом академическом сообществе, но и в сферах госуправления, бизнеса, медицины, инноваций, IT-технологий.
+- Проект стал прорывным и лидером в своей области не только в Казахстане, но и на всем постсоветском пространстве. За небольшой срок университет вырос в элитное учебное заведение по подготовке профессиональных кадров, развитию отечественных научных исследований и разработок. Главным активом университета, конечно же, является его интеллектуальный потенциал – преподаватели, студенты, управленческий персонал, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана призвал выпускников принимать активное участие в жизни страны и общества.
+- Вы должны быть не только высококлассными специалистами, но и активно участвовать в общественной жизни, проявляя свою гражданскую ответственность. Какой бы путь вы ни избрали – продолжить дальнейшее обучение, трудиться на благо страны, представлять Казахстан за рубежом или начать свое дело, желаю вам светлой дороги и реализации намеченных планов, - заключил Елбасы.
+Крупный план.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -5318,7 +6205,18 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. PGM (программный микс).</t>
+          <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета.
+Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
+- Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана отметил результаты и достижения учащихся Университета в научно-исследовательской деятельности.
+- В прошлом году в Бостоне студенческая команда Школы наук и технологий получила золотую медаль на Международном конкурсе генно-инженерных машин. В качестве проекта по коммерциализации можно отметить проект EGIStic, - сказал Елбасы.
+Нурсултан Назарбаев указал, что сегодня высококвалифицированные кадры Университета вносят значительный вклад в технологическое развитие Казахстана.
+- 2019 год объявлен Годом молодежи. Образование молодежи является ключевым фактором конкурентоспособности нашей страны в современном мире. Именно от вас, ваших знаний, энергии и патриотизма зависит будущее Казахстана. Мы принимаем все меры для того, чтобы вы смогли в полной мере реализовать свой потенциал и возможности, - обратился к выпускникам Первый Президент Казахстана.
+Елбасы подчеркнул, что брэнд «NU – Назарбаев Университет» стал широко узнаваем не только в мировом академическом сообществе, но и в сферах госуправления, бизнеса, медицины, инноваций, IT-технологий.
+- Проект стал прорывным и лидером в своей области не только в Казахстане, но и на всем постсоветском пространстве. За небольшой срок университет вырос в элитное учебное заведение по подготовке профессиональных кадров, развитию отечественных научных исследований и разработок. Главным активом университета, конечно же, является его интеллектуальный потенциал – преподаватели, студенты, управленческий персонал, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана призвал выпускников принимать активное участие в жизни страны и общества.
+- Вы должны быть не только высококлассными специалистами, но и активно участвовать в общественной жизни, проявляя свою гражданскую ответственность. Какой бы путь вы ни избрали – продолжить дальнейшее обучение, трудиться на благо страны, представлять Казахстан за рубежом или начать свое дело, желаю вам светлой дороги и реализации намеченных планов, - заключил Елбасы.
+PGM (программный микс).</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -5370,7 +6268,18 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. Крупный план; без Елбасы.</t>
+          <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета.
+Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
+- Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана отметил результаты и достижения учащихся Университета в научно-исследовательской деятельности.
+- В прошлом году в Бостоне студенческая команда Школы наук и технологий получила золотую медаль на Международном конкурсе генно-инженерных машин. В качестве проекта по коммерциализации можно отметить проект EGIStic, - сказал Елбасы.
+Нурсултан Назарбаев указал, что сегодня высококвалифицированные кадры Университета вносят значительный вклад в технологическое развитие Казахстана.
+- 2019 год объявлен Годом молодежи. Образование молодежи является ключевым фактором конкурентоспособности нашей страны в современном мире. Именно от вас, ваших знаний, энергии и патриотизма зависит будущее Казахстана. Мы принимаем все меры для того, чтобы вы смогли в полной мере реализовать свой потенциал и возможности, - обратился к выпускникам Первый Президент Казахстана.
+Елбасы подчеркнул, что брэнд «NU – Назарбаев Университет» стал широко узнаваем не только в мировом академическом сообществе, но и в сферах госуправления, бизнеса, медицины, инноваций, IT-технологий.
+- Проект стал прорывным и лидером в своей области не только в Казахстане, но и на всем постсоветском пространстве. За небольшой срок университет вырос в элитное учебное заведение по подготовке профессиональных кадров, развитию отечественных научных исследований и разработок. Главным активом университета, конечно же, является его интеллектуальный потенциал – преподаватели, студенты, управленческий персонал, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана призвал выпускников принимать активное участие в жизни страны и общества.
+- Вы должны быть не только высококлассными специалистами, но и активно участвовать в общественной жизни, проявляя свою гражданскую ответственность. Какой бы путь вы ни избрали – продолжить дальнейшее обучение, трудиться на благо страны, представлять Казахстан за рубежом или начать свое дело, желаю вам светлой дороги и реализации намеченных планов, - заключил Елбасы.
+Крупный план; без Елбасы.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -5422,7 +6331,18 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Церемония вручения дипломов выпускникам Назарбаев Университета. Первый Президент РК – Елбасы Н.А.Назарбаев вручил дипломы с отличием, выступление перед выпускниками. PGM (программный микс); без Елбасы.</t>
+          <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета.
+Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
+- Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана отметил результаты и достижения учащихся Университета в научно-исследовательской деятельности.
+- В прошлом году в Бостоне студенческая команда Школы наук и технологий получила золотую медаль на Международном конкурсе генно-инженерных машин. В качестве проекта по коммерциализации можно отметить проект EGIStic, - сказал Елбасы.
+Нурсултан Назарбаев указал, что сегодня высококвалифицированные кадры Университета вносят значительный вклад в технологическое развитие Казахстана.
+- 2019 год объявлен Годом молодежи. Образование молодежи является ключевым фактором конкурентоспособности нашей страны в современном мире. Именно от вас, ваших знаний, энергии и патриотизма зависит будущее Казахстана. Мы принимаем все меры для того, чтобы вы смогли в полной мере реализовать свой потенциал и возможности, - обратился к выпускникам Первый Президент Казахстана.
+Елбасы подчеркнул, что брэнд «NU – Назарбаев Университет» стал широко узнаваем не только в мировом академическом сообществе, но и в сферах госуправления, бизнеса, медицины, инноваций, IT-технологий.
+- Проект стал прорывным и лидером в своей области не только в Казахстане, но и на всем постсоветском пространстве. За небольшой срок университет вырос в элитное учебное заведение по подготовке профессиональных кадров, развитию отечественных научных исследований и разработок. Главным активом университета, конечно же, является его интеллектуальный потенциал – преподаватели, студенты, управленческий персонал, - сказал Нурсултан Назарбаев.
+Первый Президент Казахстана призвал выпускников принимать активное участие в жизни страны и общества.
+- Вы должны быть не только высококлассными специалистами, но и активно участвовать в общественной жизни, проявляя свою гражданскую ответственность. Какой бы путь вы ни избрали – продолжить дальнейшее обучение, трудиться на благо страны, представлять Казахстан за рубежом или начать свое дело, желаю вам светлой дороги и реализации намеченных планов, - заключил Елбасы.
+PGM (программный микс); без Елбасы.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -5474,7 +6394,16 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Международная научно-практическая конференция «30 лет лидерства» с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Выступление Елбасы. г. Алматы (по имени файла). Крупный план.</t>
+          <t>Первый Президент Казахстана принял участие в Международной научно-практической конференции «30 лет лидерства».
+Выступая перед участниками конференции, Елбасы отметил, что вся его деятельность на посту первого руководителя страны была посвящена развитию Казахстана.
+Нурсултан Назарбаев рассказал о трудностях на пути строительства и становления Независимости. В частности, Первый Президент Казахстана напомнил о ситуации в стране в начале 1990-х годов, связанной с развалом национальной экономики и рисками возникновения межэтнических конфликтов.
+- Казахстан стоял на пороге демографической катастрофы. Согласно переписи населения 1989 года, коренное население – казахи – составляли 39% или немногим более 6,5 миллионов человек. Тяжелейшая экономическая ситуация того периода вызвала масштабную эмиграцию населения из Казахстана. Средняя продолжительность жизни в те годы уменьшилась на пять лет, резко упала рождаемость, - сказал Елбасы.
+Нурсултан Назарбаев также подчеркнул, что в начале пути Казахстан был в числе самых технологически отсталых республик, в которой наблюдалась несбалансированность транспортных маршрутов и были серьезные проблемы с экологией.
+Первый Президент Казахстана остановился на результатах осуществления принятых в стране программ и стратегий развития, направленных на решение острых социально-экономических проблем.
+В своем выступлении Елбасы указал на несколько стратегических вызовов, влияющих на мировое развитие. Среди них, динамичная и непрерывная технологическая волна, смена экономической парадигмы, вызванная очередной индустриальной революцией, изменения в мировом геополитическом раскладе, столкновение разных глобальных реалий.
+- Народ и Президент должны быть всегда вместе. Только так мы достигали успеха. Я обращаюсь к нашему старшему поколению. Ваша мудрость должна помочь молодым людям идти по верному пути, любить Родину, крепить государство, защищать Независимость и работать ради будущего. Я обращаюсь к среднему поколению. Ваш приобретенный опыт – это неоценимый капитал, который поможет всем нам пройти сквозь невзгоды. И наконец, я обращаюсь к нашей молодежи. Чтобы лучше жить есть лишь один путь – трудиться. Дальнейший путь страны определять вам, - сказал Елбасы.
+С полным текстом выступления Первого Президента Казахстан можно ознакомиться здесь.
+Крупный план.</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -5528,7 +6457,16 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Международная научно-практическая конференция «30 лет лидерства» с участием Первого Президента РК – Елбасы Н.А.Назарбаева. Выступление Елбасы. г. Алматы (по имени файла). PGM (программный микс).</t>
+          <t>Первый Президент Казахстана принял участие в Международной научно-практической конференции «30 лет лидерства».
+Выступая перед участниками конференции, Елбасы отметил, что вся его деятельность на посту первого руководителя страны была посвящена развитию Казахстана.
+Нурсултан Назарбаев рассказал о трудностях на пути строительства и становления Независимости. В частности, Первый Президент Казахстана напомнил о ситуации в стране в начале 1990-х годов, связанной с развалом национальной экономики и рисками возникновения межэтнических конфликтов.
+- Казахстан стоял на пороге демографической катастрофы. Согласно переписи населения 1989 года, коренное население – казахи – составляли 39% или немногим более 6,5 миллионов человек. Тяжелейшая экономическая ситуация того периода вызвала масштабную эмиграцию населения из Казахстана. Средняя продолжительность жизни в те годы уменьшилась на пять лет, резко упала рождаемость, - сказал Елбасы.
+Нурсултан Назарбаев также подчеркнул, что в начале пути Казахстан был в числе самых технологически отсталых республик, в которой наблюдалась несбалансированность транспортных маршрутов и были серьезные проблемы с экологией.
+Первый Президент Казахстана остановился на результатах осуществления принятых в стране программ и стратегий развития, направленных на решение острых социально-экономических проблем.
+В своем выступлении Елбасы указал на несколько стратегических вызовов, влияющих на мировое развитие. Среди них, динамичная и непрерывная технологическая волна, смена экономической парадигмы, вызванная очередной индустриальной революцией, изменения в мировом геополитическом раскладе, столкновение разных глобальных реалий.
+- Народ и Президент должны быть всегда вместе. Только так мы достигали успеха. Я обращаюсь к нашему старшему поколению. Ваша мудрость должна помочь молодым людям идти по верному пути, любить Родину, крепить государство, защищать Независимость и работать ради будущего. Я обращаюсь к среднему поколению. Ваш приобретенный опыт – это неоценимый капитал, который поможет всем нам пройти сквозь невзгоды. И наконец, я обращаюсь к нашей молодежи. Чтобы лучше жить есть лишь один путь – трудиться. Дальнейший путь страны определять вам, - сказал Елбасы.
+С полным текстом выступления Первого Президента Казахстан можно ознакомиться здесь.
+PGM (программный микс).</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">

--- a/output/Каталог_2019_май.xlsx
+++ b/output/Каталог_2019_май.xlsx
@@ -6520,7 +6520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6559,7 +6559,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>43583</v>
+        <v>43586</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -6568,112 +6568,15 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Елбасы Нурсултан Назарбаев встретился с известным актером Джеки Чаном</t>
+          <t>Елбасы Нурсултан Назарбаев посетил народные гуляния по случаю празднования Дня единства народа Казахстана</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://nazarbayev.kz/ru/news/2019-04/elbasy-nursultan-nazarbaev-vstretilsya-s-izvestnym-akterom-dzheki-chanom</t>
+          <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-nursultan-nazarbaev-posetil-narodnye-gulyaniya-po-sluchayu-prazdnovaniya-dnya</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Во встрече также приняли участие соратники и члены творческой команды выдающегося китайского актера.
-В ходе беседы Первый Президент Казахстана отметил значимую роль Джеки Чана в мировом кинематографе.
-– Я очень рад встретится с такой знаменитостью. Вы популярны во все мире, – сказал Елбасы.
-В свою очередь китайский актер рассказал о творческих планах на ближайший период и поделился своим видением реализации совместных проектов в сфере киноиндустрии.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>43583</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>СОБЫТИЯ</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Нурсултан Назарбаев награжден Орденом Дружбы Китайской Народной Республики</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>https://nazarbayev.kz/ru/news/2019-04/nursultan-nazarbaev-nagrazhden-ordenom-druzhby-kitayskoy-narodnoy-respubliki</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>В Доме народных собраний КНР состоялась официальная церемония награждения Первого Президента Казахстана Орденом Дружбы за его вклад в продвижение добрососедских двусторонних отношений и развитие всестороннего стратегического партнерства между государствами.
-- Хочу отметить, что с первых дней установления дипломатических связей в 1992 году я работаю над развитием и укреплением сотрудничества независимого Казахстана с Китаем. Я очень рад, что нам удалось выстроить доверительные и добрососедские отношения с Вашим государством. Наше сотрудничество является показательным. Наши страны совместно вносят весомый вклад в обеспечение мира, стабильности и устойчивого развития в регионе и в глобальном масштабе, - сказал Елбасы в ходе своего выступления.
-Нурсултан Назарбаев остановился на процессе продвижения инициативы «Один пояс, один путь», подчеркнув ее значимость в деле устойчивого глобального развития.
-- За относительно небольшой период времени проект «Один пояс, один путь» вошел в перечень так называемых глобальных «историй успеха». Объединительная идея развития господина Си Цзиньпина стала эффективным ответом на современные вызовы. Предложенная Китаем новая платформа международного сотрудничества играет все более важную политическую, экономическую и культурную роль в развитии многих стран Азии, Европы и Африки, - сказал Первый Президент Казахстана.
-Елбасы отметил, что Второй Форум международного сотрудничества «Один путь, один пояс» стал важной площадкой по вопросам развития взаимовыгодной кооперации.
-Первый Президент Казахстана также подчеркнул результаты совместной работы двух стран по реализации экономических проектов.
-- Пользуясь случаем, поздравляю Вас, Председатель Си Цзиньпин, китайское правительство и народ с успешным проведением Форума «Один пояс, один путь». Уверен, что под Вашим личным руководством и Коммунистической партии Китая будут реализованы все поставленные цели и задачи по построению социализма с китайской спецификой «новой эпохи» и воплощению в жизнь «китайской мечты», - сказал Нурсултан Назарбаев.
-Первый Президент Казахстана еще раз поблагодарил руководство и народ Китая за награду и оказанное гостеприимство.
-- Надеюсь на дальнейшее углубление казахстанско-китайского всестороннего стратегического партнерства во имя процветания и благополучия наших народов. Желаю Вам дальнейших успехов в ответственной государственной деятельности, а дружественному народу Китая – мира и процветания, - заключил Елбасы Нурсултан Назарбаев.
-Председатель КНР Си Цзиньпин, отмечая заслуги Первого Президента Казахстана в укреплении двусторонних отношений, особо акцентировал внимание на вкладе Елбасы в развитие международной кооперации.
-- Сегодня мы проводим торжественную церемонию вручения давнему и большому другу китайского народа Первому Президенту Казахстана Нурсултану Назарбаеву высшей внешней награды КНР – Ордена Дружбы. Президент Назарбаев пользуется авторитетом во всем мире, является основателем казахстанско-китайского всестороннего стратегического партнерства и всегда продвигает его развитие вперед. Казахстан – страна-основатель ШОС и инициатор СВМДА. Президент Назарбаев своей дальновидностью продвигает развитие этих организаций, вносит весомый вклад в поддержание мира, стабильности на региональном и глобальном уровне, - сказал Си Цзиньпин.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>43584</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>СОБЫТИЯ</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>XXVII сессия Ассамблеи народа Казахстана под председательством Первого Президента Республики Казахстан – Елбасы Нурсултана Назарбаева</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>https://nazarbayev.kz/ru/news/2019-04/xxvii-sessiya-assamblei-naroda-kazakhstana-pod-predsedatelstvom-pervogo-prezidenta</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Председатель Ассамблеи народа Казахстана Нурсултан Назарбаев поздравил участников с началом работы сессии, подчеркнув важную роль АНК в деле сохранения мира и стабильности в стране.
-- Глобальный мир переживает мощную трансформацию. Мы все понимаем, что живем уже в совершенно новую историческую эпоху. Кардинально изменились экономика, жизнь общества, технологии. Мы принимаем эти новшества, многому учимся, многое умеем. Но в этом мире переменных величин есть одна постоянная, фундаментальная ценность – единство общества и межнациональное согласие, - сказал Елбасы.
-Нурсултан Назарбаев акцентировал внимание на том, что за годы Независимости народ Казахстана опроверг все деструктивные прогнозы относительно будущего развития межэтнических отношений в стране.
-- Мы создали крепкое государство с динамичной экономикой. Вместе обошли все ловушки истории, а благодаря прагматичной и взвешенной внешней политике заработали высокий международный авторитет. Модель межэтнических отношений в нашей стране сбалансирована, эффективна и испытана временем. Она служит примером для всех, - отметил Елбасы.
-В ходе сессии Елбасы поручил обеспечить слаженную и эффективную работу всех механизмов, направленных на сохранение стабильности в казахстанском обществе.
-Первый Президент Казахстана указал на необходимость активизации работы института медиации и общественных советов при государственных органах. Елбасы призвал расширить экономическое сотрудничество с зарубежными инвесторами по линии Ассоциации предпринимателей Ассамблеи, активно использовать потенциал депутатского корпуса АНК.
-В своем выступлении Нурсултан Назарбаев поздравил мусульман с предстоящим началом благословенного месяца Рамазан и христиан с завершением Великого поста и праздником Пасхи.
-- Хотел бы выразить благодарность нашему народу, в том числе всем членам АНК, за поддержку и понимание. Президентские выборы назначены на 9 июня. На внеочередном ХІХ съезде партии «Nur Otan» была выдвинута кандидатура Касым-Жомарта Кемелевича Токаева. Он опытный государственный деятель, настоящий патриот Казахстана, который достоин руководить страной. Призываю всех казахстанцев, членов Ассамблеи принять активное участие в предстоящих выборах и снова показать наше единство. Желаю всем казахстанцам чистого неба над головой, мира, добра и благополучия каждой семье, - сказал Елбасы.
-В ходе сессии новыми заместителями Председателя АНК были назначены Юсуп Келигов и Шерзод Пулатов.
-С полным текстом выступления можно ознакомиться здесь.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>43586</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>СОБЫТИЯ</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Елбасы Нурсултан Назарбаев посетил народные гуляния по случаю празднования Дня единства народа Казахстана</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-nursultan-nazarbaev-posetil-narodnye-gulyaniya-po-sluchayu-prazdnovaniya-dnya</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Выступая перед жителями и гостями столицы, Первый Президент Нурсултан Назарбаев поздравил всех казахстанцев с праздником единства народа Казахстана.
 - Благодаря единству наши предки преодолели все трудности, сохранив для нас Великую степь. Мы вместе создали независимый Казахстан, тем самым исполнив мечту наших прадедов, - сказал Нурсултан Назарбаев.
@@ -6684,9 +6587,87 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>43588</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>СОБЫТИЯ</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Елбасы Нурсултан Назарбаев принял академика Серика Кирабаева</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-nursultan-nazarbaev-prinyal-akademika-serika-kirabaeva</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Первый Президент Казахстана и известный ученый-литературовед обсудили текущее состояние и перспективы развития отечественной литературы. Особое внимание было уделено актуальным вопросам образования и науки.
+В ходе беседы С. Кирабаев выразил поддержку решению Нурсултана Назарбаева о сложении полномочий Президента и пожелал Елбасы успехов в дальнейшей деятельности.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>43588</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>СОБЫТИЯ</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Первый Президент Казахстана принял академика Уалихана Калижанова</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-prinyal-akademika-ualikhana-kalizhanova</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Нурсултану Назарбаеву была представлена информация о текущей научно-исследовательской деятельности Института литературы и искусства им. М.О.Ауэзова.
+Елбасы отметил вклад академика в развитие отечественной литературы и искусства, и поблагодарил за плодотворную работу во имя процветания Казахстана.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>43591</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ТЕЛЕГРАММЫ И ПИСЬМА</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Телеграмма соболезнования Первого Президента Казахстана Нурсултана Назарбаева Президенту Российской Федерации Владимиру Путину</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://nazarbayev.kz/ru/news/2019-05/telegramma-soboleznovaniya-pervogo-prezidenta-kazakhstana-nursultana-nazarbaeva</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Елбасы Нурсултан Назарбаев с глубоким прискорбием воспринял известие о трагической гибели людей в результате возгорания пассажирского самолета в аэропорту Шереметьево.
+«Выражаю искренние соболезнования родным и близким погибших, а также всему российскому народу. Пострадавшим желаю скорейшего выздоровления и возвращения к своим семьям», - говорится в телеграмме.</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>43588</v>
+        <v>43594</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -6695,93 +6676,15 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Елбасы Нурсултан Назарбаев принял академика Серика Кирабаева</t>
+          <t>Первый Президент Казахстана посетил военный парад по случаю 74-й годовщины Победы в Великой Отечественной войне</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-nursultan-nazarbaev-prinyal-akademika-serika-kirabaeva</t>
+          <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-posetil-voennyy-parad-po-sluchayu-74-y-godovschiny-pobedy</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Первый Президент Казахстана и известный ученый-литературовед обсудили текущее состояние и перспективы развития отечественной литературы. Особое внимание было уделено актуальным вопросам образования и науки.
-В ходе беседы С. Кирабаев выразил поддержку решению Нурсултана Назарбаева о сложении полномочий Президента и пожелал Елбасы успехов в дальнейшей деятельности.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>43588</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>СОБЫТИЯ</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Первый Президент Казахстана принял академика Уалихана Калижанова</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-prinyal-akademika-ualikhana-kalizhanova</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Нурсултану Назарбаеву была представлена информация о текущей научно-исследовательской деятельности Института литературы и искусства им. М.О.Ауэзова.
-Елбасы отметил вклад академика в развитие отечественной литературы и искусства, и поблагодарил за плодотворную работу во имя процветания Казахстана.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>43591</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>ТЕЛЕГРАММЫ И ПИСЬМА</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Телеграмма соболезнования Первого Президента Казахстана Нурсултана Назарбаева Президенту Российской Федерации Владимиру Путину</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>https://nazarbayev.kz/ru/news/2019-05/telegramma-soboleznovaniya-pervogo-prezidenta-kazakhstana-nursultana-nazarbaeva</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Елбасы Нурсултан Назарбаев с глубоким прискорбием воспринял известие о трагической гибели людей в результате возгорания пассажирского самолета в аэропорту Шереметьево.
-«Выражаю искренние соболезнования родным и близким погибших, а также всему российскому народу. Пострадавшим желаю скорейшего выздоровления и возвращения к своим семьям», - говорится в телеграмме.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>43594</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>СОБЫТИЯ</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Первый Президент Казахстана посетил военный парад по случаю 74-й годовщины Победы в Великой Отечественной войне</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-posetil-voennyy-parad-po-sluchayu-74-y-godovschiny-pobedy</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Нурсултан Назарбаев стал почетным гостем военного парада по случаю 74-й годовщины Победы, который прошел на Красной площади в Москве.
 Перед началом парада Елбасы и Президент России Владимир Путин поприветствовали ветеранов Великой Отечественной войны.
@@ -6789,26 +6692,26 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
+    <row r="7">
+      <c r="A7" s="3" t="n">
         <v>43598</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Елбасы Нурсултан Назарбаев посетил Международный центр зеленых технологий и инвестиционных проектов</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-nursultan-nazarbaev-posetil-mezhdunarodnyy-centr-zelenykh-tekhnologiy-i</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>В ходе посещения Первому Президенту Казахстана была представлена информация по основным направлениям работы Центра в сфере развития зеленой экономики и обеспечения безопасности окружающей среды.
 Елбасы Н. Назарбаеву был презентован прототип цифровой площадки, объединяющей информацию о потенциале ветровых, солнечных, гидро- и геотермальных ресурсов, расположении полигонов ТБО и биомассы.
@@ -6819,26 +6722,26 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
+    <row r="8">
+      <c r="A8" s="3" t="n">
         <v>43598</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Нурсултан Назарбаев встретился с Чрезвычайным и Полномочным Послом Соединенных Штатов Америки в Казахстане Уильямом Мозером</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/nursultan-nazarbaev-vstretilsya-s-chrezvychaynym-i-polnomochnym-poslom-soedinennykh</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Елбасы поздравил У. Мозера с началом дипломатической миссии в Казахстане, пожелав успехов и достижений на ответственном посту.
 - За все эти годы мы построили с США отношения, основанные на взаимопонимании и дружбе. В Казахстан пришли большие инвестиции из США. Работают 420 совместных предприятий. Мой визит в Вашингтон в прошлом году, в рамках которого состоялись переговоры с Президентом Трампом и встречи с бизнесменами, создал условия для дальнейшего развития нашего сотрудничества, - сказал Первый Президент Казахстана.
@@ -6848,26 +6751,26 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
+    <row r="9">
+      <c r="A9" s="3" t="n">
         <v>43598</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана принял Управляющего Международным финансовым центром «Астана» Кайрата Келимбетова</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-prinyal-upravlyayuschego-mezhdunarodnym-finansovym</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи Елбасы Н.Назарбаеву была представлена информация о текущей деятельности и дальнейших планах работы МФЦА.
 Нурсултан Назарбаев подчеркнул важность проводимой работы по развитию Международного финансового центра «Астана».
@@ -6875,26 +6778,26 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
+    <row r="10">
+      <c r="A10" s="3" t="n">
         <v>43601</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Елбасы Нурсултан Назарбаев принял участие в работе XII Астанинского экономического форума «Вдохновляющий рост: люди, города, экономики»</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-nursultan-nazarbaev-prinyal-uchastie-v-rabote-xii-astaninskogo-ekonomicheskogo</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Выступая перед участниками пленарного заседания Форума, Первый Президент Казахстана подчеркнул важную роль АЭФ в процессе преодоления региональных и глобальных вызовов.
 - Рекомендации и идеи, которые обсуждались здесь в предыдущие годы, во многом помогли Казахстану своевременно реагировать на глобальные вызовы и успешно преодолевать трудности. Вы знаете, казахстанская модель развития вопреки всем обстоятельствам и прогнозам уже доказала свою устойчивость и эффективность. Мы ставили амбициозные цели, и мы их достигали, - сказал Нурсултан Назарбаев.
@@ -6906,26 +6809,26 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
+    <row r="11">
+      <c r="A11" s="3" t="n">
         <v>43602</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Нурсултан Назарбаев принял исполнительного директора Фонда Первого Президента РК – Елбасы Асета Исекешева</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/nursultan-nazarbaev-prinyal-ispolnitelnogo-direktora-fonda-pervogo-prezidenta-rk</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи Асет Исекешев доложил о работе Фонда в 2019 году, а также о реализации мероприятий и социальных проектов, в том числе направленных на поддержку талантливой молодежи.
 Кроме того, исполнительный директор Фонда презентовал Елбасы новые направления работы и программы Фонда в сферах образования, культуры, международной деятельности, по усилению экспертно-аналитической работы и в других областях.
@@ -6933,26 +6836,26 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>43602</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана принял председателя Верховного суда Жакипа Асанова</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-prinyal-predsedatelya-verkhovnogo-suda-zhakipa-asanova</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Елбасы Н.Назарбаев был проинформирован о ходе модернизации судебной системы.
 Председатель Верховного суда, в частности, доложил, что на сегодняшний день разработано 15 законопроектов, направленных на улучшение качества деятельности судов и повышение доверия населения к работе судей.
@@ -6960,26 +6863,26 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
+    <row r="13">
+      <c r="A13" s="3" t="n">
         <v>43605</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Елбасы принял президента АОО «Назарбаев Университет» Шигео Катсу</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-prinyal-prezidenta-aoo-nazarbaev-universitet-shigeo-katsu</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи Первому Президенту Казахстана было доложено о текущем развитии «Назарбаев Университета» и ходе подготовки к пятой церемонии вручения дипломов выпускникам вуза.
 - Многие не верили, что у нас будет университет международного уровня. И вот Вы уже долгие годы являетесь ректором такого университета. У вуза есть интеллектуальный потенциал – ученые, которые поднимают уровень учебного заведения. «Назарбаев Университет» стал одним из брендов Казахстана, - сказал Елбасы.
@@ -6987,51 +6890,51 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
+    <row r="14">
+      <c r="A14" s="3" t="n">
         <v>43605</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Нурсултан Назарбаев встретился с председателем Комитета по финансам и бюджету Мажилиса Парламента Гульжаной Карагусовой</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/nursultan-nazarbaev-vstretilsya-s-predsedatelem-komiteta-po-finansam-i-byudzhetu</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи были обсуждены вопросы законотворческой работы Комитета в сфере бюджетного планирования и налоговой политики.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
+    <row r="15">
+      <c r="A15" s="3" t="n">
         <v>43606</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Елбасы Нурсултан Назарбаев принял министра труда и социальной защиты населения Бердибека Сапарбаева</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-nursultan-nazarbaev-prinyal-ministra-truda-i-socialnoy-zaschity-naseleniya</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Елбасы Нурсултан Назарбаев принял министра труда и социальной защиты населения Бердибека Сапарбаева В ходе встречи Елбасы был проинформирован о деятельности Правительственной рабочей группы по разъяснению новых социальных мер «Әлеуметтік қамқорлық».
 Первый Президент Казахстана отметил, что Б.Сапарбаев обладает достаточным опытом и управленческими навыками для решения поставленных перед министерством задач.
@@ -7044,26 +6947,26 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
+    <row r="16">
+      <c r="A16" s="3" t="n">
         <v>43606</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Елбасы принял молодого композитора Рахат-Би Абдысагина</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-prinyal-molodogo-kompozitora-rakhat-bi-abdysagina</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи талантливый композитор, один из победителей конкурса «100 новых лиц Казахстана» представил Нурсултану Назарбаеву свою новую оперу «Путь, освещенный солнцем».
 Музыкальное произведение будет посвящено истории становления и развития Независимого Казахстана.
@@ -7071,26 +6974,26 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
+    <row r="17">
+      <c r="A17" s="3" t="n">
         <v>43607</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Заседание Совета по управлению Фондом национального благосостояния «Самрук-Казына» под председательством Первого Президента Республики Казахстан – Елбасы</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/zasedanie-soveta-po-upravleniyu-fondom-nacionalnogo-blagosostoyaniya-samruk-kazyna-pod</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>В совещании приняли участие Премьер-министр А. Мамин, Руководитель Администрации Президента Б. Сагинтаев, председатель правления АО «Самрук-Казына» А.Есимов, независимый директор АО «Самрук-Казына» Р.Эванс, помощник Первого Президента Д. Акишев, члены правления и руководители национальных компаний Фонда.
 На заседании был заслушан отчет о реализации стратегии развития АО «Самрук-Казына» на 2018-2028 годы, а также рассмотрен ход выполнения поручений по дальнейшей трансформации Фонда.
@@ -7108,26 +7011,26 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
+    <row r="18">
+      <c r="A18" s="3" t="n">
         <v>43608</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана Нурсултан Назарбаев посетил Республиканский общественный штаб кандидата от партии «Nur Otan»</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-nursultan-nazarbaev-posetil-respublikanskiy</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Елбасы встретился с членами Республиканского общественного штаба и провел селекторное совещание с руководителями региональных штабов.
 Открывая совещание, Нурсултан Назарбаев подчеркнул, что работа предвыборного штаба находится на его личном контроле.
@@ -7145,26 +7048,26 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
+    <row r="19">
+      <c r="A19" s="3" t="n">
         <v>43609</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Елбасы Нурсултан Назарбаев встретился с министром иностранных дел Турецкой Республики Мевлютом Чавушоглу</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-nursultan-nazarbaev-vstretilsya-s-ministrom-inostrannykh-del-tureckoy</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи Первый Президент Казахстана отметил важность сохранения и дальнейшего углубления сотрудничества между двумя братскими странами.
 - С первых дней независимости Турция всегда поддерживала нас. Наши государства и народы очень близки друг к другу. Мы ввели безвизовый режим между двумя странами. Отношения Казахстана и Турции крепнут год от года. Уверен, что этот курс будет продолжен, - сказал Елбасы.
@@ -7177,47 +7080,47 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
+    <row r="20">
+      <c r="A20" s="3" t="n">
         <v>43610</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>РЕШЕНИЯ</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Решением Первого Президента Республики Казахстан – Елбасы в соответствии с Законом Республики Казахстан «О государственной службе Республики Казахстан» в связи с достижением пенсионного возраста Танирберген Саидмурат Бапанулы освобожден от должности заведующего Секретариатом Совета Безопасности Республики Казахстан</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/resheniem-pervogo-prezidenta-respubliki-kazakhstan-elbasy-v-sootvetstvii-s-zakonom</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="E20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
         <v>43613</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Елбасы встретился с Премьер-Министром Республики Армения Николом Пашиняном</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-vstretilsya-s-premer-ministrom-respubliki-armeniya-nikolom-pashinyanom</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Поприветствовав высокого гостя, Нурсултан Назарбаев отметил важность развития и укрепления двусторонних торгово-экономических отношений.
 - Между Казахстаном и Арменией всегда были добрые отношения. Армянская диаспора в Казахстане является мостом между нашими странами, - сказал Елбасы.
@@ -7227,26 +7130,26 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
+    <row r="22">
+      <c r="A22" s="3" t="n">
         <v>43613</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Елбасы встретился с Президентом Кыргызской Республики Сооронбаем Жээнбековым</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-vstretilsya-s-prezidentom-kyrgyzskoy-respubliki-sooronbaem-zheenbekovym</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи Нурсултан Назарбаев вручил Сооронбаю Жээнбекову орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
 Первый Президент Казахстана подчеркнул высокий уровень отношений между двумя братскими народами.
@@ -7256,26 +7159,26 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
+    <row r="23">
+      <c r="A23" s="3" t="n">
         <v>43613</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Нурсултан Назарбаев встретился с Президентом Республики Таджикистан Эмомали Рахмоном</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/nursultan-nazarbaev-vstretilsya-s-prezidentom-respubliki-tadzhikistan-emomali</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>В ходе переговоров Елбасы отметил, что с первых дней сотрудничества Казахстан и Таджикистан построили крепкие дружественные и доверительные отношения.
 - Наша дружба крепнет год от года. Вы возглавляете Таджикистан в условиях сложной ситуации в мире. Вы поступательно развиваетесь, в стране обеспечивается стабильность, - сказал Нурсултан Назарбаев.
@@ -7285,26 +7188,26 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
+    <row r="24">
+      <c r="A24" s="3" t="n">
         <v>43613</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Нурсултан Назарбаев встретился с Президентом Российской Федерации Владимиром Путиным</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/nursultan-nazarbaev-vstretilsya-s-prezidentom-rossiyskoy-federacii-vladimirom-putinym</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи Елбасы лично вручил Владимиру Путину орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
 Первый Президент Казахстана отметил текущие результаты и перспективы дальнейшего развития Евразийского экономического союза.
@@ -7314,26 +7217,26 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
+    <row r="25">
+      <c r="A25" s="3" t="n">
         <v>43613</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана принял председателя Коллегии Евразийской экономической комиссии Тиграна Саркисяна</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-prinyal-predsedatelya-kollegii-evraziyskoy-ekonomicheskoy</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи стороны обсудили текущее состояние и перспективы развития Евразийского экономического союза.
 Нурсултан Назарбаев подчеркнул, что многие страны и организации заинтересованы в налаживании сотрудничества с ЕАЭС и указал на необходимость расширения географии экономических партнеров союза.
@@ -7343,26 +7246,26 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
+    <row r="26">
+      <c r="A26" s="3" t="n">
         <v>43613</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана встретился с Президентом Республики Беларусь Александром Лукашенко</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-vstretilsya-s-prezidentom-respubliki-belarus-aleksandrom</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи Елбасы вручил высокому гостю орден «Қазақстан Республикасының Тұңғыш Президенті – Елбасы Нұрсұлтан Назарбаев».
 Первый Президент Казахстана особо отметил роль и вклад Александра Лукашенко в развитие интеграционных процессов и становление Евразийского экономического союза.
@@ -7374,26 +7277,26 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
+    <row r="27">
+      <c r="A27" s="3" t="n">
         <v>43614</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Нурсултан Назарбаев принял участие в заседании Высшего Евразийского экономического совета в расширенном составе</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/nursultan-nazarbaev-prinyal-uchastie-v-zasedanii-vysshego-evraziyskogo-ekonomicheskogo</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>После заседания в узком составе Елбасы принял участие в заседании Высшего Евразийского экономического совета в расширенном формате.
 В своем выступлении Первый Президент Казахстана выразил благодарность Президенту Российской Федерации Владимиру Путину за инициативу по присвоению звания Почетного Председателя Высшего Евразийского экономического совета и всем членам ВЕЭС за поддержку данного предложения.
@@ -7412,26 +7315,26 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
+    <row r="28">
+      <c r="A28" s="3" t="n">
         <v>43616</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Елбасы принял участие в церемонии открытия нового Атлетического центра Назарбаев Университета</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/elbasy-prinyal-uchastie-v-ceremonii-otkrytiya-novogo-atleticheskogo-centra-nazarbaev</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана посетил новое многофункциональное спортивное сооружение Назарбаев Университета.
 В Атлетическом центре учебного заведения предусмотрена все необходимая спортивная инфраструктура, в том числе олимпийский бассейн, паркетная арена на 660 зрителей, тренажерный зал и зал единоборств. Объект оснащен передовыми технологиями спортивной индустрии.
@@ -7439,26 +7342,26 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
+    <row r="29">
+      <c r="A29" s="3" t="n">
         <v>43616</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана вручил дипломы с отличием выпускникам Назарбаев Университета</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-vruchil-diplomy-s-otlichiem-vypusknikam-nazarbaev</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Выступая перед участниками церемонии, Елбасы поздравил всех выпускников со знаменательным событием в их жизни. Первый Президент Казахстана подчеркнул, что за предыдущие четыре выпуска Университет окончили более 2 600 студентов.
 - Выпускники Университета – это конкурентоспособные специалисты, востребованные как на Родине, так и за рубежом. Из завершающих сегодня обучение 963 выпускников 565 окончили программы бакалавриата, 378 – магистратуру, 20 – докторантуру. Более 40 процентов выпускников-бакалавров решили продолжить свое обучение, получив приглашение в лучшие вузы мира, - сказал Нурсултан Назарбаев.
@@ -7474,26 +7377,26 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
+    <row r="30">
+      <c r="A30" s="3" t="n">
         <v>43616</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана встретился с Председателем Европейского совета Дональдом Туском</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-05/pervyy-prezident-kazakhstana-vstretilsya-s-predsedatelem-evropeyskogo-soveta-donaldom</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Поприветствовав гостя, Нурсултан Назарбаев отметил высокий уровень развития взаимоотношений между Казахстаном и Европейским союзом.
 - Мы встречались с вами несколько раз. В период вашего председательства было заключено Соглашение о расширенном партнерстве и сотрудничестве между Европейским Союзом и Республикой Казахстан. В этом году ожидается завершение его ратификации. В целом, у нас хорошие перспективы, - сказал Елбасы.
@@ -7503,26 +7406,26 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
+    <row r="31">
+      <c r="A31" s="3" t="n">
         <v>43620</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Елбасы Нурсултан Назарбаев принял заведующего Секретариатом, заместителя Председателя Ассамблеи народа Казахстана Жансеита Туймебаева</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/elbasy-nursultan-nazarbaev-prinyal-zaveduyuschego-sekretariatom-zamestitelya</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи Первому Президенту Казахстана было доложено о текущей деятельности Ассамблеи и предпринимаемых мерах по реализации задач, озвученных в ходе XXVII сессии.
 Нурсултан Назарбаев особо подчеркнул важность проводимой Ассамблеей работы по сохранению стабильности и укреплению единства в обществе.
@@ -7532,26 +7435,26 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
+    <row r="32">
+      <c r="A32" s="3" t="n">
         <v>43620</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>ТЕЛЕФОННЫЕ ЗВОНКИ</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Состоялся телефонный разговор Первого Президента Республики Казахстан – Елбасы Нурсултана Назарбаева с Президентом Турецкой Республики Реджепом Тайипом Эрдоганом</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/sostoyalsya-telefonnyy-razgovor-pervogo-prezidenta-respubliki-kazakhstan-elbasy</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>В ходе телефонного разговора Реджеп Тайип Эрдоган поздравил Нурсултана Назарбаева с праздником Ораза айт и пожелал ему крепкого здоровья и новых успехов, а народу Казахстана – процветания и благополучия.
 В ходе беседы стороны также обменялись мнениями по наиболее актуальным вопросам казахстанско-турецкого сотрудничества, а также региональной и международной повестки дня.
@@ -7559,26 +7462,26 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
+    <row r="33">
+      <c r="A33" s="3" t="n">
         <v>43622</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Нурсултану Назарбаеву присвоен статус «Почетный сенатор»</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/nursultanu-nazarbaevu-prisvoen-status-pochetnyy-senator</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Перед началом пленарного заседания Сената Парламента состоялась церемония присвоения Елбасы статуса «Почетный сенатор».
 В ходе своего выступления Первый Президент Казахстана поблагодарил всех депутатов за поддержку и высокую оценку его деятельности.
@@ -7592,26 +7495,26 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
+    <row r="34">
+      <c r="A34" s="3" t="n">
         <v>43624</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Нурсултан Назарбаев встретился с экс-Президентом Республики Хорватия Степаном Месичем</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/nursultan-nazarbaev-vstretilsya-s-eks-prezidentom-respubliki-khorvatiya-stepanom</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи Елбасы поприветствовал высокого гостя и поблагодарил его за участие в предстоящих выборах президента в качестве независимого наблюдателя.
 - Спасибо за то, что Вы принимаете участие в выборах как наблюдатель. Вы присутствовали на выборах прошлых лет и дали высокую оценку нашей работе. Я благодарен Вам, - сказал Первый Президент Казахстана.
@@ -7619,26 +7522,26 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
+    <row r="35">
+      <c r="A35" s="3" t="n">
         <v>43625</v>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана посетил избирательный участок №58 города Нур-Султан</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/pervyy-prezident-kazakhstana-posetil-izbiratelnyy-uchastok-no58-goroda-nur-sultan</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Елбасы принял участие в процедуре голосования на выборах Президента Республики Казахстан, состоявшейся в здании столичного Дворца школьников.
 Выступая перед представителями СМИ, Нурсултан Назарбаев подчеркнул, что в этих исторических выборах народ Казахстана определяет будущее страны.
@@ -7649,68 +7552,68 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
+    <row r="36">
+      <c r="A36" s="3" t="n">
         <v>43629</v>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>РЕШЕНИЯ</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Решением Первого Президента Республики Казахстан – Елбасы Ашимбекулы Ардак назначен первым заместителем начальника Службы государственной охраны Республики Казахстан – начальником службы безопасности Первого Президента Республики Казахстан – Елбасы</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/resheniem-pervogo-prezidenta-respubliki-kazakhstan-elbasy-ashimbekuly-ardak-naznachen</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="E36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
         <v>43631</v>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>РЕШЕНИЯ</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Решением Первого Президента Республики Казахстан – Елбасы, Председателя Совета Безопасности Республики Казахстан Елшибеков Чокан Жанатович назначен заведующим Секретариатом Совета Безопасности Республики Казахстан</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/resheniem-pervogo-prezidenta-respubliki-kazakhstan-elbasy-predsedatelya-soveta</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="E37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
         <v>43636</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Нурсултан Назарбаев принял участие в церемонии открытия спортивного комплекса «Үшқоңыр»</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/nursultan-nazarbaev-prinyal-uchastie-v-ceremonii-otkrytiya-sportivnogo-kompleksa</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Елбасы, поздравив всех жителей региона с открытием спортивного комплекса «Үшқоңыр», подчеркнул значимость возведенного объекта в процессе воспитания и физического развития молодежи.
 – Сегодня мы отрываем уникальный для района спортивный комплекс. В здоровом теле – здоровый дух. В современном мире только здоровый человек добивается успеха. Поэтому, мы возвели этот объект специально для нашей молодежи, – сказал Первый Президент Казахстана.
@@ -7721,26 +7624,26 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
+    <row r="39">
+      <c r="A39" s="3" t="n">
         <v>43637</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Елбасы Нурсултан Назарбаев заложил капсулу времени с посланием к будущему поколению</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/elbasy-nursultan-nazarbaev-zalozhil-kapsulu-vremeni-s-poslaniem-k-buduschemu</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана, выступая перед участниками церемонии, подчеркнул особую значимость послания для будущего поколения казахстанцев.
 - За годы Независимости Казахстан достиг немалых высот. Старшее поколение хорошо знает, через что нам пришлось пройти, чтобы сегодняшняя молодежь жила счастливо. Мы работали во благо развития страны, открыли Казахстан миру, - сказал Елбасы.
@@ -7751,26 +7654,26 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
+    <row r="40">
+      <c r="A40" s="3" t="n">
         <v>43637</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана принял участие в Международной научно-практической конференции «30 лет лидерства»</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/pervyy-prezident-kazakhstana-prinyal-uchastie-v-mezhdunarodnoy-nauchno-prakticheskoy</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Выступая перед участниками конференции, Елбасы отметил, что вся его деятельность на посту первого руководителя страны была посвящена развитию Казахстана.
 Нурсултан Назарбаев рассказал о трудностях на пути строительства и становления Независимости. В частности, Первый Президент Казахстана напомнил о ситуации в стране в начале 1990-х годов, связанной с развалом национальной экономики и рисками возникновения межэтнических конфликтов.
@@ -7784,26 +7687,26 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
+    <row r="41">
+      <c r="A41" s="3" t="n">
         <v>43642</v>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана принял акима г.Нур-Султана Алтая Кульгинова</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/pervyy-prezident-kazakhstana-prinyal-akima-gnur-sultana-altaya-kulginova</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>В ходе встречи Елбасы подчеркнул, что на акима столицы возложена большая ответственность за дальнейшее развитие главного города страны.
 – Столица любого государства всегда находится под пристальным вниманием руководства страны и правительства. На акима столицы возлагается высокая ответственность. Все гости страны в первую очередь посещают главный город Казахстана. И по уровню развития столицы можно судить о развитии всего государства, – сказал Нурсултан Назарбаев.
@@ -7815,26 +7718,26 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
+    <row r="42">
+      <c r="A42" s="3" t="n">
         <v>43642</v>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Заседание Совета Безопасности под председательством Первого Президента Республики Казахстан – Елбасы Нурсултана Назарбаева</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/zasedanie-soveta-bezopasnosti-pod-predsedatelstvom-pervogo-prezidenta-respubliki</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>В ходе заседания была рассмотрена текущая ситуация в городе Арысь Туркестанской области и обсуждены вопросы обеспечения водной безопасности страны.
 Председатель Совета Безопасности, выразив искренние соболезнования родным и близким погибших в Арыси, отметил самоотверженный труд работников всех служб и волонтеров, принимающих участие в ликвидации последствий взрывов.
@@ -7846,26 +7749,26 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="n">
+    <row r="43">
+      <c r="A43" s="3" t="n">
         <v>43644</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Первый Президент Казахстана посетил новую столичную мечеть</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/pervyy-prezident-kazakhstana-posetil-novuyu-stolichnuyu-mechet</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Елбасы посетил новую мечеть, расположенную в Сарыаркинском районе столицы.
 Ранее озвучивалось предложение о возведении новой мечети именно в этой части города, население которой превышает 380 тысяч человек. Нурсултан Назарбаев поддержал данную инициативу.
@@ -7874,26 +7777,26 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
+    <row r="44">
+      <c r="A44" s="3" t="n">
         <v>43645</v>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>СОБЫТИЯ</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Нурсултан Назарбаев посетил центральный аппарат партии «Nur Otan»</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>https://nazarbayev.kz/ru/news/2019-06/nursultan-nazarbaev-posetil-centralnyy-apparat-partii-nur-otan</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>В ходе посещения Елбасы представил нового первого заместителя Председателя партии «Nur Otan».
 Первый Президент Казахстана отметил наличие у Бауыржана Байбек соответствующих опыта и навыков для реализации поставленных задач перед партией.

--- a/output/Каталог_2019_май.xlsx
+++ b/output/Каталог_2019_май.xlsx
@@ -5825,7 +5825,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>высокая</t>
+          <t>выбрано вручную</t>
         </is>
       </c>
     </row>
